--- a/fuentes/precios_banana_BJLapa.xlsx
+++ b/fuentes/precios_banana_BJLapa.xlsx
@@ -103,7 +103,7 @@
         </is>
       </c>
       <c r="C2" s="0">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D2" s="0">
         <v>9</v>
@@ -122,7 +122,7 @@
         </is>
       </c>
       <c r="H2" s="0">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -137,7 +137,7 @@
         </is>
       </c>
       <c r="C3" s="0">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D3" s="0">
         <v>9</v>
@@ -156,7 +156,7 @@
         </is>
       </c>
       <c r="H3" s="0">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -171,7 +171,7 @@
         </is>
       </c>
       <c r="C4" s="0">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="D4" s="0">
         <v>9</v>
@@ -190,7 +190,7 @@
         </is>
       </c>
       <c r="H4" s="0">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -205,7 +205,7 @@
         </is>
       </c>
       <c r="C5" s="0">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="D5" s="0">
         <v>9</v>
@@ -224,7 +224,7 @@
         </is>
       </c>
       <c r="H5" s="0">
-        <v>1.98</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -239,10 +239,10 @@
         </is>
       </c>
       <c r="C6" s="0">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="D6" s="0">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E6" s="0">
         <v>2026</v>
@@ -258,7 +258,7 @@
         </is>
       </c>
       <c r="H6" s="0">
-        <v>1.36</v>
+        <v>1.13</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -273,10 +273,10 @@
         </is>
       </c>
       <c r="C7" s="0">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="D7" s="0">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E7" s="0">
         <v>2026</v>
@@ -292,7 +292,7 @@
         </is>
       </c>
       <c r="H7" s="0">
-        <v>2.24</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -307,10 +307,10 @@
         </is>
       </c>
       <c r="C8" s="0">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="D8" s="0">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E8" s="0">
         <v>2026</v>
@@ -326,7 +326,7 @@
         </is>
       </c>
       <c r="H8" s="0">
-        <v>1.3</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -341,10 +341,10 @@
         </is>
       </c>
       <c r="C9" s="0">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="D9" s="0">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E9" s="0">
         <v>2026</v>
@@ -360,7 +360,7 @@
         </is>
       </c>
       <c r="H9" s="0">
-        <v>2.23</v>
+        <v>1.98</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -375,7 +375,7 @@
         </is>
       </c>
       <c r="C10" s="0">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="D10" s="0">
         <v>8</v>
@@ -394,7 +394,7 @@
         </is>
       </c>
       <c r="H10" s="0">
-        <v>2.14</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -409,7 +409,7 @@
         </is>
       </c>
       <c r="C11" s="0">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="D11" s="0">
         <v>8</v>
@@ -428,7 +428,7 @@
         </is>
       </c>
       <c r="H11" s="0">
-        <v>2.53</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -443,7 +443,7 @@
         </is>
       </c>
       <c r="C12" s="0">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="D12" s="0">
         <v>8</v>
@@ -462,7 +462,7 @@
         </is>
       </c>
       <c r="H12" s="0">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="C13" s="0">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="D13" s="0">
         <v>8</v>
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="H13" s="0">
-        <v>2.66</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -511,10 +511,10 @@
         </is>
       </c>
       <c r="C14" s="0">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="D14" s="0">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E14" s="0">
         <v>2026</v>
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="H14" s="0">
-        <v>2.4</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -545,10 +545,10 @@
         </is>
       </c>
       <c r="C15" s="0">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="D15" s="0">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E15" s="0">
         <v>2026</v>
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="H15" s="0">
-        <v>2.4</v>
+        <v>2.53</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -579,10 +579,10 @@
         </is>
       </c>
       <c r="C16" s="0">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="D16" s="0">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E16" s="0">
         <v>2026</v>
@@ -594,17 +594,17 @@
       </c>
       <c r="G16" s="0" t="inlineStr">
         <is>
-          <t>Cento</t>
+          <t>quilograma</t>
         </is>
       </c>
       <c r="H16" s="0">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="0" t="inlineStr">
         <is>
-          <t>Nanica primeira - produtor</t>
+          <t>Prata anã primeira - produtor</t>
         </is>
       </c>
       <c r="B17" s="0" t="inlineStr">
@@ -613,10 +613,10 @@
         </is>
       </c>
       <c r="C17" s="0">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="D17" s="0">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E17" s="0">
         <v>2026</v>
@@ -632,13 +632,13 @@
         </is>
       </c>
       <c r="H17" s="0">
-        <v>2.22</v>
+        <v>2.66</v>
       </c>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="0" t="inlineStr">
         <is>
-          <t>Prata anã primeira - produtor</t>
+          <t>Nanica primeira - produtor</t>
         </is>
       </c>
       <c r="B18" s="0" t="inlineStr">
@@ -647,7 +647,7 @@
         </is>
       </c>
       <c r="C18" s="0">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="D18" s="0">
         <v>7</v>
@@ -666,13 +666,13 @@
         </is>
       </c>
       <c r="H18" s="0">
-        <v>2.07</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="0" t="inlineStr">
         <is>
-          <t>Nanica primeira - produtor</t>
+          <t>Prata anã primeira - produtor</t>
         </is>
       </c>
       <c r="B19" s="0" t="inlineStr">
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="C19" s="0">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D19" s="0">
         <v>7</v>
@@ -700,13 +700,13 @@
         </is>
       </c>
       <c r="H19" s="0">
-        <v>2.13</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="0" t="inlineStr">
         <is>
-          <t>Prata anã primeira - produtor</t>
+          <t>Nanica primeira - produtor</t>
         </is>
       </c>
       <c r="B20" s="0" t="inlineStr">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="C20" s="0">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D20" s="0">
         <v>7</v>
@@ -730,11 +730,11 @@
       </c>
       <c r="G20" s="0" t="inlineStr">
         <is>
-          <t>quilograma</t>
+          <t>Cento</t>
         </is>
       </c>
       <c r="H20" s="0">
-        <v>1.83</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="C21" s="0">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="D21" s="0">
         <v>7</v>
@@ -764,17 +764,17 @@
       </c>
       <c r="G21" s="0" t="inlineStr">
         <is>
-          <t>Cento</t>
+          <t>quilograma</t>
         </is>
       </c>
       <c r="H21" s="0">
-        <v>1.9</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="0" t="inlineStr">
         <is>
-          <t>Nanica primeira - produtor</t>
+          <t>Prata anã primeira - produtor</t>
         </is>
       </c>
       <c r="B22" s="0" t="inlineStr">
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="C22" s="0">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="D22" s="0">
         <v>7</v>
@@ -802,13 +802,13 @@
         </is>
       </c>
       <c r="H22" s="0">
-        <v>1.72</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="0" t="inlineStr">
         <is>
-          <t>Prata anã primeira - produtor</t>
+          <t>Nanica primeira - produtor</t>
         </is>
       </c>
       <c r="B23" s="0" t="inlineStr">
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="C23" s="0">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D23" s="0">
         <v>7</v>
@@ -836,13 +836,13 @@
         </is>
       </c>
       <c r="H23" s="0">
-        <v>1.91</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="0" t="inlineStr">
         <is>
-          <t>Nanica primeira - produtor</t>
+          <t>Prata anã primeira - produtor</t>
         </is>
       </c>
       <c r="B24" s="0" t="inlineStr">
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="C24" s="0">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="D24" s="0">
         <v>7</v>
@@ -870,13 +870,13 @@
         </is>
       </c>
       <c r="H24" s="0">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="0" t="inlineStr">
         <is>
-          <t>Prata anã primeira - produtor</t>
+          <t>Nanica primeira - produtor</t>
         </is>
       </c>
       <c r="B25" s="0" t="inlineStr">
@@ -885,7 +885,7 @@
         </is>
       </c>
       <c r="C25" s="0">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D25" s="0">
         <v>7</v>
@@ -900,11 +900,11 @@
       </c>
       <c r="G25" s="0" t="inlineStr">
         <is>
-          <t>quilograma</t>
+          <t>Cento</t>
         </is>
       </c>
       <c r="H25" s="0">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="C26" s="0">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="D26" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E26" s="0">
         <v>2026</v>
@@ -938,7 +938,7 @@
         </is>
       </c>
       <c r="H26" s="0">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -953,10 +953,10 @@
         </is>
       </c>
       <c r="C27" s="0">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="D27" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E27" s="0">
         <v>2026</v>
@@ -972,7 +972,7 @@
         </is>
       </c>
       <c r="H27" s="0">
-        <v>2.37</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -987,10 +987,10 @@
         </is>
       </c>
       <c r="C28" s="0">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="D28" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E28" s="0">
         <v>2026</v>
@@ -1006,7 +1006,7 @@
         </is>
       </c>
       <c r="H28" s="0">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="C29" s="0">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="D29" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E29" s="0">
         <v>2026</v>
@@ -1040,7 +1040,7 @@
         </is>
       </c>
       <c r="H29" s="0">
-        <v>2.3</v>
+        <v>1.98</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -1055,7 +1055,7 @@
         </is>
       </c>
       <c r="C30" s="0">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="D30" s="0">
         <v>6</v>
@@ -1074,7 +1074,7 @@
         </is>
       </c>
       <c r="H30" s="0">
-        <v>1.56</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -1089,7 +1089,7 @@
         </is>
       </c>
       <c r="C31" s="0">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="D31" s="0">
         <v>6</v>
@@ -1108,7 +1108,7 @@
         </is>
       </c>
       <c r="H31" s="0">
-        <v>2.58</v>
+        <v>2.37</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -1123,7 +1123,7 @@
         </is>
       </c>
       <c r="C32" s="0">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="D32" s="0">
         <v>6</v>
@@ -1142,7 +1142,7 @@
         </is>
       </c>
       <c r="H32" s="0">
-        <v>1.12</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="C33" s="0">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="D33" s="0">
         <v>6</v>
@@ -1176,7 +1176,7 @@
         </is>
       </c>
       <c r="H33" s="0">
-        <v>2.63</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -1191,10 +1191,10 @@
         </is>
       </c>
       <c r="C34" s="0">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="D34" s="0">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E34" s="0">
         <v>2026</v>
@@ -1210,7 +1210,7 @@
         </is>
       </c>
       <c r="H34" s="0">
-        <v>0.86</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="C35" s="0">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="D35" s="0">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E35" s="0">
         <v>2026</v>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="H35" s="0">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -1259,10 +1259,10 @@
         </is>
       </c>
       <c r="C36" s="0">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="D36" s="0">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E36" s="0">
         <v>2026</v>
@@ -1278,7 +1278,7 @@
         </is>
       </c>
       <c r="H36" s="0">
-        <v>0.61</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -1293,10 +1293,10 @@
         </is>
       </c>
       <c r="C37" s="0">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="D37" s="0">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E37" s="0">
         <v>2026</v>
@@ -1327,7 +1327,7 @@
         </is>
       </c>
       <c r="C38" s="0">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="D38" s="0">
         <v>5</v>
@@ -1346,7 +1346,7 @@
         </is>
       </c>
       <c r="H38" s="0">
-        <v>0.62</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="C39" s="0">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="D39" s="0">
         <v>5</v>
@@ -1380,7 +1380,7 @@
         </is>
       </c>
       <c r="H39" s="0">
-        <v>2.66</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -1395,7 +1395,7 @@
         </is>
       </c>
       <c r="C40" s="0">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="D40" s="0">
         <v>5</v>
@@ -1414,13 +1414,13 @@
         </is>
       </c>
       <c r="H40" s="0">
-        <v>0.75</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="0" t="inlineStr">
         <is>
-          <t>Nanica primeira - produtor</t>
+          <t>Prata anã primeira - produtor</t>
         </is>
       </c>
       <c r="B41" s="0" t="inlineStr">
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="C41" s="0">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="D41" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E41" s="0">
         <v>2026</v>
@@ -1448,13 +1448,13 @@
         </is>
       </c>
       <c r="H41" s="0">
-        <v>0.93</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="0" t="inlineStr">
         <is>
-          <t>Prata anã primeira - produtor</t>
+          <t>Nanica primeira - produtor</t>
         </is>
       </c>
       <c r="B42" s="0" t="inlineStr">
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="C42" s="0">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="D42" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E42" s="0">
         <v>2026</v>
@@ -1482,13 +1482,13 @@
         </is>
       </c>
       <c r="H42" s="0">
-        <v>3.08</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="0" t="inlineStr">
         <is>
-          <t>Nanica primeira - produtor</t>
+          <t>Prata anã primeira - produtor</t>
         </is>
       </c>
       <c r="B43" s="0" t="inlineStr">
@@ -1497,10 +1497,10 @@
         </is>
       </c>
       <c r="C43" s="0">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D43" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E43" s="0">
         <v>2026</v>
@@ -1516,13 +1516,13 @@
         </is>
       </c>
       <c r="H43" s="0">
-        <v>0.93</v>
+        <v>2.66</v>
       </c>
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="0" t="inlineStr">
         <is>
-          <t>Prata anã primeira - produtor</t>
+          <t>Nanica primeira - produtor</t>
         </is>
       </c>
       <c r="B44" s="0" t="inlineStr">
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="C44" s="0">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="D44" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E44" s="0">
         <v>2026</v>
@@ -1550,7 +1550,7 @@
         </is>
       </c>
       <c r="H44" s="0">
-        <v>3.04</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="45" spans="1:8">
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="C45" s="0">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="D45" s="0">
         <v>4</v>
@@ -1584,7 +1584,7 @@
         </is>
       </c>
       <c r="H45" s="0">
-        <v>1.02</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="46" spans="1:8">
@@ -1599,7 +1599,7 @@
         </is>
       </c>
       <c r="C46" s="0">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="D46" s="0">
         <v>4</v>
@@ -1618,7 +1618,7 @@
         </is>
       </c>
       <c r="H46" s="0">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="47" spans="1:8">
@@ -1633,7 +1633,7 @@
         </is>
       </c>
       <c r="C47" s="0">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="D47" s="0">
         <v>4</v>
@@ -1652,7 +1652,7 @@
         </is>
       </c>
       <c r="H47" s="0">
-        <v>1.27</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="48" spans="1:8">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="C48" s="0">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="D48" s="0">
         <v>4</v>
@@ -1686,7 +1686,7 @@
         </is>
       </c>
       <c r="H48" s="0">
-        <v>3.12</v>
+        <v>3.04</v>
       </c>
     </row>
     <row r="49" spans="1:8">
@@ -1701,7 +1701,7 @@
         </is>
       </c>
       <c r="C49" s="0">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="D49" s="0">
         <v>4</v>
@@ -1720,7 +1720,7 @@
         </is>
       </c>
       <c r="H49" s="0">
-        <v>1.56</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="50" spans="1:8">
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="C50" s="0">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="D50" s="0">
         <v>4</v>
@@ -1754,7 +1754,7 @@
         </is>
       </c>
       <c r="H50" s="0">
-        <v>3.13</v>
+        <v>3.09</v>
       </c>
     </row>
     <row r="51" spans="1:8">
@@ -1769,10 +1769,10 @@
         </is>
       </c>
       <c r="C51" s="0">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="D51" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E51" s="0">
         <v>2026</v>
@@ -1788,7 +1788,7 @@
         </is>
       </c>
       <c r="H51" s="0">
-        <v>2.04</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="52" spans="1:8">
@@ -1803,10 +1803,10 @@
         </is>
       </c>
       <c r="C52" s="0">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="D52" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E52" s="0">
         <v>2026</v>
@@ -1822,7 +1822,7 @@
         </is>
       </c>
       <c r="H52" s="0">
-        <v>3.23</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="53" spans="1:8">
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="C53" s="0">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="D53" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E53" s="0">
         <v>2026</v>
@@ -1856,7 +1856,7 @@
         </is>
       </c>
       <c r="H53" s="0">
-        <v>2.36</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="54" spans="1:8">
@@ -1871,10 +1871,10 @@
         </is>
       </c>
       <c r="C54" s="0">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="D54" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E54" s="0">
         <v>2026</v>
@@ -1890,7 +1890,7 @@
         </is>
       </c>
       <c r="H54" s="0">
-        <v>3.4</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="55" spans="1:8">
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="C55" s="0">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="D55" s="0">
         <v>3</v>
@@ -1924,7 +1924,7 @@
         </is>
       </c>
       <c r="H55" s="0">
-        <v>2.23</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="56" spans="1:8">
@@ -1939,7 +1939,7 @@
         </is>
       </c>
       <c r="C56" s="0">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="D56" s="0">
         <v>3</v>
@@ -1958,7 +1958,7 @@
         </is>
       </c>
       <c r="H56" s="0">
-        <v>3.19</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="57" spans="1:8">
@@ -1973,7 +1973,7 @@
         </is>
       </c>
       <c r="C57" s="0">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="D57" s="0">
         <v>3</v>
@@ -1992,7 +1992,7 @@
         </is>
       </c>
       <c r="H57" s="0">
-        <v>1.9</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="58" spans="1:8">
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="C58" s="0">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="D58" s="0">
         <v>3</v>
@@ -2026,7 +2026,7 @@
         </is>
       </c>
       <c r="H58" s="0">
-        <v>3.11</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="59" spans="1:8">
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="C59" s="0">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="D59" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E59" s="0">
         <v>2026</v>
@@ -2060,7 +2060,7 @@
         </is>
       </c>
       <c r="H59" s="0">
-        <v>1.65</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="60" spans="1:8">
@@ -2075,10 +2075,10 @@
         </is>
       </c>
       <c r="C60" s="0">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="D60" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E60" s="0">
         <v>2026</v>
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="H60" s="0">
-        <v>3</v>
+        <v>3.19</v>
       </c>
     </row>
     <row r="61" spans="1:8">
@@ -2109,10 +2109,10 @@
         </is>
       </c>
       <c r="C61" s="0">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="D61" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E61" s="0">
         <v>2026</v>
@@ -2128,7 +2128,7 @@
         </is>
       </c>
       <c r="H61" s="0">
-        <v>1.63</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="62" spans="1:8">
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="C62" s="0">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="D62" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E62" s="0">
         <v>2026</v>
@@ -2162,7 +2162,7 @@
         </is>
       </c>
       <c r="H62" s="0">
-        <v>3.27</v>
+        <v>3.11</v>
       </c>
     </row>
     <row r="63" spans="1:8">
@@ -2177,7 +2177,7 @@
         </is>
       </c>
       <c r="C63" s="0">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="D63" s="0">
         <v>2</v>
@@ -2196,7 +2196,7 @@
         </is>
       </c>
       <c r="H63" s="0">
-        <v>1.24</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="64" spans="1:8">
@@ -2211,7 +2211,7 @@
         </is>
       </c>
       <c r="C64" s="0">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="D64" s="0">
         <v>2</v>
@@ -2230,7 +2230,7 @@
         </is>
       </c>
       <c r="H64" s="0">
-        <v>3.06</v>
+        <v>3</v>
       </c>
     </row>
     <row r="65" spans="1:8">
@@ -2245,7 +2245,7 @@
         </is>
       </c>
       <c r="C65" s="0">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="D65" s="0">
         <v>2</v>
@@ -2264,7 +2264,7 @@
         </is>
       </c>
       <c r="H65" s="0">
-        <v>1.17</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="66" spans="1:8">
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="C66" s="0">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="D66" s="0">
         <v>2</v>
@@ -2298,7 +2298,7 @@
         </is>
       </c>
       <c r="H66" s="0">
-        <v>3.05</v>
+        <v>3.27</v>
       </c>
     </row>
     <row r="67" spans="1:8">
@@ -2313,10 +2313,10 @@
         </is>
       </c>
       <c r="C67" s="0">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="D67" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E67" s="0">
         <v>2026</v>
@@ -2332,7 +2332,7 @@
         </is>
       </c>
       <c r="H67" s="0">
-        <v>1</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="68" spans="1:8">
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="C68" s="0">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="D68" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E68" s="0">
         <v>2026</v>
@@ -2366,7 +2366,7 @@
         </is>
       </c>
       <c r="H68" s="0">
-        <v>3.01</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="69" spans="1:8">
@@ -2381,10 +2381,10 @@
         </is>
       </c>
       <c r="C69" s="0">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="D69" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E69" s="0">
         <v>2026</v>
@@ -2400,7 +2400,7 @@
         </is>
       </c>
       <c r="H69" s="0">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="70" spans="1:8">
@@ -2415,10 +2415,10 @@
         </is>
       </c>
       <c r="C70" s="0">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="D70" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E70" s="0">
         <v>2026</v>
@@ -2434,7 +2434,7 @@
         </is>
       </c>
       <c r="H70" s="0">
-        <v>2.97</v>
+        <v>3.05</v>
       </c>
     </row>
     <row r="71" spans="1:8">
@@ -2449,7 +2449,7 @@
         </is>
       </c>
       <c r="C71" s="0">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="D71" s="0">
         <v>1</v>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="H71" s="0">
-        <v>1.64</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72" spans="1:8">
@@ -2483,7 +2483,7 @@
         </is>
       </c>
       <c r="C72" s="0">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="D72" s="0">
         <v>1</v>
@@ -2502,7 +2502,7 @@
         </is>
       </c>
       <c r="H72" s="0">
-        <v>3.49</v>
+        <v>3.01</v>
       </c>
     </row>
     <row r="73" spans="1:8">
@@ -2517,7 +2517,7 @@
         </is>
       </c>
       <c r="C73" s="0">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="D73" s="0">
         <v>1</v>
@@ -2536,7 +2536,7 @@
         </is>
       </c>
       <c r="H73" s="0">
-        <v>2.06</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="74" spans="1:8">
@@ -2551,7 +2551,7 @@
         </is>
       </c>
       <c r="C74" s="0">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="D74" s="0">
         <v>1</v>
@@ -2570,7 +2570,7 @@
         </is>
       </c>
       <c r="H74" s="0">
-        <v>3.63</v>
+        <v>2.97</v>
       </c>
     </row>
     <row r="75" spans="1:8">
@@ -2585,7 +2585,7 @@
         </is>
       </c>
       <c r="C75" s="0">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="D75" s="0">
         <v>1</v>
@@ -2604,7 +2604,7 @@
         </is>
       </c>
       <c r="H75" s="0">
-        <v>2.63</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="76" spans="1:8">
@@ -2619,7 +2619,7 @@
         </is>
       </c>
       <c r="C76" s="0">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="D76" s="0">
         <v>1</v>
@@ -2653,13 +2653,13 @@
         </is>
       </c>
       <c r="C77" s="0">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="D77" s="0">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E77" s="0">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="F77" s="0" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
         </is>
       </c>
       <c r="H77" s="0">
-        <v>2.67</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="78" spans="1:8">
@@ -2687,13 +2687,13 @@
         </is>
       </c>
       <c r="C78" s="0">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="D78" s="0">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E78" s="0">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="F78" s="0" t="inlineStr">
         <is>
@@ -2706,13 +2706,13 @@
         </is>
       </c>
       <c r="H78" s="0">
-        <v>3.4</v>
+        <v>3.63</v>
       </c>
     </row>
     <row r="79" spans="1:8">
       <c r="A79" s="0" t="inlineStr">
         <is>
-          <t>Prata litoral primeira - produtor</t>
+          <t>Nanica primeira - produtor</t>
         </is>
       </c>
       <c r="B79" s="0" t="inlineStr">
@@ -2721,13 +2721,13 @@
         </is>
       </c>
       <c r="C79" s="0">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="D79" s="0">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E79" s="0">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="F79" s="0" t="inlineStr">
         <is>
@@ -2740,13 +2740,13 @@
         </is>
       </c>
       <c r="H79" s="0">
-        <v>3</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="80" spans="1:8">
       <c r="A80" s="0" t="inlineStr">
         <is>
-          <t>Nanica primeira - produtor</t>
+          <t>Prata anã primeira - produtor</t>
         </is>
       </c>
       <c r="B80" s="0" t="inlineStr">
@@ -2755,13 +2755,13 @@
         </is>
       </c>
       <c r="C80" s="0">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="D80" s="0">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E80" s="0">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="F80" s="0" t="inlineStr">
         <is>
@@ -2774,13 +2774,13 @@
         </is>
       </c>
       <c r="H80" s="0">
-        <v>2.83</v>
+        <v>3.49</v>
       </c>
     </row>
     <row r="81" spans="1:8">
       <c r="A81" s="0" t="inlineStr">
         <is>
-          <t>Prata anã primeira - produtor</t>
+          <t>Nanica primeira - produtor</t>
         </is>
       </c>
       <c r="B81" s="0" t="inlineStr">
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="C81" s="0">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="D81" s="0">
         <v>12</v>
@@ -2808,13 +2808,13 @@
         </is>
       </c>
       <c r="H81" s="0">
-        <v>3.59</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="82" spans="1:8">
       <c r="A82" s="0" t="inlineStr">
         <is>
-          <t>Nanica primeira - produtor</t>
+          <t>Prata anã primeira - produtor</t>
         </is>
       </c>
       <c r="B82" s="0" t="inlineStr">
@@ -2823,7 +2823,7 @@
         </is>
       </c>
       <c r="C82" s="0">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="D82" s="0">
         <v>12</v>
@@ -2842,13 +2842,13 @@
         </is>
       </c>
       <c r="H82" s="0">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="83" spans="1:8">
       <c r="A83" s="0" t="inlineStr">
         <is>
-          <t>Prata anã primeira - produtor</t>
+          <t>Prata litoral primeira - produtor</t>
         </is>
       </c>
       <c r="B83" s="0" t="inlineStr">
@@ -2857,7 +2857,7 @@
         </is>
       </c>
       <c r="C83" s="0">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="D83" s="0">
         <v>12</v>
@@ -2876,7 +2876,7 @@
         </is>
       </c>
       <c r="H83" s="0">
-        <v>3.54</v>
+        <v>3</v>
       </c>
     </row>
     <row r="84" spans="1:8">
@@ -2891,7 +2891,7 @@
         </is>
       </c>
       <c r="C84" s="0">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="D84" s="0">
         <v>12</v>
@@ -2910,7 +2910,7 @@
         </is>
       </c>
       <c r="H84" s="0">
-        <v>2.89</v>
+        <v>2.83</v>
       </c>
     </row>
     <row r="85" spans="1:8">
@@ -2925,7 +2925,7 @@
         </is>
       </c>
       <c r="C85" s="0">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="D85" s="0">
         <v>12</v>
@@ -2944,7 +2944,7 @@
         </is>
       </c>
       <c r="H85" s="0">
-        <v>3.7</v>
+        <v>3.59</v>
       </c>
     </row>
     <row r="86" spans="1:8">
@@ -2959,10 +2959,10 @@
         </is>
       </c>
       <c r="C86" s="0">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="D86" s="0">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E86" s="0">
         <v>2025</v>
@@ -2978,7 +2978,7 @@
         </is>
       </c>
       <c r="H86" s="0">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="87" spans="1:8">
@@ -2993,10 +2993,10 @@
         </is>
       </c>
       <c r="C87" s="0">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="D87" s="0">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E87" s="0">
         <v>2025</v>
@@ -3012,7 +3012,7 @@
         </is>
       </c>
       <c r="H87" s="0">
-        <v>3.7</v>
+        <v>3.54</v>
       </c>
     </row>
     <row r="88" spans="1:8">
@@ -3027,10 +3027,10 @@
         </is>
       </c>
       <c r="C88" s="0">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="D88" s="0">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E88" s="0">
         <v>2025</v>
@@ -3046,7 +3046,7 @@
         </is>
       </c>
       <c r="H88" s="0">
-        <v>2.79</v>
+        <v>2.89</v>
       </c>
     </row>
     <row r="89" spans="1:8">
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="C89" s="0">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="D89" s="0">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E89" s="0">
         <v>2025</v>
@@ -3080,7 +3080,7 @@
         </is>
       </c>
       <c r="H89" s="0">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="90" spans="1:8">
@@ -3095,7 +3095,7 @@
         </is>
       </c>
       <c r="C90" s="0">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="D90" s="0">
         <v>11</v>
@@ -3114,7 +3114,7 @@
         </is>
       </c>
       <c r="H90" s="0">
-        <v>2.67</v>
+        <v>2.82</v>
       </c>
     </row>
     <row r="91" spans="1:8">
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="C91" s="0">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="D91" s="0">
         <v>11</v>
@@ -3148,7 +3148,7 @@
         </is>
       </c>
       <c r="H91" s="0">
-        <v>3.59</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="92" spans="1:8">
@@ -3163,7 +3163,7 @@
         </is>
       </c>
       <c r="C92" s="0">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="D92" s="0">
         <v>11</v>
@@ -3182,7 +3182,7 @@
         </is>
       </c>
       <c r="H92" s="0">
-        <v>2.68</v>
+        <v>2.79</v>
       </c>
     </row>
     <row r="93" spans="1:8">
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="C93" s="0">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="D93" s="0">
         <v>11</v>
@@ -3216,7 +3216,7 @@
         </is>
       </c>
       <c r="H93" s="0">
-        <v>3.2</v>
+        <v>3.58</v>
       </c>
     </row>
     <row r="94" spans="1:8">
@@ -3231,10 +3231,10 @@
         </is>
       </c>
       <c r="C94" s="0">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="D94" s="0">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E94" s="0">
         <v>2025</v>
@@ -3250,7 +3250,7 @@
         </is>
       </c>
       <c r="H94" s="0">
-        <v>2.98</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="95" spans="1:8">
@@ -3265,10 +3265,10 @@
         </is>
       </c>
       <c r="C95" s="0">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="D95" s="0">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E95" s="0">
         <v>2025</v>
@@ -3284,7 +3284,7 @@
         </is>
       </c>
       <c r="H95" s="0">
-        <v>2.43</v>
+        <v>3.59</v>
       </c>
     </row>
     <row r="96" spans="1:8">
@@ -3299,10 +3299,10 @@
         </is>
       </c>
       <c r="C96" s="0">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="D96" s="0">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E96" s="0">
         <v>2025</v>
@@ -3318,7 +3318,7 @@
         </is>
       </c>
       <c r="H96" s="0">
-        <v>2.77</v>
+        <v>2.68</v>
       </c>
     </row>
     <row r="97" spans="1:8">
@@ -3333,10 +3333,10 @@
         </is>
       </c>
       <c r="C97" s="0">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="D97" s="0">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E97" s="0">
         <v>2025</v>
@@ -3352,7 +3352,7 @@
         </is>
       </c>
       <c r="H97" s="0">
-        <v>2.25</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="98" spans="1:8">
@@ -3367,7 +3367,7 @@
         </is>
       </c>
       <c r="C98" s="0">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D98" s="0">
         <v>10</v>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="H98" s="0">
-        <v>2.88</v>
+        <v>2.98</v>
       </c>
     </row>
     <row r="99" spans="1:8">
@@ -3401,7 +3401,7 @@
         </is>
       </c>
       <c r="C99" s="0">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D99" s="0">
         <v>10</v>
@@ -3420,7 +3420,7 @@
         </is>
       </c>
       <c r="H99" s="0">
-        <v>2.31</v>
+        <v>2.43</v>
       </c>
     </row>
     <row r="100" spans="1:8">
@@ -3435,7 +3435,7 @@
         </is>
       </c>
       <c r="C100" s="0">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="D100" s="0">
         <v>10</v>
@@ -3454,7 +3454,7 @@
         </is>
       </c>
       <c r="H100" s="0">
-        <v>2.96</v>
+        <v>2.77</v>
       </c>
     </row>
     <row r="101" spans="1:8">
@@ -3469,7 +3469,7 @@
         </is>
       </c>
       <c r="C101" s="0">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="D101" s="0">
         <v>10</v>
@@ -3488,7 +3488,7 @@
         </is>
       </c>
       <c r="H101" s="0">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="102" spans="1:8">
@@ -3503,7 +3503,7 @@
         </is>
       </c>
       <c r="C102" s="0">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="D102" s="0">
         <v>10</v>
@@ -3522,7 +3522,7 @@
         </is>
       </c>
       <c r="H102" s="0">
-        <v>2.98</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="103" spans="1:8">
@@ -3537,7 +3537,7 @@
         </is>
       </c>
       <c r="C103" s="0">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="D103" s="0">
         <v>10</v>
@@ -3556,7 +3556,7 @@
         </is>
       </c>
       <c r="H103" s="0">
-        <v>2.6</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="104" spans="1:8">
@@ -3571,10 +3571,10 @@
         </is>
       </c>
       <c r="C104" s="0">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="D104" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E104" s="0">
         <v>2025</v>
@@ -3590,7 +3590,7 @@
         </is>
       </c>
       <c r="H104" s="0">
-        <v>2.99</v>
+        <v>2.96</v>
       </c>
     </row>
     <row r="105" spans="1:8">
@@ -3605,10 +3605,10 @@
         </is>
       </c>
       <c r="C105" s="0">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="D105" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E105" s="0">
         <v>2025</v>
@@ -3624,7 +3624,7 @@
         </is>
       </c>
       <c r="H105" s="0">
-        <v>3.11</v>
+        <v>2.37</v>
       </c>
     </row>
     <row r="106" spans="1:8">
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="C106" s="0">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="D106" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E106" s="0">
         <v>2025</v>
@@ -3658,7 +3658,7 @@
         </is>
       </c>
       <c r="H106" s="0">
-        <v>3.03</v>
+        <v>2.98</v>
       </c>
     </row>
     <row r="107" spans="1:8">
@@ -3673,10 +3673,10 @@
         </is>
       </c>
       <c r="C107" s="0">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="D107" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E107" s="0">
         <v>2025</v>
@@ -3692,7 +3692,7 @@
         </is>
       </c>
       <c r="H107" s="0">
-        <v>3.77</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="108" spans="1:8">
@@ -3707,7 +3707,7 @@
         </is>
       </c>
       <c r="C108" s="0">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="D108" s="0">
         <v>9</v>
@@ -3726,7 +3726,7 @@
         </is>
       </c>
       <c r="H108" s="0">
-        <v>2.96</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="109" spans="1:8">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="C109" s="0">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="D109" s="0">
         <v>9</v>
@@ -3760,7 +3760,7 @@
         </is>
       </c>
       <c r="H109" s="0">
-        <v>3.61</v>
+        <v>3.11</v>
       </c>
     </row>
     <row r="110" spans="1:8">
@@ -3775,7 +3775,7 @@
         </is>
       </c>
       <c r="C110" s="0">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="D110" s="0">
         <v>9</v>
@@ -3794,7 +3794,7 @@
         </is>
       </c>
       <c r="H110" s="0">
-        <v>2.84</v>
+        <v>3.03</v>
       </c>
     </row>
     <row r="111" spans="1:8">
@@ -3809,7 +3809,7 @@
         </is>
       </c>
       <c r="C111" s="0">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="D111" s="0">
         <v>9</v>
@@ -3828,7 +3828,7 @@
         </is>
       </c>
       <c r="H111" s="0">
-        <v>3.48</v>
+        <v>3.77</v>
       </c>
     </row>
     <row r="112" spans="1:8">
@@ -3843,10 +3843,10 @@
         </is>
       </c>
       <c r="C112" s="0">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="D112" s="0">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E112" s="0">
         <v>2025</v>
@@ -3862,7 +3862,7 @@
         </is>
       </c>
       <c r="H112" s="0">
-        <v>3.12</v>
+        <v>2.96</v>
       </c>
     </row>
     <row r="113" spans="1:8">
@@ -3877,10 +3877,10 @@
         </is>
       </c>
       <c r="C113" s="0">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="D113" s="0">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E113" s="0">
         <v>2025</v>
@@ -3896,7 +3896,7 @@
         </is>
       </c>
       <c r="H113" s="0">
-        <v>3.72</v>
+        <v>3.61</v>
       </c>
     </row>
     <row r="114" spans="1:8">
@@ -3911,10 +3911,10 @@
         </is>
       </c>
       <c r="C114" s="0">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="D114" s="0">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E114" s="0">
         <v>2025</v>
@@ -3930,7 +3930,7 @@
         </is>
       </c>
       <c r="H114" s="0">
-        <v>3.06</v>
+        <v>2.84</v>
       </c>
     </row>
     <row r="115" spans="1:8">
@@ -3945,10 +3945,10 @@
         </is>
       </c>
       <c r="C115" s="0">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="D115" s="0">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E115" s="0">
         <v>2025</v>
@@ -3964,7 +3964,7 @@
         </is>
       </c>
       <c r="H115" s="0">
-        <v>3.6</v>
+        <v>3.48</v>
       </c>
     </row>
     <row r="116" spans="1:8">
@@ -3979,7 +3979,7 @@
         </is>
       </c>
       <c r="C116" s="0">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="D116" s="0">
         <v>8</v>
@@ -3998,7 +3998,7 @@
         </is>
       </c>
       <c r="H116" s="0">
-        <v>3.06</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="117" spans="1:8">
@@ -4013,7 +4013,7 @@
         </is>
       </c>
       <c r="C117" s="0">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="D117" s="0">
         <v>8</v>
@@ -4032,7 +4032,7 @@
         </is>
       </c>
       <c r="H117" s="0">
-        <v>3.67</v>
+        <v>3.72</v>
       </c>
     </row>
     <row r="118" spans="1:8">
@@ -4047,7 +4047,7 @@
         </is>
       </c>
       <c r="C118" s="0">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="D118" s="0">
         <v>8</v>
@@ -4066,7 +4066,7 @@
         </is>
       </c>
       <c r="H118" s="0">
-        <v>2.73</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="119" spans="1:8">
@@ -4081,7 +4081,7 @@
         </is>
       </c>
       <c r="C119" s="0">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="D119" s="0">
         <v>8</v>
@@ -4100,7 +4100,7 @@
         </is>
       </c>
       <c r="H119" s="0">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="120" spans="1:8">
@@ -4115,10 +4115,10 @@
         </is>
       </c>
       <c r="C120" s="0">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="D120" s="0">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E120" s="0">
         <v>2025</v>
@@ -4134,7 +4134,7 @@
         </is>
       </c>
       <c r="H120" s="0">
-        <v>2.3</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="121" spans="1:8">
@@ -4149,10 +4149,10 @@
         </is>
       </c>
       <c r="C121" s="0">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="D121" s="0">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E121" s="0">
         <v>2025</v>
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="H121" s="0">
-        <v>3.16</v>
+        <v>3.67</v>
       </c>
     </row>
     <row r="122" spans="1:8">
@@ -4183,10 +4183,10 @@
         </is>
       </c>
       <c r="C122" s="0">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="D122" s="0">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E122" s="0">
         <v>2025</v>
@@ -4202,7 +4202,7 @@
         </is>
       </c>
       <c r="H122" s="0">
-        <v>1.61</v>
+        <v>2.73</v>
       </c>
     </row>
     <row r="123" spans="1:8">
@@ -4217,10 +4217,10 @@
         </is>
       </c>
       <c r="C123" s="0">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="D123" s="0">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E123" s="0">
         <v>2025</v>
@@ -4236,7 +4236,7 @@
         </is>
       </c>
       <c r="H123" s="0">
-        <v>2.97</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="124" spans="1:8">
@@ -4251,7 +4251,7 @@
         </is>
       </c>
       <c r="C124" s="0">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="D124" s="0">
         <v>7</v>
@@ -4270,7 +4270,7 @@
         </is>
       </c>
       <c r="H124" s="0">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="125" spans="1:8">
@@ -4285,7 +4285,7 @@
         </is>
       </c>
       <c r="C125" s="0">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="D125" s="0">
         <v>7</v>
@@ -4304,7 +4304,7 @@
         </is>
       </c>
       <c r="H125" s="0">
-        <v>2.79</v>
+        <v>3.16</v>
       </c>
     </row>
     <row r="126" spans="1:8">
@@ -4319,7 +4319,7 @@
         </is>
       </c>
       <c r="C126" s="0">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D126" s="0">
         <v>7</v>
@@ -4338,7 +4338,7 @@
         </is>
       </c>
       <c r="H126" s="0">
-        <v>1.34</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="127" spans="1:8">
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="C127" s="0">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D127" s="0">
         <v>7</v>
@@ -4372,7 +4372,7 @@
         </is>
       </c>
       <c r="H127" s="0">
-        <v>2.69</v>
+        <v>2.97</v>
       </c>
     </row>
     <row r="128" spans="1:8">
@@ -4387,7 +4387,7 @@
         </is>
       </c>
       <c r="C128" s="0">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="D128" s="0">
         <v>7</v>
@@ -4406,7 +4406,7 @@
         </is>
       </c>
       <c r="H128" s="0">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="129" spans="1:8">
@@ -4421,7 +4421,7 @@
         </is>
       </c>
       <c r="C129" s="0">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="D129" s="0">
         <v>7</v>
@@ -4440,7 +4440,7 @@
         </is>
       </c>
       <c r="H129" s="0">
-        <v>2.82</v>
+        <v>2.79</v>
       </c>
     </row>
     <row r="130" spans="1:8">
@@ -4455,10 +4455,10 @@
         </is>
       </c>
       <c r="C130" s="0">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="D130" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E130" s="0">
         <v>2025</v>
@@ -4474,7 +4474,7 @@
         </is>
       </c>
       <c r="H130" s="0">
-        <v>1.21</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="131" spans="1:8">
@@ -4489,10 +4489,10 @@
         </is>
       </c>
       <c r="C131" s="0">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="D131" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E131" s="0">
         <v>2025</v>
@@ -4508,7 +4508,7 @@
         </is>
       </c>
       <c r="H131" s="0">
-        <v>2.73</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="132" spans="1:8">
@@ -4523,10 +4523,10 @@
         </is>
       </c>
       <c r="C132" s="0">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="D132" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E132" s="0">
         <v>2025</v>
@@ -4542,7 +4542,7 @@
         </is>
       </c>
       <c r="H132" s="0">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="133" spans="1:8">
@@ -4557,10 +4557,10 @@
         </is>
       </c>
       <c r="C133" s="0">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="D133" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E133" s="0">
         <v>2025</v>
@@ -4576,7 +4576,7 @@
         </is>
       </c>
       <c r="H133" s="0">
-        <v>2.57</v>
+        <v>2.82</v>
       </c>
     </row>
     <row r="134" spans="1:8">
@@ -4591,7 +4591,7 @@
         </is>
       </c>
       <c r="C134" s="0">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="D134" s="0">
         <v>6</v>
@@ -4610,7 +4610,7 @@
         </is>
       </c>
       <c r="H134" s="0">
-        <v>1.06</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="135" spans="1:8">
@@ -4625,7 +4625,7 @@
         </is>
       </c>
       <c r="C135" s="0">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="D135" s="0">
         <v>6</v>
@@ -4644,7 +4644,7 @@
         </is>
       </c>
       <c r="H135" s="0">
-        <v>2.4</v>
+        <v>2.73</v>
       </c>
     </row>
     <row r="136" spans="1:8">
@@ -4659,7 +4659,7 @@
         </is>
       </c>
       <c r="C136" s="0">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="D136" s="0">
         <v>6</v>
@@ -4678,7 +4678,7 @@
         </is>
       </c>
       <c r="H136" s="0">
-        <v>0.93</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="137" spans="1:8">
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="C137" s="0">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="D137" s="0">
         <v>6</v>
@@ -4712,7 +4712,7 @@
         </is>
       </c>
       <c r="H137" s="0">
-        <v>2.23</v>
+        <v>2.57</v>
       </c>
     </row>
     <row r="138" spans="1:8">
@@ -4727,10 +4727,10 @@
         </is>
       </c>
       <c r="C138" s="0">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="D138" s="0">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E138" s="0">
         <v>2025</v>
@@ -4746,7 +4746,7 @@
         </is>
       </c>
       <c r="H138" s="0">
-        <v>0.73</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="139" spans="1:8">
@@ -4761,10 +4761,10 @@
         </is>
       </c>
       <c r="C139" s="0">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="D139" s="0">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E139" s="0">
         <v>2025</v>
@@ -4780,7 +4780,7 @@
         </is>
       </c>
       <c r="H139" s="0">
-        <v>2.23</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="140" spans="1:8">
@@ -4795,10 +4795,10 @@
         </is>
       </c>
       <c r="C140" s="0">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="D140" s="0">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E140" s="0">
         <v>2025</v>
@@ -4814,7 +4814,7 @@
         </is>
       </c>
       <c r="H140" s="0">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="141" spans="1:8">
@@ -4829,10 +4829,10 @@
         </is>
       </c>
       <c r="C141" s="0">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="D141" s="0">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E141" s="0">
         <v>2025</v>
@@ -4848,7 +4848,7 @@
         </is>
       </c>
       <c r="H141" s="0">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="142" spans="1:8">
@@ -4863,7 +4863,7 @@
         </is>
       </c>
       <c r="C142" s="0">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="D142" s="0">
         <v>5</v>
@@ -4882,7 +4882,7 @@
         </is>
       </c>
       <c r="H142" s="0">
-        <v>0.89</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="143" spans="1:8">
@@ -4897,7 +4897,7 @@
         </is>
       </c>
       <c r="C143" s="0">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="D143" s="0">
         <v>5</v>
@@ -4916,7 +4916,7 @@
         </is>
       </c>
       <c r="H143" s="0">
-        <v>2.53</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="144" spans="1:8">
@@ -4931,7 +4931,7 @@
         </is>
       </c>
       <c r="C144" s="0">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="D144" s="0">
         <v>5</v>
@@ -4950,7 +4950,7 @@
         </is>
       </c>
       <c r="H144" s="0">
-        <v>1.01</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="145" spans="1:8">
@@ -4965,7 +4965,7 @@
         </is>
       </c>
       <c r="C145" s="0">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="D145" s="0">
         <v>5</v>
@@ -4984,7 +4984,7 @@
         </is>
       </c>
       <c r="H145" s="0">
-        <v>2.66</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="146" spans="1:8">
@@ -4999,7 +4999,7 @@
         </is>
       </c>
       <c r="C146" s="0">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="D146" s="0">
         <v>5</v>
@@ -5018,7 +5018,7 @@
         </is>
       </c>
       <c r="H146" s="0">
-        <v>1.31</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="147" spans="1:8">
@@ -5033,7 +5033,7 @@
         </is>
       </c>
       <c r="C147" s="0">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="D147" s="0">
         <v>5</v>
@@ -5052,7 +5052,7 @@
         </is>
       </c>
       <c r="H147" s="0">
-        <v>3.19</v>
+        <v>2.53</v>
       </c>
     </row>
     <row r="148" spans="1:8">
@@ -5067,10 +5067,10 @@
         </is>
       </c>
       <c r="C148" s="0">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D148" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E148" s="0">
         <v>2025</v>
@@ -5086,7 +5086,7 @@
         </is>
       </c>
       <c r="H148" s="0">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="149" spans="1:8">
@@ -5101,10 +5101,10 @@
         </is>
       </c>
       <c r="C149" s="0">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D149" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E149" s="0">
         <v>2025</v>
@@ -5120,7 +5120,7 @@
         </is>
       </c>
       <c r="H149" s="0">
-        <v>3.26</v>
+        <v>2.66</v>
       </c>
     </row>
     <row r="150" spans="1:8">
@@ -5135,10 +5135,10 @@
         </is>
       </c>
       <c r="C150" s="0">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="D150" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E150" s="0">
         <v>2025</v>
@@ -5154,7 +5154,7 @@
         </is>
       </c>
       <c r="H150" s="0">
-        <v>1.39</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="151" spans="1:8">
@@ -5169,10 +5169,10 @@
         </is>
       </c>
       <c r="C151" s="0">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="D151" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E151" s="0">
         <v>2025</v>
@@ -5188,7 +5188,7 @@
         </is>
       </c>
       <c r="H151" s="0">
-        <v>3.12</v>
+        <v>3.19</v>
       </c>
     </row>
     <row r="152" spans="1:8">
@@ -5203,7 +5203,7 @@
         </is>
       </c>
       <c r="C152" s="0">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D152" s="0">
         <v>4</v>
@@ -5222,7 +5222,7 @@
         </is>
       </c>
       <c r="H152" s="0">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="153" spans="1:8">
@@ -5237,7 +5237,7 @@
         </is>
       </c>
       <c r="C153" s="0">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D153" s="0">
         <v>4</v>
@@ -5256,7 +5256,7 @@
         </is>
       </c>
       <c r="H153" s="0">
-        <v>2.94</v>
+        <v>3.26</v>
       </c>
     </row>
     <row r="154" spans="1:8">
@@ -5271,7 +5271,7 @@
         </is>
       </c>
       <c r="C154" s="0">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="D154" s="0">
         <v>4</v>
@@ -5290,7 +5290,7 @@
         </is>
       </c>
       <c r="H154" s="0">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="155" spans="1:8">
@@ -5305,7 +5305,7 @@
         </is>
       </c>
       <c r="C155" s="0">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="D155" s="0">
         <v>4</v>
@@ -5324,7 +5324,7 @@
         </is>
       </c>
       <c r="H155" s="0">
-        <v>2.81</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="156" spans="1:8">
@@ -5339,10 +5339,10 @@
         </is>
       </c>
       <c r="C156" s="0">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="D156" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E156" s="0">
         <v>2025</v>
@@ -5358,7 +5358,7 @@
         </is>
       </c>
       <c r="H156" s="0">
-        <v>1.51</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="157" spans="1:8">
@@ -5373,10 +5373,10 @@
         </is>
       </c>
       <c r="C157" s="0">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="D157" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E157" s="0">
         <v>2025</v>
@@ -5392,7 +5392,7 @@
         </is>
       </c>
       <c r="H157" s="0">
-        <v>3.18</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="158" spans="1:8">
@@ -5407,10 +5407,10 @@
         </is>
       </c>
       <c r="C158" s="0">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="D158" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E158" s="0">
         <v>2025</v>
@@ -5426,7 +5426,7 @@
         </is>
       </c>
       <c r="H158" s="0">
-        <v>1.6</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="159" spans="1:8">
@@ -5441,10 +5441,10 @@
         </is>
       </c>
       <c r="C159" s="0">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="D159" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E159" s="0">
         <v>2025</v>
@@ -5460,7 +5460,7 @@
         </is>
       </c>
       <c r="H159" s="0">
-        <v>3.58</v>
+        <v>2.81</v>
       </c>
     </row>
     <row r="160" spans="1:8">
@@ -5475,7 +5475,7 @@
         </is>
       </c>
       <c r="C160" s="0">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="D160" s="0">
         <v>3</v>
@@ -5494,7 +5494,7 @@
         </is>
       </c>
       <c r="H160" s="0">
-        <v>1.69</v>
+        <v>1.51</v>
       </c>
     </row>
     <row r="161" spans="1:8">
@@ -5509,7 +5509,7 @@
         </is>
       </c>
       <c r="C161" s="0">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="D161" s="0">
         <v>3</v>
@@ -5528,7 +5528,7 @@
         </is>
       </c>
       <c r="H161" s="0">
-        <v>3.75</v>
+        <v>3.18</v>
       </c>
     </row>
     <row r="162" spans="1:8">
@@ -5543,7 +5543,7 @@
         </is>
       </c>
       <c r="C162" s="0">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="D162" s="0">
         <v>3</v>
@@ -5562,7 +5562,7 @@
         </is>
       </c>
       <c r="H162" s="0">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="163" spans="1:8">
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="C163" s="0">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="D163" s="0">
         <v>3</v>
@@ -5596,7 +5596,7 @@
         </is>
       </c>
       <c r="H163" s="0">
-        <v>3.59</v>
+        <v>3.58</v>
       </c>
     </row>
     <row r="164" spans="1:8">
@@ -5611,10 +5611,10 @@
         </is>
       </c>
       <c r="C164" s="0">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="D164" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E164" s="0">
         <v>2025</v>
@@ -5630,7 +5630,7 @@
         </is>
       </c>
       <c r="H164" s="0">
-        <v>1.63</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="165" spans="1:8">
@@ -5645,10 +5645,10 @@
         </is>
       </c>
       <c r="C165" s="0">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="D165" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E165" s="0">
         <v>2025</v>
@@ -5664,7 +5664,7 @@
         </is>
       </c>
       <c r="H165" s="0">
-        <v>3.66</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="166" spans="1:8">
@@ -5679,10 +5679,10 @@
         </is>
       </c>
       <c r="C166" s="0">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="D166" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E166" s="0">
         <v>2025</v>
@@ -5698,7 +5698,7 @@
         </is>
       </c>
       <c r="H166" s="0">
-        <v>1.87</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="167" spans="1:8">
@@ -5713,10 +5713,10 @@
         </is>
       </c>
       <c r="C167" s="0">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="D167" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E167" s="0">
         <v>2025</v>
@@ -5732,7 +5732,7 @@
         </is>
       </c>
       <c r="H167" s="0">
-        <v>3.71</v>
+        <v>3.59</v>
       </c>
     </row>
     <row r="168" spans="1:8">
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="C168" s="0">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="D168" s="0">
         <v>2</v>
@@ -5766,7 +5766,7 @@
         </is>
       </c>
       <c r="H168" s="0">
-        <v>1.69</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="169" spans="1:8">
@@ -5781,7 +5781,7 @@
         </is>
       </c>
       <c r="C169" s="0">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="D169" s="0">
         <v>2</v>
@@ -5800,7 +5800,7 @@
         </is>
       </c>
       <c r="H169" s="0">
-        <v>3.79</v>
+        <v>3.66</v>
       </c>
     </row>
     <row r="170" spans="1:8">
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="C170" s="0">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="D170" s="0">
         <v>2</v>
@@ -5834,7 +5834,7 @@
         </is>
       </c>
       <c r="H170" s="0">
-        <v>1.53</v>
+        <v>1.87</v>
       </c>
     </row>
     <row r="171" spans="1:8">
@@ -5849,7 +5849,7 @@
         </is>
       </c>
       <c r="C171" s="0">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="D171" s="0">
         <v>2</v>
@@ -5868,7 +5868,7 @@
         </is>
       </c>
       <c r="H171" s="0">
-        <v>3.42</v>
+        <v>3.71</v>
       </c>
     </row>
     <row r="172" spans="1:8">
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="C172" s="0">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="D172" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E172" s="0">
         <v>2025</v>
@@ -5902,7 +5902,7 @@
         </is>
       </c>
       <c r="H172" s="0">
-        <v>1.56</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="173" spans="1:8">
@@ -5917,10 +5917,10 @@
         </is>
       </c>
       <c r="C173" s="0">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="D173" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E173" s="0">
         <v>2025</v>
@@ -5936,7 +5936,7 @@
         </is>
       </c>
       <c r="H173" s="0">
-        <v>3.37</v>
+        <v>3.79</v>
       </c>
     </row>
     <row r="174" spans="1:8">
@@ -5951,10 +5951,10 @@
         </is>
       </c>
       <c r="C174" s="0">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="D174" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E174" s="0">
         <v>2025</v>
@@ -5970,7 +5970,7 @@
         </is>
       </c>
       <c r="H174" s="0">
-        <v>1.74</v>
+        <v>1.53</v>
       </c>
     </row>
     <row r="175" spans="1:8">
@@ -5985,10 +5985,10 @@
         </is>
       </c>
       <c r="C175" s="0">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="D175" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E175" s="0">
         <v>2025</v>
@@ -6004,7 +6004,7 @@
         </is>
       </c>
       <c r="H175" s="0">
-        <v>3.6</v>
+        <v>3.42</v>
       </c>
     </row>
     <row r="176" spans="1:8">
@@ -6019,7 +6019,7 @@
         </is>
       </c>
       <c r="C176" s="0">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D176" s="0">
         <v>1</v>
@@ -6038,7 +6038,7 @@
         </is>
       </c>
       <c r="H176" s="0">
-        <v>1.88</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="177" spans="1:8">
@@ -6053,7 +6053,7 @@
         </is>
       </c>
       <c r="C177" s="0">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D177" s="0">
         <v>1</v>
@@ -6072,7 +6072,7 @@
         </is>
       </c>
       <c r="H177" s="0">
-        <v>3.68</v>
+        <v>3.37</v>
       </c>
     </row>
     <row r="178" spans="1:8">
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="C178" s="0">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="D178" s="0">
         <v>1</v>
@@ -6106,7 +6106,7 @@
         </is>
       </c>
       <c r="H178" s="0">
-        <v>1.96</v>
+        <v>1.74</v>
       </c>
     </row>
     <row r="179" spans="1:8">
@@ -6121,7 +6121,7 @@
         </is>
       </c>
       <c r="C179" s="0">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="D179" s="0">
         <v>1</v>
@@ -6140,7 +6140,7 @@
         </is>
       </c>
       <c r="H179" s="0">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="180" spans="1:8">
@@ -6155,7 +6155,7 @@
         </is>
       </c>
       <c r="C180" s="0">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="D180" s="0">
         <v>1</v>
@@ -6174,7 +6174,7 @@
         </is>
       </c>
       <c r="H180" s="0">
-        <v>2.33</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="181" spans="1:8">
@@ -6189,7 +6189,7 @@
         </is>
       </c>
       <c r="C181" s="0">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="D181" s="0">
         <v>1</v>
@@ -6208,7 +6208,7 @@
         </is>
       </c>
       <c r="H181" s="0">
-        <v>3.02</v>
+        <v>3.68</v>
       </c>
     </row>
     <row r="182" spans="1:8">
@@ -6223,13 +6223,13 @@
         </is>
       </c>
       <c r="C182" s="0">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="D182" s="0">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E182" s="0">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="F182" s="0" t="inlineStr">
         <is>
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="H182" s="0">
-        <v>2.33</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="183" spans="1:8">
@@ -6257,13 +6257,13 @@
         </is>
       </c>
       <c r="C183" s="0">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="D183" s="0">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E183" s="0">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="F183" s="0" t="inlineStr">
         <is>
@@ -6276,7 +6276,7 @@
         </is>
       </c>
       <c r="H183" s="0">
-        <v>3.02</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="184" spans="1:8">
@@ -6291,13 +6291,13 @@
         </is>
       </c>
       <c r="C184" s="0">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="D184" s="0">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E184" s="0">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="F184" s="0" t="inlineStr">
         <is>
@@ -6310,7 +6310,7 @@
         </is>
       </c>
       <c r="H184" s="0">
-        <v>2.49</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="185" spans="1:8">
@@ -6325,13 +6325,13 @@
         </is>
       </c>
       <c r="C185" s="0">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="D185" s="0">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E185" s="0">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="F185" s="0" t="inlineStr">
         <is>
@@ -6344,7 +6344,7 @@
         </is>
       </c>
       <c r="H185" s="0">
-        <v>3</v>
+        <v>3.02</v>
       </c>
     </row>
     <row r="186" spans="1:8">
@@ -6359,7 +6359,7 @@
         </is>
       </c>
       <c r="C186" s="0">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="D186" s="0">
         <v>12</v>
@@ -6378,7 +6378,7 @@
         </is>
       </c>
       <c r="H186" s="0">
-        <v>2.48</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="187" spans="1:8">
@@ -6393,7 +6393,7 @@
         </is>
       </c>
       <c r="C187" s="0">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="D187" s="0">
         <v>12</v>
@@ -6412,7 +6412,7 @@
         </is>
       </c>
       <c r="H187" s="0">
-        <v>3.04</v>
+        <v>3.02</v>
       </c>
     </row>
     <row r="188" spans="1:8">
@@ -6427,7 +6427,7 @@
         </is>
       </c>
       <c r="C188" s="0">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="D188" s="0">
         <v>12</v>
@@ -6446,7 +6446,7 @@
         </is>
       </c>
       <c r="H188" s="0">
-        <v>2.61</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="189" spans="1:8">
@@ -6461,7 +6461,7 @@
         </is>
       </c>
       <c r="C189" s="0">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="D189" s="0">
         <v>12</v>
@@ -6480,7 +6480,7 @@
         </is>
       </c>
       <c r="H189" s="0">
-        <v>3.06</v>
+        <v>3</v>
       </c>
     </row>
     <row r="190" spans="1:8">
@@ -6495,10 +6495,10 @@
         </is>
       </c>
       <c r="C190" s="0">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="D190" s="0">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E190" s="0">
         <v>2024</v>
@@ -6514,7 +6514,7 @@
         </is>
       </c>
       <c r="H190" s="0">
-        <v>2.63</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="191" spans="1:8">
@@ -6529,10 +6529,10 @@
         </is>
       </c>
       <c r="C191" s="0">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="D191" s="0">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E191" s="0">
         <v>2024</v>
@@ -6548,7 +6548,7 @@
         </is>
       </c>
       <c r="H191" s="0">
-        <v>3.21</v>
+        <v>3.04</v>
       </c>
     </row>
     <row r="192" spans="1:8">
@@ -6563,10 +6563,10 @@
         </is>
       </c>
       <c r="C192" s="0">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="D192" s="0">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E192" s="0">
         <v>2024</v>
@@ -6582,7 +6582,7 @@
         </is>
       </c>
       <c r="H192" s="0">
-        <v>2.58</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="193" spans="1:8">
@@ -6597,10 +6597,10 @@
         </is>
       </c>
       <c r="C193" s="0">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="D193" s="0">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E193" s="0">
         <v>2024</v>
@@ -6616,7 +6616,7 @@
         </is>
       </c>
       <c r="H193" s="0">
-        <v>3.28</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="194" spans="1:8">
@@ -6631,7 +6631,7 @@
         </is>
       </c>
       <c r="C194" s="0">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="D194" s="0">
         <v>11</v>
@@ -6650,7 +6650,7 @@
         </is>
       </c>
       <c r="H194" s="0">
-        <v>2.22</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="195" spans="1:8">
@@ -6665,7 +6665,7 @@
         </is>
       </c>
       <c r="C195" s="0">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="D195" s="0">
         <v>11</v>
@@ -6684,7 +6684,7 @@
         </is>
       </c>
       <c r="H195" s="0">
-        <v>2.8</v>
+        <v>3.21</v>
       </c>
     </row>
     <row r="196" spans="1:8">
@@ -6699,7 +6699,7 @@
         </is>
       </c>
       <c r="C196" s="0">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="D196" s="0">
         <v>11</v>
@@ -6718,7 +6718,7 @@
         </is>
       </c>
       <c r="H196" s="0">
-        <v>2.22</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="197" spans="1:8">
@@ -6733,7 +6733,7 @@
         </is>
       </c>
       <c r="C197" s="0">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="D197" s="0">
         <v>11</v>
@@ -6752,7 +6752,7 @@
         </is>
       </c>
       <c r="H197" s="0">
-        <v>2.61</v>
+        <v>3.28</v>
       </c>
     </row>
     <row r="198" spans="1:8">
@@ -6767,10 +6767,10 @@
         </is>
       </c>
       <c r="C198" s="0">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D198" s="0">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E198" s="0">
         <v>2024</v>
@@ -6786,7 +6786,7 @@
         </is>
       </c>
       <c r="H198" s="0">
-        <v>2.45</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="199" spans="1:8">
@@ -6801,10 +6801,10 @@
         </is>
       </c>
       <c r="C199" s="0">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D199" s="0">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E199" s="0">
         <v>2024</v>
@@ -6820,7 +6820,7 @@
         </is>
       </c>
       <c r="H199" s="0">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="200" spans="1:8">
@@ -6835,10 +6835,10 @@
         </is>
       </c>
       <c r="C200" s="0">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="D200" s="0">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E200" s="0">
         <v>2024</v>
@@ -6854,7 +6854,7 @@
         </is>
       </c>
       <c r="H200" s="0">
-        <v>2.82</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="201" spans="1:8">
@@ -6869,10 +6869,10 @@
         </is>
       </c>
       <c r="C201" s="0">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="D201" s="0">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E201" s="0">
         <v>2024</v>
@@ -6888,7 +6888,7 @@
         </is>
       </c>
       <c r="H201" s="0">
-        <v>3</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="202" spans="1:8">
@@ -6903,7 +6903,7 @@
         </is>
       </c>
       <c r="C202" s="0">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="D202" s="0">
         <v>10</v>
@@ -6922,7 +6922,7 @@
         </is>
       </c>
       <c r="H202" s="0">
-        <v>2.84</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="203" spans="1:8">
@@ -6937,7 +6937,7 @@
         </is>
       </c>
       <c r="C203" s="0">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="D203" s="0">
         <v>10</v>
@@ -6956,7 +6956,7 @@
         </is>
       </c>
       <c r="H203" s="0">
-        <v>3.11</v>
+        <v>2.79</v>
       </c>
     </row>
     <row r="204" spans="1:8">
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="C204" s="0">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="D204" s="0">
         <v>10</v>
@@ -6990,7 +6990,7 @@
         </is>
       </c>
       <c r="H204" s="0">
-        <v>2.99</v>
+        <v>2.82</v>
       </c>
     </row>
     <row r="205" spans="1:8">
@@ -7005,7 +7005,7 @@
         </is>
       </c>
       <c r="C205" s="0">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="D205" s="0">
         <v>10</v>
@@ -7024,7 +7024,7 @@
         </is>
       </c>
       <c r="H205" s="0">
-        <v>3.04</v>
+        <v>3</v>
       </c>
     </row>
     <row r="206" spans="1:8">
@@ -7039,10 +7039,10 @@
         </is>
       </c>
       <c r="C206" s="0">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="D206" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E206" s="0">
         <v>2024</v>
@@ -7058,7 +7058,7 @@
         </is>
       </c>
       <c r="H206" s="0">
-        <v>3.06</v>
+        <v>2.84</v>
       </c>
     </row>
     <row r="207" spans="1:8">
@@ -7073,10 +7073,10 @@
         </is>
       </c>
       <c r="C207" s="0">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="D207" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E207" s="0">
         <v>2024</v>
@@ -7092,7 +7092,7 @@
         </is>
       </c>
       <c r="H207" s="0">
-        <v>3.27</v>
+        <v>3.11</v>
       </c>
     </row>
     <row r="208" spans="1:8">
@@ -7107,10 +7107,10 @@
         </is>
       </c>
       <c r="C208" s="0">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="D208" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E208" s="0">
         <v>2024</v>
@@ -7126,7 +7126,7 @@
         </is>
       </c>
       <c r="H208" s="0">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="209" spans="1:8">
@@ -7141,10 +7141,10 @@
         </is>
       </c>
       <c r="C209" s="0">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="D209" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E209" s="0">
         <v>2024</v>
@@ -7160,7 +7160,7 @@
         </is>
       </c>
       <c r="H209" s="0">
-        <v>3.45</v>
+        <v>3.04</v>
       </c>
     </row>
     <row r="210" spans="1:8">
@@ -7175,7 +7175,7 @@
         </is>
       </c>
       <c r="C210" s="0">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="D210" s="0">
         <v>9</v>
@@ -7194,7 +7194,7 @@
         </is>
       </c>
       <c r="H210" s="0">
-        <v>2.67</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="211" spans="1:8">
@@ -7209,7 +7209,7 @@
         </is>
       </c>
       <c r="C211" s="0">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="D211" s="0">
         <v>9</v>
@@ -7228,7 +7228,7 @@
         </is>
       </c>
       <c r="H211" s="0">
-        <v>3.5</v>
+        <v>3.27</v>
       </c>
     </row>
     <row r="212" spans="1:8">
@@ -7243,7 +7243,7 @@
         </is>
       </c>
       <c r="C212" s="0">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="D212" s="0">
         <v>9</v>
@@ -7262,7 +7262,7 @@
         </is>
       </c>
       <c r="H212" s="0">
-        <v>2.42</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="213" spans="1:8">
@@ -7277,7 +7277,7 @@
         </is>
       </c>
       <c r="C213" s="0">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="D213" s="0">
         <v>9</v>
@@ -7296,7 +7296,7 @@
         </is>
       </c>
       <c r="H213" s="0">
-        <v>3.94</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="214" spans="1:8">
@@ -7311,10 +7311,10 @@
         </is>
       </c>
       <c r="C214" s="0">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="D214" s="0">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E214" s="0">
         <v>2024</v>
@@ -7330,7 +7330,7 @@
         </is>
       </c>
       <c r="H214" s="0">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="215" spans="1:8">
@@ -7345,10 +7345,10 @@
         </is>
       </c>
       <c r="C215" s="0">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="D215" s="0">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E215" s="0">
         <v>2024</v>
@@ -7364,7 +7364,7 @@
         </is>
       </c>
       <c r="H215" s="0">
-        <v>4.29</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="216" spans="1:8">
@@ -7379,10 +7379,10 @@
         </is>
       </c>
       <c r="C216" s="0">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="D216" s="0">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E216" s="0">
         <v>2024</v>
@@ -7398,7 +7398,7 @@
         </is>
       </c>
       <c r="H216" s="0">
-        <v>2.7</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="217" spans="1:8">
@@ -7413,10 +7413,10 @@
         </is>
       </c>
       <c r="C217" s="0">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="D217" s="0">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E217" s="0">
         <v>2024</v>
@@ -7432,7 +7432,7 @@
         </is>
       </c>
       <c r="H217" s="0">
-        <v>4.44</v>
+        <v>3.94</v>
       </c>
     </row>
     <row r="218" spans="1:8">
@@ -7447,7 +7447,7 @@
         </is>
       </c>
       <c r="C218" s="0">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="D218" s="0">
         <v>8</v>
@@ -7462,11 +7462,11 @@
       </c>
       <c r="G218" s="0" t="inlineStr">
         <is>
-          <t>caixa de 22 Kg</t>
+          <t>quilograma</t>
         </is>
       </c>
       <c r="H218" s="0">
-        <v>2.82</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="219" spans="1:8">
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="C219" s="0">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="D219" s="0">
         <v>8</v>
@@ -7496,11 +7496,11 @@
       </c>
       <c r="G219" s="0" t="inlineStr">
         <is>
-          <t>Caixa 20 Kg</t>
+          <t>quilograma</t>
         </is>
       </c>
       <c r="H219" s="0">
-        <v>4.99</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="220" spans="1:8">
@@ -7515,7 +7515,7 @@
         </is>
       </c>
       <c r="C220" s="0">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="D220" s="0">
         <v>8</v>
@@ -7530,11 +7530,11 @@
       </c>
       <c r="G220" s="0" t="inlineStr">
         <is>
-          <t>caixa de 22 Kg</t>
+          <t>quilograma</t>
         </is>
       </c>
       <c r="H220" s="0">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="221" spans="1:8">
@@ -7549,7 +7549,7 @@
         </is>
       </c>
       <c r="C221" s="0">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="D221" s="0">
         <v>8</v>
@@ -7564,11 +7564,11 @@
       </c>
       <c r="G221" s="0" t="inlineStr">
         <is>
-          <t>Caixa 20 Kg</t>
+          <t>quilograma</t>
         </is>
       </c>
       <c r="H221" s="0">
-        <v>5.2</v>
+        <v>4.44</v>
       </c>
     </row>
     <row r="222" spans="1:8">
@@ -7583,7 +7583,7 @@
         </is>
       </c>
       <c r="C222" s="0">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="D222" s="0">
         <v>8</v>
@@ -7602,7 +7602,7 @@
         </is>
       </c>
       <c r="H222" s="0">
-        <v>2.49</v>
+        <v>2.82</v>
       </c>
     </row>
     <row r="223" spans="1:8">
@@ -7617,7 +7617,7 @@
         </is>
       </c>
       <c r="C223" s="0">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="D223" s="0">
         <v>8</v>
@@ -7636,7 +7636,7 @@
         </is>
       </c>
       <c r="H223" s="0">
-        <v>4.93</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="224" spans="1:8">
@@ -7651,10 +7651,10 @@
         </is>
       </c>
       <c r="C224" s="0">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="D224" s="0">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E224" s="0">
         <v>2024</v>
@@ -7670,7 +7670,7 @@
         </is>
       </c>
       <c r="H224" s="0">
-        <v>2.04</v>
+        <v>2.74</v>
       </c>
     </row>
     <row r="225" spans="1:8">
@@ -7685,10 +7685,10 @@
         </is>
       </c>
       <c r="C225" s="0">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="D225" s="0">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E225" s="0">
         <v>2024</v>
@@ -7704,7 +7704,7 @@
         </is>
       </c>
       <c r="H225" s="0">
-        <v>3.76</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="226" spans="1:8">
@@ -7719,10 +7719,10 @@
         </is>
       </c>
       <c r="C226" s="0">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="D226" s="0">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E226" s="0">
         <v>2024</v>
@@ -7738,7 +7738,7 @@
         </is>
       </c>
       <c r="H226" s="0">
-        <v>1.98</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="227" spans="1:8">
@@ -7753,10 +7753,10 @@
         </is>
       </c>
       <c r="C227" s="0">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="D227" s="0">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E227" s="0">
         <v>2024</v>
@@ -7772,7 +7772,7 @@
         </is>
       </c>
       <c r="H227" s="0">
-        <v>3.16</v>
+        <v>4.93</v>
       </c>
     </row>
     <row r="228" spans="1:8">
@@ -7787,7 +7787,7 @@
         </is>
       </c>
       <c r="C228" s="0">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="D228" s="0">
         <v>7</v>
@@ -7806,7 +7806,7 @@
         </is>
       </c>
       <c r="H228" s="0">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="229" spans="1:8">
@@ -7821,7 +7821,7 @@
         </is>
       </c>
       <c r="C229" s="0">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="D229" s="0">
         <v>7</v>
@@ -7840,7 +7840,7 @@
         </is>
       </c>
       <c r="H229" s="0">
-        <v>2.85</v>
+        <v>3.76</v>
       </c>
     </row>
     <row r="230" spans="1:8">
@@ -7855,7 +7855,7 @@
         </is>
       </c>
       <c r="C230" s="0">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="D230" s="0">
         <v>7</v>
@@ -7874,7 +7874,7 @@
         </is>
       </c>
       <c r="H230" s="0">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
     </row>
     <row r="231" spans="1:8">
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="C231" s="0">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="D231" s="0">
         <v>7</v>
@@ -7908,7 +7908,7 @@
         </is>
       </c>
       <c r="H231" s="0">
-        <v>2.66</v>
+        <v>3.16</v>
       </c>
     </row>
     <row r="232" spans="1:8">
@@ -7923,10 +7923,10 @@
         </is>
       </c>
       <c r="C232" s="0">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="D232" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E232" s="0">
         <v>2024</v>
@@ -7938,11 +7938,11 @@
       </c>
       <c r="G232" s="0" t="inlineStr">
         <is>
-          <t>quilograma</t>
+          <t>caixa de 22 Kg</t>
         </is>
       </c>
       <c r="H232" s="0">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="233" spans="1:8">
@@ -7957,10 +7957,10 @@
         </is>
       </c>
       <c r="C233" s="0">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="D233" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E233" s="0">
         <v>2024</v>
@@ -7972,11 +7972,11 @@
       </c>
       <c r="G233" s="0" t="inlineStr">
         <is>
-          <t>quilograma</t>
+          <t>Caixa 20 Kg</t>
         </is>
       </c>
       <c r="H233" s="0">
-        <v>2.32</v>
+        <v>2.85</v>
       </c>
     </row>
     <row r="234" spans="1:8">
@@ -7991,10 +7991,10 @@
         </is>
       </c>
       <c r="C234" s="0">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="D234" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E234" s="0">
         <v>2024</v>
@@ -8006,11 +8006,11 @@
       </c>
       <c r="G234" s="0" t="inlineStr">
         <is>
-          <t>quilograma</t>
+          <t>caixa de 22 Kg</t>
         </is>
       </c>
       <c r="H234" s="0">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="235" spans="1:8">
@@ -8025,10 +8025,10 @@
         </is>
       </c>
       <c r="C235" s="0">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="D235" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E235" s="0">
         <v>2024</v>
@@ -8040,11 +8040,11 @@
       </c>
       <c r="G235" s="0" t="inlineStr">
         <is>
-          <t>quilograma</t>
+          <t>Caixa 20 Kg</t>
         </is>
       </c>
       <c r="H235" s="0">
-        <v>2.2</v>
+        <v>2.66</v>
       </c>
     </row>
     <row r="236" spans="1:8">
@@ -8059,7 +8059,7 @@
         </is>
       </c>
       <c r="C236" s="0">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="D236" s="0">
         <v>6</v>
@@ -8078,7 +8078,7 @@
         </is>
       </c>
       <c r="H236" s="0">
-        <v>1.65</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="237" spans="1:8">
@@ -8093,7 +8093,7 @@
         </is>
       </c>
       <c r="C237" s="0">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="D237" s="0">
         <v>6</v>
@@ -8112,7 +8112,7 @@
         </is>
       </c>
       <c r="H237" s="0">
-        <v>2.49</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="238" spans="1:8">
@@ -8127,7 +8127,7 @@
         </is>
       </c>
       <c r="C238" s="0">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="D238" s="0">
         <v>6</v>
@@ -8146,7 +8146,7 @@
         </is>
       </c>
       <c r="H238" s="0">
-        <v>1.5</v>
+        <v>1.97</v>
       </c>
     </row>
     <row r="239" spans="1:8">
@@ -8161,7 +8161,7 @@
         </is>
       </c>
       <c r="C239" s="0">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="D239" s="0">
         <v>6</v>
@@ -8180,7 +8180,7 @@
         </is>
       </c>
       <c r="H239" s="0">
-        <v>2.73</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="240" spans="1:8">
@@ -8195,10 +8195,10 @@
         </is>
       </c>
       <c r="C240" s="0">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="D240" s="0">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E240" s="0">
         <v>2024</v>
@@ -8214,7 +8214,7 @@
         </is>
       </c>
       <c r="H240" s="0">
-        <v>1.17</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="241" spans="1:8">
@@ -8229,10 +8229,10 @@
         </is>
       </c>
       <c r="C241" s="0">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="D241" s="0">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E241" s="0">
         <v>2024</v>
@@ -8248,7 +8248,7 @@
         </is>
       </c>
       <c r="H241" s="0">
-        <v>3.05</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="242" spans="1:8">
@@ -8263,10 +8263,10 @@
         </is>
       </c>
       <c r="C242" s="0">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="D242" s="0">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E242" s="0">
         <v>2024</v>
@@ -8282,7 +8282,7 @@
         </is>
       </c>
       <c r="H242" s="0">
-        <v>1.22</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="243" spans="1:8">
@@ -8297,10 +8297,10 @@
         </is>
       </c>
       <c r="C243" s="0">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="D243" s="0">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E243" s="0">
         <v>2024</v>
@@ -8331,7 +8331,7 @@
         </is>
       </c>
       <c r="C244" s="0">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D244" s="0">
         <v>5</v>
@@ -8350,7 +8350,7 @@
         </is>
       </c>
       <c r="H244" s="0">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="245" spans="1:8">
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="C245" s="0">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D245" s="0">
         <v>5</v>
@@ -8384,7 +8384,7 @@
         </is>
       </c>
       <c r="H245" s="0">
-        <v>2.85</v>
+        <v>3.05</v>
       </c>
     </row>
     <row r="246" spans="1:8">
@@ -8399,7 +8399,7 @@
         </is>
       </c>
       <c r="C246" s="0">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="D246" s="0">
         <v>5</v>
@@ -8418,7 +8418,7 @@
         </is>
       </c>
       <c r="H246" s="0">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="247" spans="1:8">
@@ -8433,7 +8433,7 @@
         </is>
       </c>
       <c r="C247" s="0">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="D247" s="0">
         <v>5</v>
@@ -8452,7 +8452,7 @@
         </is>
       </c>
       <c r="H247" s="0">
-        <v>2.69</v>
+        <v>2.73</v>
       </c>
     </row>
     <row r="248" spans="1:8">
@@ -8467,7 +8467,7 @@
         </is>
       </c>
       <c r="C248" s="0">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="D248" s="0">
         <v>5</v>
@@ -8486,7 +8486,7 @@
         </is>
       </c>
       <c r="H248" s="0">
-        <v>1.03</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="249" spans="1:8">
@@ -8501,7 +8501,7 @@
         </is>
       </c>
       <c r="C249" s="0">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="D249" s="0">
         <v>5</v>
@@ -8520,7 +8520,7 @@
         </is>
       </c>
       <c r="H249" s="0">
-        <v>2.65</v>
+        <v>2.85</v>
       </c>
     </row>
     <row r="250" spans="1:8">
@@ -8535,10 +8535,10 @@
         </is>
       </c>
       <c r="C250" s="0">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="D250" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E250" s="0">
         <v>2024</v>
@@ -8554,7 +8554,7 @@
         </is>
       </c>
       <c r="H250" s="0">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="251" spans="1:8">
@@ -8569,10 +8569,10 @@
         </is>
       </c>
       <c r="C251" s="0">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="D251" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E251" s="0">
         <v>2024</v>
@@ -8588,7 +8588,7 @@
         </is>
       </c>
       <c r="H251" s="0">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="252" spans="1:8">
@@ -8603,10 +8603,10 @@
         </is>
       </c>
       <c r="C252" s="0">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="D252" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E252" s="0">
         <v>2024</v>
@@ -8622,7 +8622,7 @@
         </is>
       </c>
       <c r="H252" s="0">
-        <v>1.17</v>
+        <v>1.03</v>
       </c>
     </row>
     <row r="253" spans="1:8">
@@ -8637,10 +8637,10 @@
         </is>
       </c>
       <c r="C253" s="0">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="D253" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E253" s="0">
         <v>2024</v>
@@ -8656,7 +8656,7 @@
         </is>
       </c>
       <c r="H253" s="0">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
     </row>
     <row r="254" spans="1:8">
@@ -8671,7 +8671,7 @@
         </is>
       </c>
       <c r="C254" s="0">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="D254" s="0">
         <v>4</v>
@@ -8690,7 +8690,7 @@
         </is>
       </c>
       <c r="H254" s="0">
-        <v>1.24</v>
+        <v>1.09</v>
       </c>
     </row>
     <row r="255" spans="1:8">
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="C255" s="0">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="D255" s="0">
         <v>4</v>
@@ -8724,7 +8724,7 @@
         </is>
       </c>
       <c r="H255" s="0">
-        <v>4.86</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="256" spans="1:8">
@@ -8739,7 +8739,7 @@
         </is>
       </c>
       <c r="C256" s="0">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="D256" s="0">
         <v>4</v>
@@ -8758,7 +8758,7 @@
         </is>
       </c>
       <c r="H256" s="0">
-        <v>1.54</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="257" spans="1:8">
@@ -8773,7 +8773,7 @@
         </is>
       </c>
       <c r="C257" s="0">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="D257" s="0">
         <v>4</v>
@@ -8792,7 +8792,7 @@
         </is>
       </c>
       <c r="H257" s="0">
-        <v>6.23</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="258" spans="1:8">
@@ -8807,10 +8807,10 @@
         </is>
       </c>
       <c r="C258" s="0">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="D258" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E258" s="0">
         <v>2024</v>
@@ -8826,7 +8826,7 @@
         </is>
       </c>
       <c r="H258" s="0">
-        <v>2.13</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="259" spans="1:8">
@@ -8841,10 +8841,10 @@
         </is>
       </c>
       <c r="C259" s="0">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="D259" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E259" s="0">
         <v>2024</v>
@@ -8860,7 +8860,7 @@
         </is>
       </c>
       <c r="H259" s="0">
-        <v>6.4</v>
+        <v>4.86</v>
       </c>
     </row>
     <row r="260" spans="1:8">
@@ -8875,10 +8875,10 @@
         </is>
       </c>
       <c r="C260" s="0">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="D260" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E260" s="0">
         <v>2024</v>
@@ -8894,7 +8894,7 @@
         </is>
       </c>
       <c r="H260" s="0">
-        <v>2.49</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="261" spans="1:8">
@@ -8909,10 +8909,10 @@
         </is>
       </c>
       <c r="C261" s="0">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="D261" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E261" s="0">
         <v>2024</v>
@@ -8928,7 +8928,7 @@
         </is>
       </c>
       <c r="H261" s="0">
-        <v>6.3</v>
+        <v>6.23</v>
       </c>
     </row>
     <row r="262" spans="1:8">
@@ -8943,7 +8943,7 @@
         </is>
       </c>
       <c r="C262" s="0">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="D262" s="0">
         <v>3</v>
@@ -8962,7 +8962,7 @@
         </is>
       </c>
       <c r="H262" s="0">
-        <v>2.64</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="263" spans="1:8">
@@ -8977,7 +8977,7 @@
         </is>
       </c>
       <c r="C263" s="0">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="D263" s="0">
         <v>3</v>
@@ -8996,13 +8996,13 @@
         </is>
       </c>
       <c r="H263" s="0">
-        <v>6.46</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="264" spans="1:8">
       <c r="A264" s="0" t="inlineStr">
         <is>
-          <t>Prata anã primeira - produtor</t>
+          <t>Nanica primeira - produtor</t>
         </is>
       </c>
       <c r="B264" s="0" t="inlineStr">
@@ -9011,7 +9011,7 @@
         </is>
       </c>
       <c r="C264" s="0">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="D264" s="0">
         <v>3</v>
@@ -9030,13 +9030,13 @@
         </is>
       </c>
       <c r="H264" s="0">
-        <v>6.39</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="265" spans="1:8">
       <c r="A265" s="0" t="inlineStr">
         <is>
-          <t>Nanica primeira - produtor</t>
+          <t>Prata anã primeira - produtor</t>
         </is>
       </c>
       <c r="B265" s="0" t="inlineStr">
@@ -9045,10 +9045,10 @@
         </is>
       </c>
       <c r="C265" s="0">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="D265" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E265" s="0">
         <v>2024</v>
@@ -9064,13 +9064,13 @@
         </is>
       </c>
       <c r="H265" s="0">
-        <v>2.91</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="266" spans="1:8">
       <c r="A266" s="0" t="inlineStr">
         <is>
-          <t>Prata anã primeira - produtor</t>
+          <t>Nanica primeira - produtor</t>
         </is>
       </c>
       <c r="B266" s="0" t="inlineStr">
@@ -9079,10 +9079,10 @@
         </is>
       </c>
       <c r="C266" s="0">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="D266" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E266" s="0">
         <v>2024</v>
@@ -9098,13 +9098,13 @@
         </is>
       </c>
       <c r="H266" s="0">
-        <v>6.31</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="267" spans="1:8">
       <c r="A267" s="0" t="inlineStr">
         <is>
-          <t>Nanica primeira - produtor</t>
+          <t>Prata anã primeira - produtor</t>
         </is>
       </c>
       <c r="B267" s="0" t="inlineStr">
@@ -9113,10 +9113,10 @@
         </is>
       </c>
       <c r="C267" s="0">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="D267" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E267" s="0">
         <v>2024</v>
@@ -9132,7 +9132,7 @@
         </is>
       </c>
       <c r="H267" s="0">
-        <v>3.79</v>
+        <v>6.46</v>
       </c>
     </row>
     <row r="268" spans="1:8">
@@ -9147,10 +9147,10 @@
         </is>
       </c>
       <c r="C268" s="0">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="D268" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E268" s="0">
         <v>2024</v>
@@ -9166,7 +9166,7 @@
         </is>
       </c>
       <c r="H268" s="0">
-        <v>6.26</v>
+        <v>6.39</v>
       </c>
     </row>
     <row r="269" spans="1:8">
@@ -9181,7 +9181,7 @@
         </is>
       </c>
       <c r="C269" s="0">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="D269" s="0">
         <v>2</v>
@@ -9200,7 +9200,7 @@
         </is>
       </c>
       <c r="H269" s="0">
-        <v>4.11</v>
+        <v>2.91</v>
       </c>
     </row>
     <row r="270" spans="1:8">
@@ -9215,7 +9215,7 @@
         </is>
       </c>
       <c r="C270" s="0">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="D270" s="0">
         <v>2</v>
@@ -9234,7 +9234,7 @@
         </is>
       </c>
       <c r="H270" s="0">
-        <v>6.16</v>
+        <v>6.31</v>
       </c>
     </row>
     <row r="271" spans="1:8">
@@ -9249,7 +9249,7 @@
         </is>
       </c>
       <c r="C271" s="0">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="D271" s="0">
         <v>2</v>
@@ -9268,7 +9268,7 @@
         </is>
       </c>
       <c r="H271" s="0">
-        <v>4.05</v>
+        <v>3.79</v>
       </c>
     </row>
     <row r="272" spans="1:8">
@@ -9283,7 +9283,7 @@
         </is>
       </c>
       <c r="C272" s="0">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="D272" s="0">
         <v>2</v>
@@ -9302,7 +9302,7 @@
         </is>
       </c>
       <c r="H272" s="0">
-        <v>5.88</v>
+        <v>6.26</v>
       </c>
     </row>
     <row r="273" spans="1:8">
@@ -9317,7 +9317,7 @@
         </is>
       </c>
       <c r="C273" s="0">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="D273" s="0">
         <v>2</v>
@@ -9336,7 +9336,7 @@
         </is>
       </c>
       <c r="H273" s="0">
-        <v>2.42</v>
+        <v>4.11</v>
       </c>
     </row>
     <row r="274" spans="1:8">
@@ -9351,7 +9351,7 @@
         </is>
       </c>
       <c r="C274" s="0">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="D274" s="0">
         <v>2</v>
@@ -9370,7 +9370,7 @@
         </is>
       </c>
       <c r="H274" s="0">
-        <v>5.61</v>
+        <v>6.16</v>
       </c>
     </row>
     <row r="275" spans="1:8">
@@ -9385,10 +9385,10 @@
         </is>
       </c>
       <c r="C275" s="0">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="D275" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E275" s="0">
         <v>2024</v>
@@ -9404,7 +9404,7 @@
         </is>
       </c>
       <c r="H275" s="0">
-        <v>2.21</v>
+        <v>4.05</v>
       </c>
     </row>
     <row r="276" spans="1:8">
@@ -9419,10 +9419,10 @@
         </is>
       </c>
       <c r="C276" s="0">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="D276" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E276" s="0">
         <v>2024</v>
@@ -9438,7 +9438,7 @@
         </is>
       </c>
       <c r="H276" s="0">
-        <v>5.47</v>
+        <v>5.88</v>
       </c>
     </row>
     <row r="277" spans="1:8">
@@ -9453,10 +9453,10 @@
         </is>
       </c>
       <c r="C277" s="0">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="D277" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E277" s="0">
         <v>2024</v>
@@ -9472,7 +9472,7 @@
         </is>
       </c>
       <c r="H277" s="0">
-        <v>2.12</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="278" spans="1:8">
@@ -9487,10 +9487,10 @@
         </is>
       </c>
       <c r="C278" s="0">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="D278" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E278" s="0">
         <v>2024</v>
@@ -9506,7 +9506,7 @@
         </is>
       </c>
       <c r="H278" s="0">
-        <v>5.5</v>
+        <v>5.61</v>
       </c>
     </row>
     <row r="279" spans="1:8">
@@ -9521,7 +9521,7 @@
         </is>
       </c>
       <c r="C279" s="0">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="D279" s="0">
         <v>1</v>
@@ -9540,7 +9540,7 @@
         </is>
       </c>
       <c r="H279" s="0">
-        <v>2.4</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="280" spans="1:8">
@@ -9555,7 +9555,7 @@
         </is>
       </c>
       <c r="C280" s="0">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="D280" s="0">
         <v>1</v>
@@ -9574,7 +9574,7 @@
         </is>
       </c>
       <c r="H280" s="0">
-        <v>5.46</v>
+        <v>5.47</v>
       </c>
     </row>
     <row r="281" spans="1:8">
@@ -9589,7 +9589,7 @@
         </is>
       </c>
       <c r="C281" s="0">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="D281" s="0">
         <v>1</v>
@@ -9608,13 +9608,13 @@
         </is>
       </c>
       <c r="H281" s="0">
-        <v>2.42</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="282" spans="1:8">
       <c r="A282" s="0" t="inlineStr">
         <is>
-          <t>Nanica primeira - produtor</t>
+          <t>Prata anã primeira - produtor</t>
         </is>
       </c>
       <c r="B282" s="0" t="inlineStr">
@@ -9623,7 +9623,7 @@
         </is>
       </c>
       <c r="C282" s="0">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="D282" s="0">
         <v>1</v>
@@ -9642,13 +9642,13 @@
         </is>
       </c>
       <c r="H282" s="0">
-        <v>2.42</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="283" spans="1:8">
       <c r="A283" s="0" t="inlineStr">
         <is>
-          <t>Prata anã primeira - produtor</t>
+          <t>Nanica primeira - produtor</t>
         </is>
       </c>
       <c r="B283" s="0" t="inlineStr">
@@ -9657,7 +9657,7 @@
         </is>
       </c>
       <c r="C283" s="0">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D283" s="0">
         <v>1</v>
@@ -9676,7 +9676,7 @@
         </is>
       </c>
       <c r="H283" s="0">
-        <v>5.47</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="284" spans="1:8">
@@ -9691,7 +9691,7 @@
         </is>
       </c>
       <c r="C284" s="0">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D284" s="0">
         <v>1</v>
@@ -9710,7 +9710,7 @@
         </is>
       </c>
       <c r="H284" s="0">
-        <v>5.47</v>
+        <v>5.46</v>
       </c>
     </row>
     <row r="285" spans="1:8">
@@ -9725,13 +9725,13 @@
         </is>
       </c>
       <c r="C285" s="0">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="D285" s="0">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E285" s="0">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F285" s="0" t="inlineStr">
         <is>
@@ -9744,13 +9744,13 @@
         </is>
       </c>
       <c r="H285" s="0">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="286" spans="1:8">
       <c r="A286" s="0" t="inlineStr">
         <is>
-          <t>Prata anã primeira - produtor</t>
+          <t>Nanica primeira - produtor</t>
         </is>
       </c>
       <c r="B286" s="0" t="inlineStr">
@@ -9759,13 +9759,13 @@
         </is>
       </c>
       <c r="C286" s="0">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="D286" s="0">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E286" s="0">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F286" s="0" t="inlineStr">
         <is>
@@ -9778,13 +9778,13 @@
         </is>
       </c>
       <c r="H286" s="0">
-        <v>5.5</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="287" spans="1:8">
       <c r="A287" s="0" t="inlineStr">
         <is>
-          <t>Nanica primeira - produtor</t>
+          <t>Prata anã primeira - produtor</t>
         </is>
       </c>
       <c r="B287" s="0" t="inlineStr">
@@ -9793,13 +9793,13 @@
         </is>
       </c>
       <c r="C287" s="0">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="D287" s="0">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E287" s="0">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F287" s="0" t="inlineStr">
         <is>
@@ -9812,7 +9812,7 @@
         </is>
       </c>
       <c r="H287" s="0">
-        <v>2.36</v>
+        <v>5.47</v>
       </c>
     </row>
     <row r="288" spans="1:8">
@@ -9827,13 +9827,13 @@
         </is>
       </c>
       <c r="C288" s="0">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="D288" s="0">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E288" s="0">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F288" s="0" t="inlineStr">
         <is>
@@ -9846,7 +9846,7 @@
         </is>
       </c>
       <c r="H288" s="0">
-        <v>5.44</v>
+        <v>5.47</v>
       </c>
     </row>
     <row r="289" spans="1:8">
@@ -9861,7 +9861,7 @@
         </is>
       </c>
       <c r="C289" s="0">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="D289" s="0">
         <v>12</v>
@@ -9880,7 +9880,7 @@
         </is>
       </c>
       <c r="H289" s="0">
-        <v>2.21</v>
+        <v>2.43</v>
       </c>
     </row>
     <row r="290" spans="1:8">
@@ -9895,7 +9895,7 @@
         </is>
       </c>
       <c r="C290" s="0">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="D290" s="0">
         <v>12</v>
@@ -9914,7 +9914,7 @@
         </is>
       </c>
       <c r="H290" s="0">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="291" spans="1:8">
@@ -9929,7 +9929,7 @@
         </is>
       </c>
       <c r="C291" s="0">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="D291" s="0">
         <v>12</v>
@@ -9948,7 +9948,7 @@
         </is>
       </c>
       <c r="H291" s="0">
-        <v>2.04</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="292" spans="1:8">
@@ -9963,7 +9963,7 @@
         </is>
       </c>
       <c r="C292" s="0">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="D292" s="0">
         <v>12</v>
@@ -9982,7 +9982,7 @@
         </is>
       </c>
       <c r="H292" s="0">
-        <v>4.73</v>
+        <v>5.44</v>
       </c>
     </row>
     <row r="293" spans="1:8">
@@ -9997,10 +9997,10 @@
         </is>
       </c>
       <c r="C293" s="0">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="D293" s="0">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E293" s="0">
         <v>2023</v>
@@ -10016,7 +10016,7 @@
         </is>
       </c>
       <c r="H293" s="0">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="294" spans="1:8">
@@ -10031,10 +10031,10 @@
         </is>
       </c>
       <c r="C294" s="0">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="D294" s="0">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E294" s="0">
         <v>2023</v>
@@ -10050,7 +10050,7 @@
         </is>
       </c>
       <c r="H294" s="0">
-        <v>3.88</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="295" spans="1:8">
@@ -10065,10 +10065,10 @@
         </is>
       </c>
       <c r="C295" s="0">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="D295" s="0">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E295" s="0">
         <v>2023</v>
@@ -10084,7 +10084,7 @@
         </is>
       </c>
       <c r="H295" s="0">
-        <v>2.58</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="296" spans="1:8">
@@ -10099,10 +10099,10 @@
         </is>
       </c>
       <c r="C296" s="0">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="D296" s="0">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E296" s="0">
         <v>2023</v>
@@ -10118,7 +10118,7 @@
         </is>
       </c>
       <c r="H296" s="0">
-        <v>3.8</v>
+        <v>4.73</v>
       </c>
     </row>
     <row r="297" spans="1:8">
@@ -10133,7 +10133,7 @@
         </is>
       </c>
       <c r="C297" s="0">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="D297" s="0">
         <v>11</v>
@@ -10152,7 +10152,7 @@
         </is>
       </c>
       <c r="H297" s="0">
-        <v>2.64</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="298" spans="1:8">
@@ -10167,7 +10167,7 @@
         </is>
       </c>
       <c r="C298" s="0">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="D298" s="0">
         <v>11</v>
@@ -10186,7 +10186,7 @@
         </is>
       </c>
       <c r="H298" s="0">
-        <v>3.83</v>
+        <v>3.88</v>
       </c>
     </row>
     <row r="299" spans="1:8">
@@ -10201,7 +10201,7 @@
         </is>
       </c>
       <c r="C299" s="0">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="D299" s="0">
         <v>11</v>
@@ -10220,7 +10220,7 @@
         </is>
       </c>
       <c r="H299" s="0">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="300" spans="1:8">
@@ -10235,7 +10235,7 @@
         </is>
       </c>
       <c r="C300" s="0">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="D300" s="0">
         <v>11</v>
@@ -10254,7 +10254,7 @@
         </is>
       </c>
       <c r="H300" s="0">
-        <v>3.54</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="301" spans="1:8">
@@ -10269,7 +10269,7 @@
         </is>
       </c>
       <c r="C301" s="0">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="D301" s="0">
         <v>11</v>
@@ -10288,7 +10288,7 @@
         </is>
       </c>
       <c r="H301" s="0">
-        <v>2.19</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="302" spans="1:8">
@@ -10303,7 +10303,7 @@
         </is>
       </c>
       <c r="C302" s="0">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="D302" s="0">
         <v>11</v>
@@ -10322,7 +10322,7 @@
         </is>
       </c>
       <c r="H302" s="0">
-        <v>2.81</v>
+        <v>3.83</v>
       </c>
     </row>
     <row r="303" spans="1:8">
@@ -10337,10 +10337,10 @@
         </is>
       </c>
       <c r="C303" s="0">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="D303" s="0">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E303" s="0">
         <v>2023</v>
@@ -10356,7 +10356,7 @@
         </is>
       </c>
       <c r="H303" s="0">
-        <v>1.98</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="304" spans="1:8">
@@ -10371,10 +10371,10 @@
         </is>
       </c>
       <c r="C304" s="0">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="D304" s="0">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E304" s="0">
         <v>2023</v>
@@ -10390,7 +10390,7 @@
         </is>
       </c>
       <c r="H304" s="0">
-        <v>2.67</v>
+        <v>3.54</v>
       </c>
     </row>
     <row r="305" spans="1:8">
@@ -10405,10 +10405,10 @@
         </is>
       </c>
       <c r="C305" s="0">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="D305" s="0">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E305" s="0">
         <v>2023</v>
@@ -10424,7 +10424,7 @@
         </is>
       </c>
       <c r="H305" s="0">
-        <v>2.06</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="306" spans="1:8">
@@ -10439,10 +10439,10 @@
         </is>
       </c>
       <c r="C306" s="0">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="D306" s="0">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E306" s="0">
         <v>2023</v>
@@ -10458,7 +10458,7 @@
         </is>
       </c>
       <c r="H306" s="0">
-        <v>2.74</v>
+        <v>2.81</v>
       </c>
     </row>
     <row r="307" spans="1:8">
@@ -10473,7 +10473,7 @@
         </is>
       </c>
       <c r="C307" s="0">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="D307" s="0">
         <v>10</v>
@@ -10492,7 +10492,7 @@
         </is>
       </c>
       <c r="H307" s="0">
-        <v>1.89</v>
+        <v>1.98</v>
       </c>
     </row>
     <row r="308" spans="1:8">
@@ -10507,7 +10507,7 @@
         </is>
       </c>
       <c r="C308" s="0">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="D308" s="0">
         <v>10</v>
@@ -10526,7 +10526,7 @@
         </is>
       </c>
       <c r="H308" s="0">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="309" spans="1:8">
@@ -10541,7 +10541,7 @@
         </is>
       </c>
       <c r="C309" s="0">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="D309" s="0">
         <v>10</v>
@@ -10560,7 +10560,7 @@
         </is>
       </c>
       <c r="H309" s="0">
-        <v>1.7</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="310" spans="1:8">
@@ -10575,7 +10575,7 @@
         </is>
       </c>
       <c r="C310" s="0">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="D310" s="0">
         <v>10</v>
@@ -10594,7 +10594,7 @@
         </is>
       </c>
       <c r="H310" s="0">
-        <v>2.66</v>
+        <v>2.74</v>
       </c>
     </row>
     <row r="311" spans="1:8">
@@ -10609,10 +10609,10 @@
         </is>
       </c>
       <c r="C311" s="0">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="D311" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E311" s="0">
         <v>2023</v>
@@ -10628,7 +10628,7 @@
         </is>
       </c>
       <c r="H311" s="0">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="312" spans="1:8">
@@ -10643,10 +10643,10 @@
         </is>
       </c>
       <c r="C312" s="0">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="D312" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E312" s="0">
         <v>2023</v>
@@ -10662,7 +10662,7 @@
         </is>
       </c>
       <c r="H312" s="0">
-        <v>2.59</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="313" spans="1:8">
@@ -10677,10 +10677,10 @@
         </is>
       </c>
       <c r="C313" s="0">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="D313" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E313" s="0">
         <v>2023</v>
@@ -10696,7 +10696,7 @@
         </is>
       </c>
       <c r="H313" s="0">
-        <v>2.34</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="314" spans="1:8">
@@ -10711,10 +10711,10 @@
         </is>
       </c>
       <c r="C314" s="0">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="D314" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E314" s="0">
         <v>2023</v>
@@ -10730,7 +10730,7 @@
         </is>
       </c>
       <c r="H314" s="0">
-        <v>2.56</v>
+        <v>2.66</v>
       </c>
     </row>
     <row r="315" spans="1:8">
@@ -10745,7 +10745,7 @@
         </is>
       </c>
       <c r="C315" s="0">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="D315" s="0">
         <v>9</v>
@@ -10764,7 +10764,7 @@
         </is>
       </c>
       <c r="H315" s="0">
-        <v>2.45</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="316" spans="1:8">
@@ -10779,7 +10779,7 @@
         </is>
       </c>
       <c r="C316" s="0">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="D316" s="0">
         <v>9</v>
@@ -10798,7 +10798,7 @@
         </is>
       </c>
       <c r="H316" s="0">
-        <v>2.54</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="317" spans="1:8">
@@ -10813,7 +10813,7 @@
         </is>
       </c>
       <c r="C317" s="0">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="D317" s="0">
         <v>9</v>
@@ -10832,7 +10832,7 @@
         </is>
       </c>
       <c r="H317" s="0">
-        <v>2.86</v>
+        <v>2.34</v>
       </c>
     </row>
     <row r="318" spans="1:8">
@@ -10847,7 +10847,7 @@
         </is>
       </c>
       <c r="C318" s="0">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="D318" s="0">
         <v>9</v>
@@ -10866,7 +10866,7 @@
         </is>
       </c>
       <c r="H318" s="0">
-        <v>2.69</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="319" spans="1:8">
@@ -10881,10 +10881,10 @@
         </is>
       </c>
       <c r="C319" s="0">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="D319" s="0">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E319" s="0">
         <v>2023</v>
@@ -10900,7 +10900,7 @@
         </is>
       </c>
       <c r="H319" s="0">
-        <v>3.05</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="320" spans="1:8">
@@ -10915,10 +10915,10 @@
         </is>
       </c>
       <c r="C320" s="0">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="D320" s="0">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E320" s="0">
         <v>2023</v>
@@ -10934,7 +10934,7 @@
         </is>
       </c>
       <c r="H320" s="0">
-        <v>2.86</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="321" spans="1:8">
@@ -10949,10 +10949,10 @@
         </is>
       </c>
       <c r="C321" s="0">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="D321" s="0">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E321" s="0">
         <v>2023</v>
@@ -10968,7 +10968,7 @@
         </is>
       </c>
       <c r="H321" s="0">
-        <v>3.26</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="322" spans="1:8">
@@ -10983,10 +10983,10 @@
         </is>
       </c>
       <c r="C322" s="0">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="D322" s="0">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E322" s="0">
         <v>2023</v>
@@ -11002,7 +11002,7 @@
         </is>
       </c>
       <c r="H322" s="0">
-        <v>3.06</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="323" spans="1:8">
@@ -11017,7 +11017,7 @@
         </is>
       </c>
       <c r="C323" s="0">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="D323" s="0">
         <v>8</v>
@@ -11036,7 +11036,7 @@
         </is>
       </c>
       <c r="H323" s="0">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
     </row>
     <row r="324" spans="1:8">
@@ -11051,7 +11051,7 @@
         </is>
       </c>
       <c r="C324" s="0">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="D324" s="0">
         <v>8</v>
@@ -11070,7 +11070,7 @@
         </is>
       </c>
       <c r="H324" s="0">
-        <v>3.06</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="325" spans="1:8">
@@ -11085,7 +11085,7 @@
         </is>
       </c>
       <c r="C325" s="0">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D325" s="0">
         <v>8</v>
@@ -11104,7 +11104,7 @@
         </is>
       </c>
       <c r="H325" s="0">
-        <v>3.21</v>
+        <v>3.26</v>
       </c>
     </row>
     <row r="326" spans="1:8">
@@ -11119,7 +11119,7 @@
         </is>
       </c>
       <c r="C326" s="0">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D326" s="0">
         <v>8</v>
@@ -11138,7 +11138,7 @@
         </is>
       </c>
       <c r="H326" s="0">
-        <v>3.2</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="327" spans="1:8">
@@ -11153,7 +11153,7 @@
         </is>
       </c>
       <c r="C327" s="0">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="D327" s="0">
         <v>8</v>
@@ -11172,7 +11172,7 @@
         </is>
       </c>
       <c r="H327" s="0">
-        <v>2.85</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="328" spans="1:8">
@@ -11187,7 +11187,7 @@
         </is>
       </c>
       <c r="C328" s="0">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="D328" s="0">
         <v>8</v>
@@ -11206,7 +11206,7 @@
         </is>
       </c>
       <c r="H328" s="0">
-        <v>2.75</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="329" spans="1:8">
@@ -11221,10 +11221,10 @@
         </is>
       </c>
       <c r="C329" s="0">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="D329" s="0">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E329" s="0">
         <v>2023</v>
@@ -11240,7 +11240,7 @@
         </is>
       </c>
       <c r="H329" s="0">
-        <v>2.66</v>
+        <v>3.21</v>
       </c>
     </row>
     <row r="330" spans="1:8">
@@ -11255,10 +11255,10 @@
         </is>
       </c>
       <c r="C330" s="0">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="D330" s="0">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E330" s="0">
         <v>2023</v>
@@ -11274,7 +11274,7 @@
         </is>
       </c>
       <c r="H330" s="0">
-        <v>2.78</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="331" spans="1:8">
@@ -11289,10 +11289,10 @@
         </is>
       </c>
       <c r="C331" s="0">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="D331" s="0">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E331" s="0">
         <v>2023</v>
@@ -11308,7 +11308,7 @@
         </is>
       </c>
       <c r="H331" s="0">
-        <v>2.45</v>
+        <v>2.85</v>
       </c>
     </row>
     <row r="332" spans="1:8">
@@ -11323,10 +11323,10 @@
         </is>
       </c>
       <c r="C332" s="0">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="D332" s="0">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E332" s="0">
         <v>2023</v>
@@ -11342,7 +11342,7 @@
         </is>
       </c>
       <c r="H332" s="0">
-        <v>2.89</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="333" spans="1:8">
@@ -11357,7 +11357,7 @@
         </is>
       </c>
       <c r="C333" s="0">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="D333" s="0">
         <v>7</v>
@@ -11376,7 +11376,7 @@
         </is>
       </c>
       <c r="H333" s="0">
-        <v>2.28</v>
+        <v>2.66</v>
       </c>
     </row>
     <row r="334" spans="1:8">
@@ -11391,7 +11391,7 @@
         </is>
       </c>
       <c r="C334" s="0">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="D334" s="0">
         <v>7</v>
@@ -11410,7 +11410,7 @@
         </is>
       </c>
       <c r="H334" s="0">
-        <v>3.04</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="335" spans="1:8">
@@ -11425,7 +11425,7 @@
         </is>
       </c>
       <c r="C335" s="0">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="D335" s="0">
         <v>7</v>
@@ -11444,7 +11444,7 @@
         </is>
       </c>
       <c r="H335" s="0">
-        <v>1.96</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="336" spans="1:8">
@@ -11459,7 +11459,7 @@
         </is>
       </c>
       <c r="C336" s="0">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="D336" s="0">
         <v>7</v>
@@ -11478,7 +11478,7 @@
         </is>
       </c>
       <c r="H336" s="0">
-        <v>3.01</v>
+        <v>2.89</v>
       </c>
     </row>
     <row r="337" spans="1:8">
@@ -11493,10 +11493,10 @@
         </is>
       </c>
       <c r="C337" s="0">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="D337" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E337" s="0">
         <v>2023</v>
@@ -11512,7 +11512,7 @@
         </is>
       </c>
       <c r="H337" s="0">
-        <v>1.57</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="338" spans="1:8">
@@ -11527,10 +11527,10 @@
         </is>
       </c>
       <c r="C338" s="0">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="D338" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E338" s="0">
         <v>2023</v>
@@ -11546,7 +11546,7 @@
         </is>
       </c>
       <c r="H338" s="0">
-        <v>2.86</v>
+        <v>3.04</v>
       </c>
     </row>
     <row r="339" spans="1:8">
@@ -11561,10 +11561,10 @@
         </is>
       </c>
       <c r="C339" s="0">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="D339" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E339" s="0">
         <v>2023</v>
@@ -11580,7 +11580,7 @@
         </is>
       </c>
       <c r="H339" s="0">
-        <v>1.42</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="340" spans="1:8">
@@ -11595,10 +11595,10 @@
         </is>
       </c>
       <c r="C340" s="0">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="D340" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E340" s="0">
         <v>2023</v>
@@ -11614,7 +11614,7 @@
         </is>
       </c>
       <c r="H340" s="0">
-        <v>2.7</v>
+        <v>3.01</v>
       </c>
     </row>
     <row r="341" spans="1:8">
@@ -11629,7 +11629,7 @@
         </is>
       </c>
       <c r="C341" s="0">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="D341" s="0">
         <v>6</v>
@@ -11648,7 +11648,7 @@
         </is>
       </c>
       <c r="H341" s="0">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="342" spans="1:8">
@@ -11663,7 +11663,7 @@
         </is>
       </c>
       <c r="C342" s="0">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="D342" s="0">
         <v>6</v>
@@ -11682,7 +11682,7 @@
         </is>
       </c>
       <c r="H342" s="0">
-        <v>2.61</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="343" spans="1:8">
@@ -11697,7 +11697,7 @@
         </is>
       </c>
       <c r="C343" s="0">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="D343" s="0">
         <v>6</v>
@@ -11716,7 +11716,7 @@
         </is>
       </c>
       <c r="H343" s="0">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="344" spans="1:8">
@@ -11731,7 +11731,7 @@
         </is>
       </c>
       <c r="C344" s="0">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="D344" s="0">
         <v>6</v>
@@ -11750,7 +11750,7 @@
         </is>
       </c>
       <c r="H344" s="0">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="345" spans="1:8">
@@ -11765,7 +11765,7 @@
         </is>
       </c>
       <c r="C345" s="0">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="D345" s="0">
         <v>6</v>
@@ -11784,7 +11784,7 @@
         </is>
       </c>
       <c r="H345" s="0">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="346" spans="1:8">
@@ -11799,7 +11799,7 @@
         </is>
       </c>
       <c r="C346" s="0">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="D346" s="0">
         <v>6</v>
@@ -11818,7 +11818,7 @@
         </is>
       </c>
       <c r="H346" s="0">
-        <v>2.58</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="347" spans="1:8">
@@ -11833,10 +11833,10 @@
         </is>
       </c>
       <c r="C347" s="0">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="D347" s="0">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E347" s="0">
         <v>2023</v>
@@ -11852,7 +11852,7 @@
         </is>
       </c>
       <c r="H347" s="0">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="348" spans="1:8">
@@ -11867,10 +11867,10 @@
         </is>
       </c>
       <c r="C348" s="0">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="D348" s="0">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E348" s="0">
         <v>2023</v>
@@ -11886,7 +11886,7 @@
         </is>
       </c>
       <c r="H348" s="0">
-        <v>2.54</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="349" spans="1:8">
@@ -11901,10 +11901,10 @@
         </is>
       </c>
       <c r="C349" s="0">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="D349" s="0">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E349" s="0">
         <v>2023</v>
@@ -11920,7 +11920,7 @@
         </is>
       </c>
       <c r="H349" s="0">
-        <v>1.52</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="350" spans="1:8">
@@ -11935,10 +11935,10 @@
         </is>
       </c>
       <c r="C350" s="0">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="D350" s="0">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E350" s="0">
         <v>2023</v>
@@ -11954,7 +11954,7 @@
         </is>
       </c>
       <c r="H350" s="0">
-        <v>2.47</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="351" spans="1:8">
@@ -11969,7 +11969,7 @@
         </is>
       </c>
       <c r="C351" s="0">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="D351" s="0">
         <v>5</v>
@@ -11988,7 +11988,7 @@
         </is>
       </c>
       <c r="H351" s="0">
-        <v>1.35</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="352" spans="1:8">
@@ -12003,7 +12003,7 @@
         </is>
       </c>
       <c r="C352" s="0">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="D352" s="0">
         <v>5</v>
@@ -12022,7 +12022,7 @@
         </is>
       </c>
       <c r="H352" s="0">
-        <v>2.45</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="353" spans="1:8">
@@ -12037,7 +12037,7 @@
         </is>
       </c>
       <c r="C353" s="0">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="D353" s="0">
         <v>5</v>
@@ -12056,7 +12056,7 @@
         </is>
       </c>
       <c r="H353" s="0">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="354" spans="1:8">
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="C354" s="0">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="D354" s="0">
         <v>5</v>
@@ -12090,7 +12090,7 @@
         </is>
       </c>
       <c r="H354" s="0">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="355" spans="1:8">
@@ -12105,10 +12105,10 @@
         </is>
       </c>
       <c r="C355" s="0">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="D355" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E355" s="0">
         <v>2023</v>
@@ -12124,7 +12124,7 @@
         </is>
       </c>
       <c r="H355" s="0">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="356" spans="1:8">
@@ -12139,10 +12139,10 @@
         </is>
       </c>
       <c r="C356" s="0">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="D356" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E356" s="0">
         <v>2023</v>
@@ -12158,7 +12158,7 @@
         </is>
       </c>
       <c r="H356" s="0">
-        <v>2.51</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="357" spans="1:8">
@@ -12173,10 +12173,10 @@
         </is>
       </c>
       <c r="C357" s="0">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D357" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E357" s="0">
         <v>2023</v>
@@ -12192,7 +12192,7 @@
         </is>
       </c>
       <c r="H357" s="0">
-        <v>1.58</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="358" spans="1:8">
@@ -12207,10 +12207,10 @@
         </is>
       </c>
       <c r="C358" s="0">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D358" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E358" s="0">
         <v>2023</v>
@@ -12226,7 +12226,7 @@
         </is>
       </c>
       <c r="H358" s="0">
-        <v>2.76</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="359" spans="1:8">
@@ -12241,7 +12241,7 @@
         </is>
       </c>
       <c r="C359" s="0">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="D359" s="0">
         <v>4</v>
@@ -12260,7 +12260,7 @@
         </is>
       </c>
       <c r="H359" s="0">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="360" spans="1:8">
@@ -12275,7 +12275,7 @@
         </is>
       </c>
       <c r="C360" s="0">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="D360" s="0">
         <v>4</v>
@@ -12294,7 +12294,7 @@
         </is>
       </c>
       <c r="H360" s="0">
-        <v>2.84</v>
+        <v>2.51</v>
       </c>
     </row>
     <row r="361" spans="1:8">
@@ -12309,7 +12309,7 @@
         </is>
       </c>
       <c r="C361" s="0">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="D361" s="0">
         <v>4</v>
@@ -12328,7 +12328,7 @@
         </is>
       </c>
       <c r="H361" s="0">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="362" spans="1:8">
@@ -12343,7 +12343,7 @@
         </is>
       </c>
       <c r="C362" s="0">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="D362" s="0">
         <v>4</v>
@@ -12362,7 +12362,7 @@
         </is>
       </c>
       <c r="H362" s="0">
-        <v>2.65</v>
+        <v>2.76</v>
       </c>
     </row>
     <row r="363" spans="1:8">
@@ -12377,10 +12377,10 @@
         </is>
       </c>
       <c r="C363" s="0">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="D363" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E363" s="0">
         <v>2023</v>
@@ -12396,7 +12396,7 @@
         </is>
       </c>
       <c r="H363" s="0">
-        <v>1.61</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="364" spans="1:8">
@@ -12411,10 +12411,10 @@
         </is>
       </c>
       <c r="C364" s="0">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="D364" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E364" s="0">
         <v>2023</v>
@@ -12430,7 +12430,7 @@
         </is>
       </c>
       <c r="H364" s="0">
-        <v>2.29</v>
+        <v>2.84</v>
       </c>
     </row>
     <row r="365" spans="1:8">
@@ -12445,10 +12445,10 @@
         </is>
       </c>
       <c r="C365" s="0">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="D365" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E365" s="0">
         <v>2023</v>
@@ -12464,7 +12464,7 @@
         </is>
       </c>
       <c r="H365" s="0">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="366" spans="1:8">
@@ -12479,10 +12479,10 @@
         </is>
       </c>
       <c r="C366" s="0">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="D366" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E366" s="0">
         <v>2023</v>
@@ -12498,7 +12498,7 @@
         </is>
       </c>
       <c r="H366" s="0">
-        <v>2.36</v>
+        <v>2.65</v>
       </c>
     </row>
     <row r="367" spans="1:8">
@@ -12513,7 +12513,7 @@
         </is>
       </c>
       <c r="C367" s="0">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D367" s="0">
         <v>3</v>
@@ -12532,7 +12532,7 @@
         </is>
       </c>
       <c r="H367" s="0">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="368" spans="1:8">
@@ -12547,7 +12547,7 @@
         </is>
       </c>
       <c r="C368" s="0">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D368" s="0">
         <v>3</v>
@@ -12566,7 +12566,7 @@
         </is>
       </c>
       <c r="H368" s="0">
-        <v>2.48</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="369" spans="1:8">
@@ -12581,7 +12581,7 @@
         </is>
       </c>
       <c r="C369" s="0">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="D369" s="0">
         <v>3</v>
@@ -12600,7 +12600,7 @@
         </is>
       </c>
       <c r="H369" s="0">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
     </row>
     <row r="370" spans="1:8">
@@ -12615,7 +12615,7 @@
         </is>
       </c>
       <c r="C370" s="0">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="D370" s="0">
         <v>3</v>
@@ -12634,7 +12634,7 @@
         </is>
       </c>
       <c r="H370" s="0">
-        <v>3.61</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="371" spans="1:8">
@@ -12649,7 +12649,7 @@
         </is>
       </c>
       <c r="C371" s="0">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="D371" s="0">
         <v>3</v>
@@ -12668,7 +12668,7 @@
         </is>
       </c>
       <c r="H371" s="0">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="372" spans="1:8">
@@ -12683,7 +12683,7 @@
         </is>
       </c>
       <c r="C372" s="0">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="D372" s="0">
         <v>3</v>
@@ -12702,7 +12702,7 @@
         </is>
       </c>
       <c r="H372" s="0">
-        <v>3.58</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="373" spans="1:8">
@@ -12717,10 +12717,10 @@
         </is>
       </c>
       <c r="C373" s="0">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="D373" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E373" s="0">
         <v>2023</v>
@@ -12751,10 +12751,10 @@
         </is>
       </c>
       <c r="C374" s="0">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="D374" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E374" s="0">
         <v>2023</v>
@@ -12770,7 +12770,7 @@
         </is>
       </c>
       <c r="H374" s="0">
-        <v>3.97</v>
+        <v>3.61</v>
       </c>
     </row>
     <row r="375" spans="1:8">
@@ -12785,10 +12785,10 @@
         </is>
       </c>
       <c r="C375" s="0">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="D375" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E375" s="0">
         <v>2023</v>
@@ -12804,7 +12804,7 @@
         </is>
       </c>
       <c r="H375" s="0">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="376" spans="1:8">
@@ -12819,10 +12819,10 @@
         </is>
       </c>
       <c r="C376" s="0">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="D376" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E376" s="0">
         <v>2023</v>
@@ -12838,7 +12838,7 @@
         </is>
       </c>
       <c r="H376" s="0">
-        <v>4.41</v>
+        <v>3.58</v>
       </c>
     </row>
     <row r="377" spans="1:8">
@@ -12853,7 +12853,7 @@
         </is>
       </c>
       <c r="C377" s="0">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="D377" s="0">
         <v>2</v>
@@ -12872,7 +12872,7 @@
         </is>
       </c>
       <c r="H377" s="0">
-        <v>1.63</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="378" spans="1:8">
@@ -12887,7 +12887,7 @@
         </is>
       </c>
       <c r="C378" s="0">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="D378" s="0">
         <v>2</v>
@@ -12906,7 +12906,7 @@
         </is>
       </c>
       <c r="H378" s="0">
-        <v>4.44</v>
+        <v>3.97</v>
       </c>
     </row>
     <row r="379" spans="1:8">
@@ -12921,7 +12921,7 @@
         </is>
       </c>
       <c r="C379" s="0">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="D379" s="0">
         <v>2</v>
@@ -12940,7 +12940,7 @@
         </is>
       </c>
       <c r="H379" s="0">
-        <v>1.39</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="380" spans="1:8">
@@ -12955,7 +12955,7 @@
         </is>
       </c>
       <c r="C380" s="0">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="D380" s="0">
         <v>2</v>
@@ -12974,7 +12974,7 @@
         </is>
       </c>
       <c r="H380" s="0">
-        <v>4.47</v>
+        <v>4.41</v>
       </c>
     </row>
     <row r="381" spans="1:8">
@@ -12989,10 +12989,10 @@
         </is>
       </c>
       <c r="C381" s="0">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="D381" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E381" s="0">
         <v>2023</v>
@@ -13008,7 +13008,7 @@
         </is>
       </c>
       <c r="H381" s="0">
-        <v>1.18</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="382" spans="1:8">
@@ -13023,10 +13023,10 @@
         </is>
       </c>
       <c r="C382" s="0">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="D382" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E382" s="0">
         <v>2023</v>
@@ -13042,7 +13042,7 @@
         </is>
       </c>
       <c r="H382" s="0">
-        <v>4.37</v>
+        <v>4.44</v>
       </c>
     </row>
     <row r="383" spans="1:8">
@@ -13057,10 +13057,10 @@
         </is>
       </c>
       <c r="C383" s="0">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D383" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E383" s="0">
         <v>2023</v>
@@ -13076,7 +13076,7 @@
         </is>
       </c>
       <c r="H383" s="0">
-        <v>1.28</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="384" spans="1:8">
@@ -13091,10 +13091,10 @@
         </is>
       </c>
       <c r="C384" s="0">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D384" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E384" s="0">
         <v>2023</v>
@@ -13110,7 +13110,7 @@
         </is>
       </c>
       <c r="H384" s="0">
-        <v>4.51</v>
+        <v>4.47</v>
       </c>
     </row>
     <row r="385" spans="1:8">
@@ -13125,7 +13125,7 @@
         </is>
       </c>
       <c r="C385" s="0">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="D385" s="0">
         <v>1</v>
@@ -13144,7 +13144,7 @@
         </is>
       </c>
       <c r="H385" s="0">
-        <v>1.42</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="386" spans="1:8">
@@ -13159,7 +13159,7 @@
         </is>
       </c>
       <c r="C386" s="0">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="D386" s="0">
         <v>1</v>
@@ -13178,7 +13178,7 @@
         </is>
       </c>
       <c r="H386" s="0">
-        <v>4.56</v>
+        <v>4.37</v>
       </c>
     </row>
     <row r="387" spans="1:8">
@@ -13193,7 +13193,7 @@
         </is>
       </c>
       <c r="C387" s="0">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="D387" s="0">
         <v>1</v>
@@ -13212,7 +13212,7 @@
         </is>
       </c>
       <c r="H387" s="0">
-        <v>1.76</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="388" spans="1:8">
@@ -13227,7 +13227,7 @@
         </is>
       </c>
       <c r="C388" s="0">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="D388" s="0">
         <v>1</v>
@@ -13246,11 +13246,147 @@
         </is>
       </c>
       <c r="H388" s="0">
+        <v>4.51</v>
+      </c>
+    </row>
+    <row r="389" spans="1:8">
+      <c r="A389" s="0" t="inlineStr">
+        <is>
+          <t>Nanica primeira - produtor</t>
+        </is>
+      </c>
+      <c r="B389" s="0" t="inlineStr">
+        <is>
+          <t>Bom Jesus da Lapa</t>
+        </is>
+      </c>
+      <c r="C389" s="0">
+        <v>13</v>
+      </c>
+      <c r="D389" s="0">
+        <v>1</v>
+      </c>
+      <c r="E389" s="0">
+        <v>2023</v>
+      </c>
+      <c r="F389" s="0" t="inlineStr">
+        <is>
+          <t>R$   </t>
+        </is>
+      </c>
+      <c r="G389" s="0" t="inlineStr">
+        <is>
+          <t>quilograma</t>
+        </is>
+      </c>
+      <c r="H389" s="0">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="390" spans="1:8">
+      <c r="A390" s="0" t="inlineStr">
+        <is>
+          <t>Prata anã primeira - produtor</t>
+        </is>
+      </c>
+      <c r="B390" s="0" t="inlineStr">
+        <is>
+          <t>Bom Jesus da Lapa</t>
+        </is>
+      </c>
+      <c r="C390" s="0">
+        <v>13</v>
+      </c>
+      <c r="D390" s="0">
+        <v>1</v>
+      </c>
+      <c r="E390" s="0">
+        <v>2023</v>
+      </c>
+      <c r="F390" s="0" t="inlineStr">
+        <is>
+          <t>R$   </t>
+        </is>
+      </c>
+      <c r="G390" s="0" t="inlineStr">
+        <is>
+          <t>quilograma</t>
+        </is>
+      </c>
+      <c r="H390" s="0">
+        <v>4.56</v>
+      </c>
+    </row>
+    <row r="391" spans="1:8">
+      <c r="A391" s="0" t="inlineStr">
+        <is>
+          <t>Nanica primeira - produtor</t>
+        </is>
+      </c>
+      <c r="B391" s="0" t="inlineStr">
+        <is>
+          <t>Bom Jesus da Lapa</t>
+        </is>
+      </c>
+      <c r="C391" s="0">
+        <v>6</v>
+      </c>
+      <c r="D391" s="0">
+        <v>1</v>
+      </c>
+      <c r="E391" s="0">
+        <v>2023</v>
+      </c>
+      <c r="F391" s="0" t="inlineStr">
+        <is>
+          <t>R$   </t>
+        </is>
+      </c>
+      <c r="G391" s="0" t="inlineStr">
+        <is>
+          <t>quilograma</t>
+        </is>
+      </c>
+      <c r="H391" s="0">
+        <v>1.76</v>
+      </c>
+    </row>
+    <row r="392" spans="1:8">
+      <c r="A392" s="0" t="inlineStr">
+        <is>
+          <t>Prata anã primeira - produtor</t>
+        </is>
+      </c>
+      <c r="B392" s="0" t="inlineStr">
+        <is>
+          <t>Bom Jesus da Lapa</t>
+        </is>
+      </c>
+      <c r="C392" s="0">
+        <v>6</v>
+      </c>
+      <c r="D392" s="0">
+        <v>1</v>
+      </c>
+      <c r="E392" s="0">
+        <v>2023</v>
+      </c>
+      <c r="F392" s="0" t="inlineStr">
+        <is>
+          <t>R$   </t>
+        </is>
+      </c>
+      <c r="G392" s="0" t="inlineStr">
+        <is>
+          <t>quilograma</t>
+        </is>
+      </c>
+      <c r="H392" s="0">
         <v>4.59</v>
       </c>
     </row>
-    <row r="389" spans="1:1">
-      <c r="A389" s="0" t="inlineStr">
+    <row r="393" spans="1:1">
+      <c r="A393" s="0" t="inlineStr">
         <is>
           <t>Fonte: Hortifruti/Cepea</t>
         </is>

--- a/fuentes/precios_banana_BJLapa.xlsx
+++ b/fuentes/precios_banana_BJLapa.xlsx
@@ -103,10 +103,10 @@
         </is>
       </c>
       <c r="C2" s="0">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="D2" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E2" s="0">
         <v>2026</v>
@@ -122,7 +122,7 @@
         </is>
       </c>
       <c r="H2" s="0">
-        <v>1.14</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -137,10 +137,10 @@
         </is>
       </c>
       <c r="C3" s="0">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="D3" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E3" s="0">
         <v>2026</v>
@@ -156,7 +156,7 @@
         </is>
       </c>
       <c r="H3" s="0">
-        <v>1.81</v>
+        <v>1.59</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -171,7 +171,7 @@
         </is>
       </c>
       <c r="C4" s="0">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D4" s="0">
         <v>9</v>
@@ -190,7 +190,7 @@
         </is>
       </c>
       <c r="H4" s="0">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -205,7 +205,7 @@
         </is>
       </c>
       <c r="C5" s="0">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D5" s="0">
         <v>9</v>
@@ -224,7 +224,7 @@
         </is>
       </c>
       <c r="H5" s="0">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -239,7 +239,7 @@
         </is>
       </c>
       <c r="C6" s="0">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="D6" s="0">
         <v>9</v>
@@ -258,7 +258,7 @@
         </is>
       </c>
       <c r="H6" s="0">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -273,7 +273,7 @@
         </is>
       </c>
       <c r="C7" s="0">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="D7" s="0">
         <v>9</v>
@@ -292,7 +292,7 @@
         </is>
       </c>
       <c r="H7" s="0">
-        <v>1.73</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -307,7 +307,7 @@
         </is>
       </c>
       <c r="C8" s="0">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D8" s="0">
         <v>9</v>
@@ -326,7 +326,7 @@
         </is>
       </c>
       <c r="H8" s="0">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -341,7 +341,7 @@
         </is>
       </c>
       <c r="C9" s="0">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D9" s="0">
         <v>9</v>
@@ -360,7 +360,7 @@
         </is>
       </c>
       <c r="H9" s="0">
-        <v>1.98</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -375,10 +375,10 @@
         </is>
       </c>
       <c r="C10" s="0">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="D10" s="0">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E10" s="0">
         <v>2026</v>
@@ -394,7 +394,7 @@
         </is>
       </c>
       <c r="H10" s="0">
-        <v>1.36</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -409,10 +409,10 @@
         </is>
       </c>
       <c r="C11" s="0">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="D11" s="0">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E11" s="0">
         <v>2026</v>
@@ -428,7 +428,7 @@
         </is>
       </c>
       <c r="H11" s="0">
-        <v>2.24</v>
+        <v>1.98</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -443,7 +443,7 @@
         </is>
       </c>
       <c r="C12" s="0">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D12" s="0">
         <v>8</v>
@@ -462,7 +462,7 @@
         </is>
       </c>
       <c r="H12" s="0">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="C13" s="0">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D13" s="0">
         <v>8</v>
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="H13" s="0">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="C14" s="0">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D14" s="0">
         <v>8</v>
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="H14" s="0">
-        <v>2.14</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="C15" s="0">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D15" s="0">
         <v>8</v>
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="H15" s="0">
-        <v>2.53</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -579,7 +579,7 @@
         </is>
       </c>
       <c r="C16" s="0">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D16" s="0">
         <v>8</v>
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="H16" s="0">
-        <v>2.4</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -613,7 +613,7 @@
         </is>
       </c>
       <c r="C17" s="0">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D17" s="0">
         <v>8</v>
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="H17" s="0">
-        <v>2.66</v>
+        <v>2.53</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -647,10 +647,10 @@
         </is>
       </c>
       <c r="C18" s="0">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="D18" s="0">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E18" s="0">
         <v>2026</v>
@@ -681,10 +681,10 @@
         </is>
       </c>
       <c r="C19" s="0">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="D19" s="0">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E19" s="0">
         <v>2026</v>
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="H19" s="0">
-        <v>2.4</v>
+        <v>2.66</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="C20" s="0">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="D20" s="0">
         <v>7</v>
@@ -730,17 +730,17 @@
       </c>
       <c r="G20" s="0" t="inlineStr">
         <is>
-          <t>Cento</t>
+          <t>quilograma</t>
         </is>
       </c>
       <c r="H20" s="0">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="0" t="inlineStr">
         <is>
-          <t>Nanica primeira - produtor</t>
+          <t>Prata anã primeira - produtor</t>
         </is>
       </c>
       <c r="B21" s="0" t="inlineStr">
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="C21" s="0">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="D21" s="0">
         <v>7</v>
@@ -768,13 +768,13 @@
         </is>
       </c>
       <c r="H21" s="0">
-        <v>2.22</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="0" t="inlineStr">
         <is>
-          <t>Prata anã primeira - produtor</t>
+          <t>Nanica primeira - produtor</t>
         </is>
       </c>
       <c r="B22" s="0" t="inlineStr">
@@ -798,11 +798,11 @@
       </c>
       <c r="G22" s="0" t="inlineStr">
         <is>
-          <t>quilograma</t>
+          <t>Cento</t>
         </is>
       </c>
       <c r="H22" s="0">
-        <v>2.07</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="C23" s="0">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D23" s="0">
         <v>7</v>
@@ -836,7 +836,7 @@
         </is>
       </c>
       <c r="H23" s="0">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="C24" s="0">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D24" s="0">
         <v>7</v>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="H24" s="0">
-        <v>1.83</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -885,7 +885,7 @@
         </is>
       </c>
       <c r="C25" s="0">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D25" s="0">
         <v>7</v>
@@ -900,17 +900,17 @@
       </c>
       <c r="G25" s="0" t="inlineStr">
         <is>
-          <t>Cento</t>
+          <t>quilograma</t>
         </is>
       </c>
       <c r="H25" s="0">
-        <v>1.9</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="0" t="inlineStr">
         <is>
-          <t>Nanica primeira - produtor</t>
+          <t>Prata anã primeira - produtor</t>
         </is>
       </c>
       <c r="B26" s="0" t="inlineStr">
@@ -919,7 +919,7 @@
         </is>
       </c>
       <c r="C26" s="0">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D26" s="0">
         <v>7</v>
@@ -938,13 +938,13 @@
         </is>
       </c>
       <c r="H26" s="0">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="0" t="inlineStr">
         <is>
-          <t>Prata anã primeira - produtor</t>
+          <t>Nanica primeira - produtor</t>
         </is>
       </c>
       <c r="B27" s="0" t="inlineStr">
@@ -968,11 +968,11 @@
       </c>
       <c r="G27" s="0" t="inlineStr">
         <is>
-          <t>quilograma</t>
+          <t>Cento</t>
         </is>
       </c>
       <c r="H27" s="0">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -987,7 +987,7 @@
         </is>
       </c>
       <c r="C28" s="0">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D28" s="0">
         <v>7</v>
@@ -1006,7 +1006,7 @@
         </is>
       </c>
       <c r="H28" s="0">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -1021,7 +1021,7 @@
         </is>
       </c>
       <c r="C29" s="0">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D29" s="0">
         <v>7</v>
@@ -1040,7 +1040,7 @@
         </is>
       </c>
       <c r="H29" s="0">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -1055,10 +1055,10 @@
         </is>
       </c>
       <c r="C30" s="0">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="D30" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E30" s="0">
         <v>2026</v>
@@ -1074,7 +1074,7 @@
         </is>
       </c>
       <c r="H30" s="0">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -1089,10 +1089,10 @@
         </is>
       </c>
       <c r="C31" s="0">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="D31" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E31" s="0">
         <v>2026</v>
@@ -1108,7 +1108,7 @@
         </is>
       </c>
       <c r="H31" s="0">
-        <v>2.37</v>
+        <v>1.98</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -1123,7 +1123,7 @@
         </is>
       </c>
       <c r="C32" s="0">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="D32" s="0">
         <v>6</v>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="C33" s="0">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="D33" s="0">
         <v>6</v>
@@ -1176,7 +1176,7 @@
         </is>
       </c>
       <c r="H33" s="0">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -1191,7 +1191,7 @@
         </is>
       </c>
       <c r="C34" s="0">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D34" s="0">
         <v>6</v>
@@ -1210,7 +1210,7 @@
         </is>
       </c>
       <c r="H34" s="0">
-        <v>1.56</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -1225,7 +1225,7 @@
         </is>
       </c>
       <c r="C35" s="0">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D35" s="0">
         <v>6</v>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="H35" s="0">
-        <v>2.58</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -1259,7 +1259,7 @@
         </is>
       </c>
       <c r="C36" s="0">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D36" s="0">
         <v>6</v>
@@ -1278,7 +1278,7 @@
         </is>
       </c>
       <c r="H36" s="0">
-        <v>1.12</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="C37" s="0">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D37" s="0">
         <v>6</v>
@@ -1312,7 +1312,7 @@
         </is>
       </c>
       <c r="H37" s="0">
-        <v>2.63</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="C38" s="0">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="D38" s="0">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E38" s="0">
         <v>2026</v>
@@ -1346,7 +1346,7 @@
         </is>
       </c>
       <c r="H38" s="0">
-        <v>0.86</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -1361,10 +1361,10 @@
         </is>
       </c>
       <c r="C39" s="0">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="D39" s="0">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E39" s="0">
         <v>2026</v>
@@ -1380,7 +1380,7 @@
         </is>
       </c>
       <c r="H39" s="0">
-        <v>2.54</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -1395,7 +1395,7 @@
         </is>
       </c>
       <c r="C40" s="0">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D40" s="0">
         <v>5</v>
@@ -1414,7 +1414,7 @@
         </is>
       </c>
       <c r="H40" s="0">
-        <v>0.61</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -1429,7 +1429,7 @@
         </is>
       </c>
       <c r="C41" s="0">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D41" s="0">
         <v>5</v>
@@ -1448,7 +1448,7 @@
         </is>
       </c>
       <c r="H41" s="0">
-        <v>2.63</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="C42" s="0">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="D42" s="0">
         <v>5</v>
@@ -1482,7 +1482,7 @@
         </is>
       </c>
       <c r="H42" s="0">
-        <v>0.62</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -1497,7 +1497,7 @@
         </is>
       </c>
       <c r="C43" s="0">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="D43" s="0">
         <v>5</v>
@@ -1516,7 +1516,7 @@
         </is>
       </c>
       <c r="H43" s="0">
-        <v>2.66</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="44" spans="1:8">
@@ -1531,7 +1531,7 @@
         </is>
       </c>
       <c r="C44" s="0">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D44" s="0">
         <v>5</v>
@@ -1550,13 +1550,13 @@
         </is>
       </c>
       <c r="H44" s="0">
-        <v>0.75</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="45" spans="1:8">
       <c r="A45" s="0" t="inlineStr">
         <is>
-          <t>Nanica primeira - produtor</t>
+          <t>Prata anã primeira - produtor</t>
         </is>
       </c>
       <c r="B45" s="0" t="inlineStr">
@@ -1565,10 +1565,10 @@
         </is>
       </c>
       <c r="C45" s="0">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="D45" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E45" s="0">
         <v>2026</v>
@@ -1584,13 +1584,13 @@
         </is>
       </c>
       <c r="H45" s="0">
-        <v>0.93</v>
+        <v>2.66</v>
       </c>
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="0" t="inlineStr">
         <is>
-          <t>Prata anã primeira - produtor</t>
+          <t>Nanica primeira - produtor</t>
         </is>
       </c>
       <c r="B46" s="0" t="inlineStr">
@@ -1599,10 +1599,10 @@
         </is>
       </c>
       <c r="C46" s="0">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="D46" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E46" s="0">
         <v>2026</v>
@@ -1618,7 +1618,7 @@
         </is>
       </c>
       <c r="H46" s="0">
-        <v>3.08</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="47" spans="1:8">
@@ -1633,7 +1633,7 @@
         </is>
       </c>
       <c r="C47" s="0">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="D47" s="0">
         <v>4</v>
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="C48" s="0">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="D48" s="0">
         <v>4</v>
@@ -1686,7 +1686,7 @@
         </is>
       </c>
       <c r="H48" s="0">
-        <v>3.04</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="49" spans="1:8">
@@ -1701,7 +1701,7 @@
         </is>
       </c>
       <c r="C49" s="0">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D49" s="0">
         <v>4</v>
@@ -1720,7 +1720,7 @@
         </is>
       </c>
       <c r="H49" s="0">
-        <v>1.02</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="50" spans="1:8">
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="C50" s="0">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D50" s="0">
         <v>4</v>
@@ -1754,7 +1754,7 @@
         </is>
       </c>
       <c r="H50" s="0">
-        <v>3.09</v>
+        <v>3.04</v>
       </c>
     </row>
     <row r="51" spans="1:8">
@@ -1769,7 +1769,7 @@
         </is>
       </c>
       <c r="C51" s="0">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D51" s="0">
         <v>4</v>
@@ -1788,7 +1788,7 @@
         </is>
       </c>
       <c r="H51" s="0">
-        <v>1.27</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="52" spans="1:8">
@@ -1803,7 +1803,7 @@
         </is>
       </c>
       <c r="C52" s="0">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D52" s="0">
         <v>4</v>
@@ -1822,7 +1822,7 @@
         </is>
       </c>
       <c r="H52" s="0">
-        <v>3.12</v>
+        <v>3.09</v>
       </c>
     </row>
     <row r="53" spans="1:8">
@@ -1837,7 +1837,7 @@
         </is>
       </c>
       <c r="C53" s="0">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D53" s="0">
         <v>4</v>
@@ -1856,7 +1856,7 @@
         </is>
       </c>
       <c r="H53" s="0">
-        <v>1.56</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="54" spans="1:8">
@@ -1871,7 +1871,7 @@
         </is>
       </c>
       <c r="C54" s="0">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D54" s="0">
         <v>4</v>
@@ -1890,7 +1890,7 @@
         </is>
       </c>
       <c r="H54" s="0">
-        <v>3.13</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="55" spans="1:8">
@@ -1905,10 +1905,10 @@
         </is>
       </c>
       <c r="C55" s="0">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="D55" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E55" s="0">
         <v>2026</v>
@@ -1924,7 +1924,7 @@
         </is>
       </c>
       <c r="H55" s="0">
-        <v>2.04</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="56" spans="1:8">
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="C56" s="0">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="D56" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E56" s="0">
         <v>2026</v>
@@ -1958,7 +1958,7 @@
         </is>
       </c>
       <c r="H56" s="0">
-        <v>3.23</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="57" spans="1:8">
@@ -1973,7 +1973,7 @@
         </is>
       </c>
       <c r="C57" s="0">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D57" s="0">
         <v>3</v>
@@ -1992,7 +1992,7 @@
         </is>
       </c>
       <c r="H57" s="0">
-        <v>2.36</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="58" spans="1:8">
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="C58" s="0">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D58" s="0">
         <v>3</v>
@@ -2026,7 +2026,7 @@
         </is>
       </c>
       <c r="H58" s="0">
-        <v>3.4</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="59" spans="1:8">
@@ -2041,7 +2041,7 @@
         </is>
       </c>
       <c r="C59" s="0">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D59" s="0">
         <v>3</v>
@@ -2060,7 +2060,7 @@
         </is>
       </c>
       <c r="H59" s="0">
-        <v>2.23</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="60" spans="1:8">
@@ -2075,7 +2075,7 @@
         </is>
       </c>
       <c r="C60" s="0">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D60" s="0">
         <v>3</v>
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="H60" s="0">
-        <v>3.19</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="61" spans="1:8">
@@ -2109,7 +2109,7 @@
         </is>
       </c>
       <c r="C61" s="0">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D61" s="0">
         <v>3</v>
@@ -2128,7 +2128,7 @@
         </is>
       </c>
       <c r="H61" s="0">
-        <v>1.9</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="62" spans="1:8">
@@ -2143,7 +2143,7 @@
         </is>
       </c>
       <c r="C62" s="0">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D62" s="0">
         <v>3</v>
@@ -2162,7 +2162,7 @@
         </is>
       </c>
       <c r="H62" s="0">
-        <v>3.11</v>
+        <v>3.19</v>
       </c>
     </row>
     <row r="63" spans="1:8">
@@ -2177,10 +2177,10 @@
         </is>
       </c>
       <c r="C63" s="0">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="D63" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E63" s="0">
         <v>2026</v>
@@ -2196,7 +2196,7 @@
         </is>
       </c>
       <c r="H63" s="0">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="64" spans="1:8">
@@ -2211,10 +2211,10 @@
         </is>
       </c>
       <c r="C64" s="0">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="D64" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E64" s="0">
         <v>2026</v>
@@ -2230,7 +2230,7 @@
         </is>
       </c>
       <c r="H64" s="0">
-        <v>3</v>
+        <v>3.11</v>
       </c>
     </row>
     <row r="65" spans="1:8">
@@ -2245,7 +2245,7 @@
         </is>
       </c>
       <c r="C65" s="0">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D65" s="0">
         <v>2</v>
@@ -2264,7 +2264,7 @@
         </is>
       </c>
       <c r="H65" s="0">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="66" spans="1:8">
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="C66" s="0">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D66" s="0">
         <v>2</v>
@@ -2298,7 +2298,7 @@
         </is>
       </c>
       <c r="H66" s="0">
-        <v>3.27</v>
+        <v>3</v>
       </c>
     </row>
     <row r="67" spans="1:8">
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="C67" s="0">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D67" s="0">
         <v>2</v>
@@ -2332,7 +2332,7 @@
         </is>
       </c>
       <c r="H67" s="0">
-        <v>1.24</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="68" spans="1:8">
@@ -2347,7 +2347,7 @@
         </is>
       </c>
       <c r="C68" s="0">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D68" s="0">
         <v>2</v>
@@ -2366,7 +2366,7 @@
         </is>
       </c>
       <c r="H68" s="0">
-        <v>3.06</v>
+        <v>3.27</v>
       </c>
     </row>
     <row r="69" spans="1:8">
@@ -2381,7 +2381,7 @@
         </is>
       </c>
       <c r="C69" s="0">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D69" s="0">
         <v>2</v>
@@ -2400,7 +2400,7 @@
         </is>
       </c>
       <c r="H69" s="0">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="70" spans="1:8">
@@ -2415,7 +2415,7 @@
         </is>
       </c>
       <c r="C70" s="0">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D70" s="0">
         <v>2</v>
@@ -2434,7 +2434,7 @@
         </is>
       </c>
       <c r="H70" s="0">
-        <v>3.05</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="71" spans="1:8">
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="C71" s="0">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="D71" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E71" s="0">
         <v>2026</v>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="H71" s="0">
-        <v>1</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="72" spans="1:8">
@@ -2483,10 +2483,10 @@
         </is>
       </c>
       <c r="C72" s="0">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="D72" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E72" s="0">
         <v>2026</v>
@@ -2502,7 +2502,7 @@
         </is>
       </c>
       <c r="H72" s="0">
-        <v>3.01</v>
+        <v>3.05</v>
       </c>
     </row>
     <row r="73" spans="1:8">
@@ -2517,7 +2517,7 @@
         </is>
       </c>
       <c r="C73" s="0">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D73" s="0">
         <v>1</v>
@@ -2536,7 +2536,7 @@
         </is>
       </c>
       <c r="H73" s="0">
-        <v>1.06</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74" spans="1:8">
@@ -2551,7 +2551,7 @@
         </is>
       </c>
       <c r="C74" s="0">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D74" s="0">
         <v>1</v>
@@ -2570,7 +2570,7 @@
         </is>
       </c>
       <c r="H74" s="0">
-        <v>2.97</v>
+        <v>3.01</v>
       </c>
     </row>
     <row r="75" spans="1:8">
@@ -2585,7 +2585,7 @@
         </is>
       </c>
       <c r="C75" s="0">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="D75" s="0">
         <v>1</v>
@@ -2604,7 +2604,7 @@
         </is>
       </c>
       <c r="H75" s="0">
-        <v>1.64</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="76" spans="1:8">
@@ -2619,7 +2619,7 @@
         </is>
       </c>
       <c r="C76" s="0">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="D76" s="0">
         <v>1</v>
@@ -2638,7 +2638,7 @@
         </is>
       </c>
       <c r="H76" s="0">
-        <v>3.49</v>
+        <v>2.97</v>
       </c>
     </row>
     <row r="77" spans="1:8">
@@ -2653,7 +2653,7 @@
         </is>
       </c>
       <c r="C77" s="0">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D77" s="0">
         <v>1</v>
@@ -2672,7 +2672,7 @@
         </is>
       </c>
       <c r="H77" s="0">
-        <v>2.06</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="78" spans="1:8">
@@ -2687,7 +2687,7 @@
         </is>
       </c>
       <c r="C78" s="0">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D78" s="0">
         <v>1</v>
@@ -2706,7 +2706,7 @@
         </is>
       </c>
       <c r="H78" s="0">
-        <v>3.63</v>
+        <v>3.49</v>
       </c>
     </row>
     <row r="79" spans="1:8">
@@ -2721,7 +2721,7 @@
         </is>
       </c>
       <c r="C79" s="0">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D79" s="0">
         <v>1</v>
@@ -2740,7 +2740,7 @@
         </is>
       </c>
       <c r="H79" s="0">
-        <v>2.63</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="80" spans="1:8">
@@ -2755,7 +2755,7 @@
         </is>
       </c>
       <c r="C80" s="0">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D80" s="0">
         <v>1</v>
@@ -2774,7 +2774,7 @@
         </is>
       </c>
       <c r="H80" s="0">
-        <v>3.49</v>
+        <v>3.63</v>
       </c>
     </row>
     <row r="81" spans="1:8">
@@ -2789,13 +2789,13 @@
         </is>
       </c>
       <c r="C81" s="0">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="D81" s="0">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E81" s="0">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="F81" s="0" t="inlineStr">
         <is>
@@ -2808,7 +2808,7 @@
         </is>
       </c>
       <c r="H81" s="0">
-        <v>2.67</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="82" spans="1:8">
@@ -2823,13 +2823,13 @@
         </is>
       </c>
       <c r="C82" s="0">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="D82" s="0">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E82" s="0">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="F82" s="0" t="inlineStr">
         <is>
@@ -2842,13 +2842,13 @@
         </is>
       </c>
       <c r="H82" s="0">
-        <v>3.4</v>
+        <v>3.49</v>
       </c>
     </row>
     <row r="83" spans="1:8">
       <c r="A83" s="0" t="inlineStr">
         <is>
-          <t>Prata litoral primeira - produtor</t>
+          <t>Nanica primeira - produtor</t>
         </is>
       </c>
       <c r="B83" s="0" t="inlineStr">
@@ -2876,13 +2876,13 @@
         </is>
       </c>
       <c r="H83" s="0">
-        <v>3</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="84" spans="1:8">
       <c r="A84" s="0" t="inlineStr">
         <is>
-          <t>Nanica primeira - produtor</t>
+          <t>Prata anã primeira - produtor</t>
         </is>
       </c>
       <c r="B84" s="0" t="inlineStr">
@@ -2891,7 +2891,7 @@
         </is>
       </c>
       <c r="C84" s="0">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="D84" s="0">
         <v>12</v>
@@ -2910,13 +2910,13 @@
         </is>
       </c>
       <c r="H84" s="0">
-        <v>2.83</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="85" spans="1:8">
       <c r="A85" s="0" t="inlineStr">
         <is>
-          <t>Prata anã primeira - produtor</t>
+          <t>Prata litoral primeira - produtor</t>
         </is>
       </c>
       <c r="B85" s="0" t="inlineStr">
@@ -2925,7 +2925,7 @@
         </is>
       </c>
       <c r="C85" s="0">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="D85" s="0">
         <v>12</v>
@@ -2944,7 +2944,7 @@
         </is>
       </c>
       <c r="H85" s="0">
-        <v>3.59</v>
+        <v>3</v>
       </c>
     </row>
     <row r="86" spans="1:8">
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="C86" s="0">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D86" s="0">
         <v>12</v>
@@ -2978,7 +2978,7 @@
         </is>
       </c>
       <c r="H86" s="0">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
     </row>
     <row r="87" spans="1:8">
@@ -2993,7 +2993,7 @@
         </is>
       </c>
       <c r="C87" s="0">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D87" s="0">
         <v>12</v>
@@ -3012,7 +3012,7 @@
         </is>
       </c>
       <c r="H87" s="0">
-        <v>3.54</v>
+        <v>3.59</v>
       </c>
     </row>
     <row r="88" spans="1:8">
@@ -3027,7 +3027,7 @@
         </is>
       </c>
       <c r="C88" s="0">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D88" s="0">
         <v>12</v>
@@ -3046,7 +3046,7 @@
         </is>
       </c>
       <c r="H88" s="0">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="89" spans="1:8">
@@ -3061,7 +3061,7 @@
         </is>
       </c>
       <c r="C89" s="0">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D89" s="0">
         <v>12</v>
@@ -3080,7 +3080,7 @@
         </is>
       </c>
       <c r="H89" s="0">
-        <v>3.7</v>
+        <v>3.54</v>
       </c>
     </row>
     <row r="90" spans="1:8">
@@ -3095,10 +3095,10 @@
         </is>
       </c>
       <c r="C90" s="0">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="D90" s="0">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E90" s="0">
         <v>2025</v>
@@ -3114,7 +3114,7 @@
         </is>
       </c>
       <c r="H90" s="0">
-        <v>2.82</v>
+        <v>2.89</v>
       </c>
     </row>
     <row r="91" spans="1:8">
@@ -3129,10 +3129,10 @@
         </is>
       </c>
       <c r="C91" s="0">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="D91" s="0">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E91" s="0">
         <v>2025</v>
@@ -3163,7 +3163,7 @@
         </is>
       </c>
       <c r="C92" s="0">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D92" s="0">
         <v>11</v>
@@ -3182,7 +3182,7 @@
         </is>
       </c>
       <c r="H92" s="0">
-        <v>2.79</v>
+        <v>2.82</v>
       </c>
     </row>
     <row r="93" spans="1:8">
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="C93" s="0">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D93" s="0">
         <v>11</v>
@@ -3216,7 +3216,7 @@
         </is>
       </c>
       <c r="H93" s="0">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="94" spans="1:8">
@@ -3231,7 +3231,7 @@
         </is>
       </c>
       <c r="C94" s="0">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D94" s="0">
         <v>11</v>
@@ -3250,7 +3250,7 @@
         </is>
       </c>
       <c r="H94" s="0">
-        <v>2.67</v>
+        <v>2.79</v>
       </c>
     </row>
     <row r="95" spans="1:8">
@@ -3265,7 +3265,7 @@
         </is>
       </c>
       <c r="C95" s="0">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D95" s="0">
         <v>11</v>
@@ -3284,7 +3284,7 @@
         </is>
       </c>
       <c r="H95" s="0">
-        <v>3.59</v>
+        <v>3.58</v>
       </c>
     </row>
     <row r="96" spans="1:8">
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="C96" s="0">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D96" s="0">
         <v>11</v>
@@ -3318,7 +3318,7 @@
         </is>
       </c>
       <c r="H96" s="0">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="97" spans="1:8">
@@ -3333,7 +3333,7 @@
         </is>
       </c>
       <c r="C97" s="0">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D97" s="0">
         <v>11</v>
@@ -3352,7 +3352,7 @@
         </is>
       </c>
       <c r="H97" s="0">
-        <v>3.2</v>
+        <v>3.59</v>
       </c>
     </row>
     <row r="98" spans="1:8">
@@ -3367,10 +3367,10 @@
         </is>
       </c>
       <c r="C98" s="0">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="D98" s="0">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E98" s="0">
         <v>2025</v>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="H98" s="0">
-        <v>2.98</v>
+        <v>2.68</v>
       </c>
     </row>
     <row r="99" spans="1:8">
@@ -3401,10 +3401,10 @@
         </is>
       </c>
       <c r="C99" s="0">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="D99" s="0">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E99" s="0">
         <v>2025</v>
@@ -3420,7 +3420,7 @@
         </is>
       </c>
       <c r="H99" s="0">
-        <v>2.43</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="100" spans="1:8">
@@ -3435,7 +3435,7 @@
         </is>
       </c>
       <c r="C100" s="0">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="D100" s="0">
         <v>10</v>
@@ -3454,7 +3454,7 @@
         </is>
       </c>
       <c r="H100" s="0">
-        <v>2.77</v>
+        <v>2.98</v>
       </c>
     </row>
     <row r="101" spans="1:8">
@@ -3469,7 +3469,7 @@
         </is>
       </c>
       <c r="C101" s="0">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="D101" s="0">
         <v>10</v>
@@ -3488,7 +3488,7 @@
         </is>
       </c>
       <c r="H101" s="0">
-        <v>2.25</v>
+        <v>2.43</v>
       </c>
     </row>
     <row r="102" spans="1:8">
@@ -3503,7 +3503,7 @@
         </is>
       </c>
       <c r="C102" s="0">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D102" s="0">
         <v>10</v>
@@ -3522,7 +3522,7 @@
         </is>
       </c>
       <c r="H102" s="0">
-        <v>2.88</v>
+        <v>2.77</v>
       </c>
     </row>
     <row r="103" spans="1:8">
@@ -3537,7 +3537,7 @@
         </is>
       </c>
       <c r="C103" s="0">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D103" s="0">
         <v>10</v>
@@ -3556,7 +3556,7 @@
         </is>
       </c>
       <c r="H103" s="0">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="104" spans="1:8">
@@ -3571,7 +3571,7 @@
         </is>
       </c>
       <c r="C104" s="0">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D104" s="0">
         <v>10</v>
@@ -3590,7 +3590,7 @@
         </is>
       </c>
       <c r="H104" s="0">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="105" spans="1:8">
@@ -3605,7 +3605,7 @@
         </is>
       </c>
       <c r="C105" s="0">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D105" s="0">
         <v>10</v>
@@ -3624,7 +3624,7 @@
         </is>
       </c>
       <c r="H105" s="0">
-        <v>2.37</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="106" spans="1:8">
@@ -3639,7 +3639,7 @@
         </is>
       </c>
       <c r="C106" s="0">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D106" s="0">
         <v>10</v>
@@ -3658,7 +3658,7 @@
         </is>
       </c>
       <c r="H106" s="0">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
     </row>
     <row r="107" spans="1:8">
@@ -3673,7 +3673,7 @@
         </is>
       </c>
       <c r="C107" s="0">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D107" s="0">
         <v>10</v>
@@ -3692,7 +3692,7 @@
         </is>
       </c>
       <c r="H107" s="0">
-        <v>2.6</v>
+        <v>2.37</v>
       </c>
     </row>
     <row r="108" spans="1:8">
@@ -3707,10 +3707,10 @@
         </is>
       </c>
       <c r="C108" s="0">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="D108" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E108" s="0">
         <v>2025</v>
@@ -3726,7 +3726,7 @@
         </is>
       </c>
       <c r="H108" s="0">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
     </row>
     <row r="109" spans="1:8">
@@ -3741,10 +3741,10 @@
         </is>
       </c>
       <c r="C109" s="0">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="D109" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E109" s="0">
         <v>2025</v>
@@ -3760,7 +3760,7 @@
         </is>
       </c>
       <c r="H109" s="0">
-        <v>3.11</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="110" spans="1:8">
@@ -3775,7 +3775,7 @@
         </is>
       </c>
       <c r="C110" s="0">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D110" s="0">
         <v>9</v>
@@ -3794,7 +3794,7 @@
         </is>
       </c>
       <c r="H110" s="0">
-        <v>3.03</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="111" spans="1:8">
@@ -3809,7 +3809,7 @@
         </is>
       </c>
       <c r="C111" s="0">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D111" s="0">
         <v>9</v>
@@ -3828,7 +3828,7 @@
         </is>
       </c>
       <c r="H111" s="0">
-        <v>3.77</v>
+        <v>3.11</v>
       </c>
     </row>
     <row r="112" spans="1:8">
@@ -3843,7 +3843,7 @@
         </is>
       </c>
       <c r="C112" s="0">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D112" s="0">
         <v>9</v>
@@ -3862,7 +3862,7 @@
         </is>
       </c>
       <c r="H112" s="0">
-        <v>2.96</v>
+        <v>3.03</v>
       </c>
     </row>
     <row r="113" spans="1:8">
@@ -3877,7 +3877,7 @@
         </is>
       </c>
       <c r="C113" s="0">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D113" s="0">
         <v>9</v>
@@ -3896,7 +3896,7 @@
         </is>
       </c>
       <c r="H113" s="0">
-        <v>3.61</v>
+        <v>3.77</v>
       </c>
     </row>
     <row r="114" spans="1:8">
@@ -3911,7 +3911,7 @@
         </is>
       </c>
       <c r="C114" s="0">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D114" s="0">
         <v>9</v>
@@ -3930,7 +3930,7 @@
         </is>
       </c>
       <c r="H114" s="0">
-        <v>2.84</v>
+        <v>2.96</v>
       </c>
     </row>
     <row r="115" spans="1:8">
@@ -3945,7 +3945,7 @@
         </is>
       </c>
       <c r="C115" s="0">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D115" s="0">
         <v>9</v>
@@ -3964,7 +3964,7 @@
         </is>
       </c>
       <c r="H115" s="0">
-        <v>3.48</v>
+        <v>3.61</v>
       </c>
     </row>
     <row r="116" spans="1:8">
@@ -3979,10 +3979,10 @@
         </is>
       </c>
       <c r="C116" s="0">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="D116" s="0">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E116" s="0">
         <v>2025</v>
@@ -3998,7 +3998,7 @@
         </is>
       </c>
       <c r="H116" s="0">
-        <v>3.12</v>
+        <v>2.84</v>
       </c>
     </row>
     <row r="117" spans="1:8">
@@ -4013,10 +4013,10 @@
         </is>
       </c>
       <c r="C117" s="0">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="D117" s="0">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E117" s="0">
         <v>2025</v>
@@ -4032,7 +4032,7 @@
         </is>
       </c>
       <c r="H117" s="0">
-        <v>3.72</v>
+        <v>3.48</v>
       </c>
     </row>
     <row r="118" spans="1:8">
@@ -4047,7 +4047,7 @@
         </is>
       </c>
       <c r="C118" s="0">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D118" s="0">
         <v>8</v>
@@ -4066,7 +4066,7 @@
         </is>
       </c>
       <c r="H118" s="0">
-        <v>3.06</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="119" spans="1:8">
@@ -4081,7 +4081,7 @@
         </is>
       </c>
       <c r="C119" s="0">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D119" s="0">
         <v>8</v>
@@ -4100,7 +4100,7 @@
         </is>
       </c>
       <c r="H119" s="0">
-        <v>3.6</v>
+        <v>3.72</v>
       </c>
     </row>
     <row r="120" spans="1:8">
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="C120" s="0">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D120" s="0">
         <v>8</v>
@@ -4149,7 +4149,7 @@
         </is>
       </c>
       <c r="C121" s="0">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D121" s="0">
         <v>8</v>
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="H121" s="0">
-        <v>3.67</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="122" spans="1:8">
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="C122" s="0">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D122" s="0">
         <v>8</v>
@@ -4202,7 +4202,7 @@
         </is>
       </c>
       <c r="H122" s="0">
-        <v>2.73</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="123" spans="1:8">
@@ -4217,7 +4217,7 @@
         </is>
       </c>
       <c r="C123" s="0">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D123" s="0">
         <v>8</v>
@@ -4236,7 +4236,7 @@
         </is>
       </c>
       <c r="H123" s="0">
-        <v>3.3</v>
+        <v>3.67</v>
       </c>
     </row>
     <row r="124" spans="1:8">
@@ -4251,10 +4251,10 @@
         </is>
       </c>
       <c r="C124" s="0">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="D124" s="0">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E124" s="0">
         <v>2025</v>
@@ -4270,7 +4270,7 @@
         </is>
       </c>
       <c r="H124" s="0">
-        <v>2.3</v>
+        <v>2.73</v>
       </c>
     </row>
     <row r="125" spans="1:8">
@@ -4285,10 +4285,10 @@
         </is>
       </c>
       <c r="C125" s="0">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="D125" s="0">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E125" s="0">
         <v>2025</v>
@@ -4304,7 +4304,7 @@
         </is>
       </c>
       <c r="H125" s="0">
-        <v>3.16</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="126" spans="1:8">
@@ -4319,7 +4319,7 @@
         </is>
       </c>
       <c r="C126" s="0">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D126" s="0">
         <v>7</v>
@@ -4338,7 +4338,7 @@
         </is>
       </c>
       <c r="H126" s="0">
-        <v>1.61</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="127" spans="1:8">
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="C127" s="0">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D127" s="0">
         <v>7</v>
@@ -4372,7 +4372,7 @@
         </is>
       </c>
       <c r="H127" s="0">
-        <v>2.97</v>
+        <v>3.16</v>
       </c>
     </row>
     <row r="128" spans="1:8">
@@ -4387,7 +4387,7 @@
         </is>
       </c>
       <c r="C128" s="0">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D128" s="0">
         <v>7</v>
@@ -4406,7 +4406,7 @@
         </is>
       </c>
       <c r="H128" s="0">
-        <v>1.4</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="129" spans="1:8">
@@ -4421,7 +4421,7 @@
         </is>
       </c>
       <c r="C129" s="0">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D129" s="0">
         <v>7</v>
@@ -4440,7 +4440,7 @@
         </is>
       </c>
       <c r="H129" s="0">
-        <v>2.79</v>
+        <v>2.97</v>
       </c>
     </row>
     <row r="130" spans="1:8">
@@ -4455,7 +4455,7 @@
         </is>
       </c>
       <c r="C130" s="0">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="D130" s="0">
         <v>7</v>
@@ -4474,7 +4474,7 @@
         </is>
       </c>
       <c r="H130" s="0">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="131" spans="1:8">
@@ -4489,7 +4489,7 @@
         </is>
       </c>
       <c r="C131" s="0">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="D131" s="0">
         <v>7</v>
@@ -4508,7 +4508,7 @@
         </is>
       </c>
       <c r="H131" s="0">
-        <v>2.69</v>
+        <v>2.79</v>
       </c>
     </row>
     <row r="132" spans="1:8">
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="C132" s="0">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D132" s="0">
         <v>7</v>
@@ -4542,7 +4542,7 @@
         </is>
       </c>
       <c r="H132" s="0">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="133" spans="1:8">
@@ -4557,7 +4557,7 @@
         </is>
       </c>
       <c r="C133" s="0">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D133" s="0">
         <v>7</v>
@@ -4576,7 +4576,7 @@
         </is>
       </c>
       <c r="H133" s="0">
-        <v>2.82</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="134" spans="1:8">
@@ -4591,10 +4591,10 @@
         </is>
       </c>
       <c r="C134" s="0">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="D134" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E134" s="0">
         <v>2025</v>
@@ -4610,7 +4610,7 @@
         </is>
       </c>
       <c r="H134" s="0">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="135" spans="1:8">
@@ -4625,10 +4625,10 @@
         </is>
       </c>
       <c r="C135" s="0">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="D135" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E135" s="0">
         <v>2025</v>
@@ -4644,7 +4644,7 @@
         </is>
       </c>
       <c r="H135" s="0">
-        <v>2.73</v>
+        <v>2.82</v>
       </c>
     </row>
     <row r="136" spans="1:8">
@@ -4659,7 +4659,7 @@
         </is>
       </c>
       <c r="C136" s="0">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D136" s="0">
         <v>6</v>
@@ -4678,7 +4678,7 @@
         </is>
       </c>
       <c r="H136" s="0">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="137" spans="1:8">
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="C137" s="0">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D137" s="0">
         <v>6</v>
@@ -4712,7 +4712,7 @@
         </is>
       </c>
       <c r="H137" s="0">
-        <v>2.57</v>
+        <v>2.73</v>
       </c>
     </row>
     <row r="138" spans="1:8">
@@ -4727,7 +4727,7 @@
         </is>
       </c>
       <c r="C138" s="0">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D138" s="0">
         <v>6</v>
@@ -4746,7 +4746,7 @@
         </is>
       </c>
       <c r="H138" s="0">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="139" spans="1:8">
@@ -4761,7 +4761,7 @@
         </is>
       </c>
       <c r="C139" s="0">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D139" s="0">
         <v>6</v>
@@ -4780,7 +4780,7 @@
         </is>
       </c>
       <c r="H139" s="0">
-        <v>2.4</v>
+        <v>2.57</v>
       </c>
     </row>
     <row r="140" spans="1:8">
@@ -4795,7 +4795,7 @@
         </is>
       </c>
       <c r="C140" s="0">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D140" s="0">
         <v>6</v>
@@ -4814,7 +4814,7 @@
         </is>
       </c>
       <c r="H140" s="0">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="141" spans="1:8">
@@ -4829,7 +4829,7 @@
         </is>
       </c>
       <c r="C141" s="0">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D141" s="0">
         <v>6</v>
@@ -4848,7 +4848,7 @@
         </is>
       </c>
       <c r="H141" s="0">
-        <v>2.23</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="142" spans="1:8">
@@ -4863,10 +4863,10 @@
         </is>
       </c>
       <c r="C142" s="0">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="D142" s="0">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E142" s="0">
         <v>2025</v>
@@ -4882,7 +4882,7 @@
         </is>
       </c>
       <c r="H142" s="0">
-        <v>0.73</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="143" spans="1:8">
@@ -4897,10 +4897,10 @@
         </is>
       </c>
       <c r="C143" s="0">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="D143" s="0">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E143" s="0">
         <v>2025</v>
@@ -4931,7 +4931,7 @@
         </is>
       </c>
       <c r="C144" s="0">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D144" s="0">
         <v>5</v>
@@ -4950,7 +4950,7 @@
         </is>
       </c>
       <c r="H144" s="0">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="145" spans="1:8">
@@ -4965,7 +4965,7 @@
         </is>
       </c>
       <c r="C145" s="0">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D145" s="0">
         <v>5</v>
@@ -4984,7 +4984,7 @@
         </is>
       </c>
       <c r="H145" s="0">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="146" spans="1:8">
@@ -4999,7 +4999,7 @@
         </is>
       </c>
       <c r="C146" s="0">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="D146" s="0">
         <v>5</v>
@@ -5018,7 +5018,7 @@
         </is>
       </c>
       <c r="H146" s="0">
-        <v>0.89</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="147" spans="1:8">
@@ -5033,7 +5033,7 @@
         </is>
       </c>
       <c r="C147" s="0">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="D147" s="0">
         <v>5</v>
@@ -5052,7 +5052,7 @@
         </is>
       </c>
       <c r="H147" s="0">
-        <v>2.53</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="148" spans="1:8">
@@ -5067,7 +5067,7 @@
         </is>
       </c>
       <c r="C148" s="0">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D148" s="0">
         <v>5</v>
@@ -5086,7 +5086,7 @@
         </is>
       </c>
       <c r="H148" s="0">
-        <v>1.01</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="149" spans="1:8">
@@ -5101,7 +5101,7 @@
         </is>
       </c>
       <c r="C149" s="0">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D149" s="0">
         <v>5</v>
@@ -5120,7 +5120,7 @@
         </is>
       </c>
       <c r="H149" s="0">
-        <v>2.66</v>
+        <v>2.53</v>
       </c>
     </row>
     <row r="150" spans="1:8">
@@ -5135,7 +5135,7 @@
         </is>
       </c>
       <c r="C150" s="0">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D150" s="0">
         <v>5</v>
@@ -5154,7 +5154,7 @@
         </is>
       </c>
       <c r="H150" s="0">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="151" spans="1:8">
@@ -5169,7 +5169,7 @@
         </is>
       </c>
       <c r="C151" s="0">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D151" s="0">
         <v>5</v>
@@ -5188,7 +5188,7 @@
         </is>
       </c>
       <c r="H151" s="0">
-        <v>3.19</v>
+        <v>2.66</v>
       </c>
     </row>
     <row r="152" spans="1:8">
@@ -5203,10 +5203,10 @@
         </is>
       </c>
       <c r="C152" s="0">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="D152" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E152" s="0">
         <v>2025</v>
@@ -5222,7 +5222,7 @@
         </is>
       </c>
       <c r="H152" s="0">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="153" spans="1:8">
@@ -5237,10 +5237,10 @@
         </is>
       </c>
       <c r="C153" s="0">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="D153" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E153" s="0">
         <v>2025</v>
@@ -5256,7 +5256,7 @@
         </is>
       </c>
       <c r="H153" s="0">
-        <v>3.26</v>
+        <v>3.19</v>
       </c>
     </row>
     <row r="154" spans="1:8">
@@ -5271,7 +5271,7 @@
         </is>
       </c>
       <c r="C154" s="0">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D154" s="0">
         <v>4</v>
@@ -5290,7 +5290,7 @@
         </is>
       </c>
       <c r="H154" s="0">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="155" spans="1:8">
@@ -5305,7 +5305,7 @@
         </is>
       </c>
       <c r="C155" s="0">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D155" s="0">
         <v>4</v>
@@ -5324,7 +5324,7 @@
         </is>
       </c>
       <c r="H155" s="0">
-        <v>3.12</v>
+        <v>3.26</v>
       </c>
     </row>
     <row r="156" spans="1:8">
@@ -5339,7 +5339,7 @@
         </is>
       </c>
       <c r="C156" s="0">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D156" s="0">
         <v>4</v>
@@ -5358,7 +5358,7 @@
         </is>
       </c>
       <c r="H156" s="0">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="157" spans="1:8">
@@ -5373,7 +5373,7 @@
         </is>
       </c>
       <c r="C157" s="0">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D157" s="0">
         <v>4</v>
@@ -5392,7 +5392,7 @@
         </is>
       </c>
       <c r="H157" s="0">
-        <v>2.94</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="158" spans="1:8">
@@ -5407,7 +5407,7 @@
         </is>
       </c>
       <c r="C158" s="0">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D158" s="0">
         <v>4</v>
@@ -5426,7 +5426,7 @@
         </is>
       </c>
       <c r="H158" s="0">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="159" spans="1:8">
@@ -5441,7 +5441,7 @@
         </is>
       </c>
       <c r="C159" s="0">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D159" s="0">
         <v>4</v>
@@ -5460,7 +5460,7 @@
         </is>
       </c>
       <c r="H159" s="0">
-        <v>2.81</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="160" spans="1:8">
@@ -5475,10 +5475,10 @@
         </is>
       </c>
       <c r="C160" s="0">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="D160" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E160" s="0">
         <v>2025</v>
@@ -5494,7 +5494,7 @@
         </is>
       </c>
       <c r="H160" s="0">
-        <v>1.51</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="161" spans="1:8">
@@ -5509,10 +5509,10 @@
         </is>
       </c>
       <c r="C161" s="0">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="D161" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E161" s="0">
         <v>2025</v>
@@ -5528,7 +5528,7 @@
         </is>
       </c>
       <c r="H161" s="0">
-        <v>3.18</v>
+        <v>2.81</v>
       </c>
     </row>
     <row r="162" spans="1:8">
@@ -5543,7 +5543,7 @@
         </is>
       </c>
       <c r="C162" s="0">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D162" s="0">
         <v>3</v>
@@ -5562,7 +5562,7 @@
         </is>
       </c>
       <c r="H162" s="0">
-        <v>1.6</v>
+        <v>1.51</v>
       </c>
     </row>
     <row r="163" spans="1:8">
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="C163" s="0">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D163" s="0">
         <v>3</v>
@@ -5596,7 +5596,7 @@
         </is>
       </c>
       <c r="H163" s="0">
-        <v>3.58</v>
+        <v>3.18</v>
       </c>
     </row>
     <row r="164" spans="1:8">
@@ -5611,7 +5611,7 @@
         </is>
       </c>
       <c r="C164" s="0">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D164" s="0">
         <v>3</v>
@@ -5630,7 +5630,7 @@
         </is>
       </c>
       <c r="H164" s="0">
-        <v>1.69</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="165" spans="1:8">
@@ -5645,7 +5645,7 @@
         </is>
       </c>
       <c r="C165" s="0">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D165" s="0">
         <v>3</v>
@@ -5664,7 +5664,7 @@
         </is>
       </c>
       <c r="H165" s="0">
-        <v>3.75</v>
+        <v>3.58</v>
       </c>
     </row>
     <row r="166" spans="1:8">
@@ -5679,7 +5679,7 @@
         </is>
       </c>
       <c r="C166" s="0">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D166" s="0">
         <v>3</v>
@@ -5698,7 +5698,7 @@
         </is>
       </c>
       <c r="H166" s="0">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="167" spans="1:8">
@@ -5713,7 +5713,7 @@
         </is>
       </c>
       <c r="C167" s="0">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D167" s="0">
         <v>3</v>
@@ -5732,7 +5732,7 @@
         </is>
       </c>
       <c r="H167" s="0">
-        <v>3.59</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="168" spans="1:8">
@@ -5747,10 +5747,10 @@
         </is>
       </c>
       <c r="C168" s="0">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="D168" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E168" s="0">
         <v>2025</v>
@@ -5766,7 +5766,7 @@
         </is>
       </c>
       <c r="H168" s="0">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="169" spans="1:8">
@@ -5781,10 +5781,10 @@
         </is>
       </c>
       <c r="C169" s="0">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="D169" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E169" s="0">
         <v>2025</v>
@@ -5800,7 +5800,7 @@
         </is>
       </c>
       <c r="H169" s="0">
-        <v>3.66</v>
+        <v>3.59</v>
       </c>
     </row>
     <row r="170" spans="1:8">
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="C170" s="0">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D170" s="0">
         <v>2</v>
@@ -5834,7 +5834,7 @@
         </is>
       </c>
       <c r="H170" s="0">
-        <v>1.87</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="171" spans="1:8">
@@ -5849,7 +5849,7 @@
         </is>
       </c>
       <c r="C171" s="0">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D171" s="0">
         <v>2</v>
@@ -5868,7 +5868,7 @@
         </is>
       </c>
       <c r="H171" s="0">
-        <v>3.71</v>
+        <v>3.66</v>
       </c>
     </row>
     <row r="172" spans="1:8">
@@ -5883,7 +5883,7 @@
         </is>
       </c>
       <c r="C172" s="0">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D172" s="0">
         <v>2</v>
@@ -5902,7 +5902,7 @@
         </is>
       </c>
       <c r="H172" s="0">
-        <v>1.69</v>
+        <v>1.87</v>
       </c>
     </row>
     <row r="173" spans="1:8">
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="C173" s="0">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D173" s="0">
         <v>2</v>
@@ -5936,7 +5936,7 @@
         </is>
       </c>
       <c r="H173" s="0">
-        <v>3.79</v>
+        <v>3.71</v>
       </c>
     </row>
     <row r="174" spans="1:8">
@@ -5951,7 +5951,7 @@
         </is>
       </c>
       <c r="C174" s="0">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D174" s="0">
         <v>2</v>
@@ -5970,7 +5970,7 @@
         </is>
       </c>
       <c r="H174" s="0">
-        <v>1.53</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="175" spans="1:8">
@@ -5985,7 +5985,7 @@
         </is>
       </c>
       <c r="C175" s="0">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D175" s="0">
         <v>2</v>
@@ -6004,7 +6004,7 @@
         </is>
       </c>
       <c r="H175" s="0">
-        <v>3.42</v>
+        <v>3.79</v>
       </c>
     </row>
     <row r="176" spans="1:8">
@@ -6019,10 +6019,10 @@
         </is>
       </c>
       <c r="C176" s="0">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="D176" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E176" s="0">
         <v>2025</v>
@@ -6038,7 +6038,7 @@
         </is>
       </c>
       <c r="H176" s="0">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
     </row>
     <row r="177" spans="1:8">
@@ -6053,10 +6053,10 @@
         </is>
       </c>
       <c r="C177" s="0">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="D177" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E177" s="0">
         <v>2025</v>
@@ -6072,7 +6072,7 @@
         </is>
       </c>
       <c r="H177" s="0">
-        <v>3.37</v>
+        <v>3.42</v>
       </c>
     </row>
     <row r="178" spans="1:8">
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="C178" s="0">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="D178" s="0">
         <v>1</v>
@@ -6106,7 +6106,7 @@
         </is>
       </c>
       <c r="H178" s="0">
-        <v>1.74</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="179" spans="1:8">
@@ -6121,7 +6121,7 @@
         </is>
       </c>
       <c r="C179" s="0">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="D179" s="0">
         <v>1</v>
@@ -6140,7 +6140,7 @@
         </is>
       </c>
       <c r="H179" s="0">
-        <v>3.6</v>
+        <v>3.37</v>
       </c>
     </row>
     <row r="180" spans="1:8">
@@ -6155,7 +6155,7 @@
         </is>
       </c>
       <c r="C180" s="0">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D180" s="0">
         <v>1</v>
@@ -6174,7 +6174,7 @@
         </is>
       </c>
       <c r="H180" s="0">
-        <v>1.88</v>
+        <v>1.74</v>
       </c>
     </row>
     <row r="181" spans="1:8">
@@ -6189,7 +6189,7 @@
         </is>
       </c>
       <c r="C181" s="0">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D181" s="0">
         <v>1</v>
@@ -6208,7 +6208,7 @@
         </is>
       </c>
       <c r="H181" s="0">
-        <v>3.68</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="182" spans="1:8">
@@ -6223,7 +6223,7 @@
         </is>
       </c>
       <c r="C182" s="0">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D182" s="0">
         <v>1</v>
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="H182" s="0">
-        <v>1.96</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="183" spans="1:8">
@@ -6257,7 +6257,7 @@
         </is>
       </c>
       <c r="C183" s="0">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D183" s="0">
         <v>1</v>
@@ -6276,7 +6276,7 @@
         </is>
       </c>
       <c r="H183" s="0">
-        <v>3.25</v>
+        <v>3.68</v>
       </c>
     </row>
     <row r="184" spans="1:8">
@@ -6291,7 +6291,7 @@
         </is>
       </c>
       <c r="C184" s="0">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D184" s="0">
         <v>1</v>
@@ -6310,7 +6310,7 @@
         </is>
       </c>
       <c r="H184" s="0">
-        <v>2.33</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="185" spans="1:8">
@@ -6325,7 +6325,7 @@
         </is>
       </c>
       <c r="C185" s="0">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D185" s="0">
         <v>1</v>
@@ -6344,7 +6344,7 @@
         </is>
       </c>
       <c r="H185" s="0">
-        <v>3.02</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="186" spans="1:8">
@@ -6359,13 +6359,13 @@
         </is>
       </c>
       <c r="C186" s="0">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="D186" s="0">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E186" s="0">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="F186" s="0" t="inlineStr">
         <is>
@@ -6393,13 +6393,13 @@
         </is>
       </c>
       <c r="C187" s="0">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="D187" s="0">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E187" s="0">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="F187" s="0" t="inlineStr">
         <is>
@@ -6427,7 +6427,7 @@
         </is>
       </c>
       <c r="C188" s="0">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="D188" s="0">
         <v>12</v>
@@ -6446,7 +6446,7 @@
         </is>
       </c>
       <c r="H188" s="0">
-        <v>2.49</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="189" spans="1:8">
@@ -6461,7 +6461,7 @@
         </is>
       </c>
       <c r="C189" s="0">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="D189" s="0">
         <v>12</v>
@@ -6480,7 +6480,7 @@
         </is>
       </c>
       <c r="H189" s="0">
-        <v>3</v>
+        <v>3.02</v>
       </c>
     </row>
     <row r="190" spans="1:8">
@@ -6495,7 +6495,7 @@
         </is>
       </c>
       <c r="C190" s="0">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D190" s="0">
         <v>12</v>
@@ -6514,7 +6514,7 @@
         </is>
       </c>
       <c r="H190" s="0">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="191" spans="1:8">
@@ -6529,7 +6529,7 @@
         </is>
       </c>
       <c r="C191" s="0">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D191" s="0">
         <v>12</v>
@@ -6548,7 +6548,7 @@
         </is>
       </c>
       <c r="H191" s="0">
-        <v>3.04</v>
+        <v>3</v>
       </c>
     </row>
     <row r="192" spans="1:8">
@@ -6563,7 +6563,7 @@
         </is>
       </c>
       <c r="C192" s="0">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D192" s="0">
         <v>12</v>
@@ -6582,7 +6582,7 @@
         </is>
       </c>
       <c r="H192" s="0">
-        <v>2.61</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="193" spans="1:8">
@@ -6597,7 +6597,7 @@
         </is>
       </c>
       <c r="C193" s="0">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D193" s="0">
         <v>12</v>
@@ -6616,7 +6616,7 @@
         </is>
       </c>
       <c r="H193" s="0">
-        <v>3.06</v>
+        <v>3.04</v>
       </c>
     </row>
     <row r="194" spans="1:8">
@@ -6631,10 +6631,10 @@
         </is>
       </c>
       <c r="C194" s="0">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="D194" s="0">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E194" s="0">
         <v>2024</v>
@@ -6650,7 +6650,7 @@
         </is>
       </c>
       <c r="H194" s="0">
-        <v>2.63</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="195" spans="1:8">
@@ -6665,10 +6665,10 @@
         </is>
       </c>
       <c r="C195" s="0">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="D195" s="0">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E195" s="0">
         <v>2024</v>
@@ -6684,7 +6684,7 @@
         </is>
       </c>
       <c r="H195" s="0">
-        <v>3.21</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="196" spans="1:8">
@@ -6699,7 +6699,7 @@
         </is>
       </c>
       <c r="C196" s="0">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D196" s="0">
         <v>11</v>
@@ -6718,7 +6718,7 @@
         </is>
       </c>
       <c r="H196" s="0">
-        <v>2.58</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="197" spans="1:8">
@@ -6733,7 +6733,7 @@
         </is>
       </c>
       <c r="C197" s="0">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D197" s="0">
         <v>11</v>
@@ -6752,7 +6752,7 @@
         </is>
       </c>
       <c r="H197" s="0">
-        <v>3.28</v>
+        <v>3.21</v>
       </c>
     </row>
     <row r="198" spans="1:8">
@@ -6767,7 +6767,7 @@
         </is>
       </c>
       <c r="C198" s="0">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D198" s="0">
         <v>11</v>
@@ -6786,7 +6786,7 @@
         </is>
       </c>
       <c r="H198" s="0">
-        <v>2.22</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="199" spans="1:8">
@@ -6801,7 +6801,7 @@
         </is>
       </c>
       <c r="C199" s="0">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D199" s="0">
         <v>11</v>
@@ -6820,7 +6820,7 @@
         </is>
       </c>
       <c r="H199" s="0">
-        <v>2.8</v>
+        <v>3.28</v>
       </c>
     </row>
     <row r="200" spans="1:8">
@@ -6835,7 +6835,7 @@
         </is>
       </c>
       <c r="C200" s="0">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D200" s="0">
         <v>11</v>
@@ -6869,7 +6869,7 @@
         </is>
       </c>
       <c r="C201" s="0">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D201" s="0">
         <v>11</v>
@@ -6888,7 +6888,7 @@
         </is>
       </c>
       <c r="H201" s="0">
-        <v>2.61</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="202" spans="1:8">
@@ -6903,10 +6903,10 @@
         </is>
       </c>
       <c r="C202" s="0">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="D202" s="0">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E202" s="0">
         <v>2024</v>
@@ -6922,7 +6922,7 @@
         </is>
       </c>
       <c r="H202" s="0">
-        <v>2.45</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="203" spans="1:8">
@@ -6937,10 +6937,10 @@
         </is>
       </c>
       <c r="C203" s="0">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="D203" s="0">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E203" s="0">
         <v>2024</v>
@@ -6956,7 +6956,7 @@
         </is>
       </c>
       <c r="H203" s="0">
-        <v>2.79</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="204" spans="1:8">
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="C204" s="0">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D204" s="0">
         <v>10</v>
@@ -6990,7 +6990,7 @@
         </is>
       </c>
       <c r="H204" s="0">
-        <v>2.82</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="205" spans="1:8">
@@ -7005,7 +7005,7 @@
         </is>
       </c>
       <c r="C205" s="0">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D205" s="0">
         <v>10</v>
@@ -7024,7 +7024,7 @@
         </is>
       </c>
       <c r="H205" s="0">
-        <v>3</v>
+        <v>2.79</v>
       </c>
     </row>
     <row r="206" spans="1:8">
@@ -7039,7 +7039,7 @@
         </is>
       </c>
       <c r="C206" s="0">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="D206" s="0">
         <v>10</v>
@@ -7058,7 +7058,7 @@
         </is>
       </c>
       <c r="H206" s="0">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
     </row>
     <row r="207" spans="1:8">
@@ -7073,7 +7073,7 @@
         </is>
       </c>
       <c r="C207" s="0">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="D207" s="0">
         <v>10</v>
@@ -7092,7 +7092,7 @@
         </is>
       </c>
       <c r="H207" s="0">
-        <v>3.11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="208" spans="1:8">
@@ -7107,7 +7107,7 @@
         </is>
       </c>
       <c r="C208" s="0">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D208" s="0">
         <v>10</v>
@@ -7126,7 +7126,7 @@
         </is>
       </c>
       <c r="H208" s="0">
-        <v>2.99</v>
+        <v>2.84</v>
       </c>
     </row>
     <row r="209" spans="1:8">
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="C209" s="0">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D209" s="0">
         <v>10</v>
@@ -7160,7 +7160,7 @@
         </is>
       </c>
       <c r="H209" s="0">
-        <v>3.04</v>
+        <v>3.11</v>
       </c>
     </row>
     <row r="210" spans="1:8">
@@ -7175,10 +7175,10 @@
         </is>
       </c>
       <c r="C210" s="0">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="D210" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E210" s="0">
         <v>2024</v>
@@ -7194,7 +7194,7 @@
         </is>
       </c>
       <c r="H210" s="0">
-        <v>3.06</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="211" spans="1:8">
@@ -7209,10 +7209,10 @@
         </is>
       </c>
       <c r="C211" s="0">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="D211" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E211" s="0">
         <v>2024</v>
@@ -7228,7 +7228,7 @@
         </is>
       </c>
       <c r="H211" s="0">
-        <v>3.27</v>
+        <v>3.04</v>
       </c>
     </row>
     <row r="212" spans="1:8">
@@ -7243,7 +7243,7 @@
         </is>
       </c>
       <c r="C212" s="0">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D212" s="0">
         <v>9</v>
@@ -7262,7 +7262,7 @@
         </is>
       </c>
       <c r="H212" s="0">
-        <v>3.1</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="213" spans="1:8">
@@ -7277,7 +7277,7 @@
         </is>
       </c>
       <c r="C213" s="0">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D213" s="0">
         <v>9</v>
@@ -7296,7 +7296,7 @@
         </is>
       </c>
       <c r="H213" s="0">
-        <v>3.45</v>
+        <v>3.27</v>
       </c>
     </row>
     <row r="214" spans="1:8">
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="C214" s="0">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D214" s="0">
         <v>9</v>
@@ -7330,7 +7330,7 @@
         </is>
       </c>
       <c r="H214" s="0">
-        <v>2.67</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="215" spans="1:8">
@@ -7345,7 +7345,7 @@
         </is>
       </c>
       <c r="C215" s="0">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D215" s="0">
         <v>9</v>
@@ -7364,7 +7364,7 @@
         </is>
       </c>
       <c r="H215" s="0">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="216" spans="1:8">
@@ -7379,7 +7379,7 @@
         </is>
       </c>
       <c r="C216" s="0">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D216" s="0">
         <v>9</v>
@@ -7398,7 +7398,7 @@
         </is>
       </c>
       <c r="H216" s="0">
-        <v>2.42</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="217" spans="1:8">
@@ -7413,7 +7413,7 @@
         </is>
       </c>
       <c r="C217" s="0">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D217" s="0">
         <v>9</v>
@@ -7432,7 +7432,7 @@
         </is>
       </c>
       <c r="H217" s="0">
-        <v>3.94</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="218" spans="1:8">
@@ -7447,10 +7447,10 @@
         </is>
       </c>
       <c r="C218" s="0">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="D218" s="0">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E218" s="0">
         <v>2024</v>
@@ -7466,7 +7466,7 @@
         </is>
       </c>
       <c r="H218" s="0">
-        <v>2.6</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="219" spans="1:8">
@@ -7481,10 +7481,10 @@
         </is>
       </c>
       <c r="C219" s="0">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="D219" s="0">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E219" s="0">
         <v>2024</v>
@@ -7500,7 +7500,7 @@
         </is>
       </c>
       <c r="H219" s="0">
-        <v>4.29</v>
+        <v>3.94</v>
       </c>
     </row>
     <row r="220" spans="1:8">
@@ -7515,7 +7515,7 @@
         </is>
       </c>
       <c r="C220" s="0">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D220" s="0">
         <v>8</v>
@@ -7534,7 +7534,7 @@
         </is>
       </c>
       <c r="H220" s="0">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="221" spans="1:8">
@@ -7549,7 +7549,7 @@
         </is>
       </c>
       <c r="C221" s="0">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D221" s="0">
         <v>8</v>
@@ -7568,7 +7568,7 @@
         </is>
       </c>
       <c r="H221" s="0">
-        <v>4.44</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="222" spans="1:8">
@@ -7583,7 +7583,7 @@
         </is>
       </c>
       <c r="C222" s="0">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="D222" s="0">
         <v>8</v>
@@ -7598,11 +7598,11 @@
       </c>
       <c r="G222" s="0" t="inlineStr">
         <is>
-          <t>caixa de 22 Kg</t>
+          <t>quilograma</t>
         </is>
       </c>
       <c r="H222" s="0">
-        <v>2.82</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="223" spans="1:8">
@@ -7617,7 +7617,7 @@
         </is>
       </c>
       <c r="C223" s="0">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="D223" s="0">
         <v>8</v>
@@ -7632,11 +7632,11 @@
       </c>
       <c r="G223" s="0" t="inlineStr">
         <is>
-          <t>Caixa 20 Kg</t>
+          <t>quilograma</t>
         </is>
       </c>
       <c r="H223" s="0">
-        <v>4.99</v>
+        <v>4.44</v>
       </c>
     </row>
     <row r="224" spans="1:8">
@@ -7651,7 +7651,7 @@
         </is>
       </c>
       <c r="C224" s="0">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D224" s="0">
         <v>8</v>
@@ -7670,7 +7670,7 @@
         </is>
       </c>
       <c r="H224" s="0">
-        <v>2.74</v>
+        <v>2.82</v>
       </c>
     </row>
     <row r="225" spans="1:8">
@@ -7685,7 +7685,7 @@
         </is>
       </c>
       <c r="C225" s="0">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D225" s="0">
         <v>8</v>
@@ -7704,7 +7704,7 @@
         </is>
       </c>
       <c r="H225" s="0">
-        <v>5.2</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="226" spans="1:8">
@@ -7719,7 +7719,7 @@
         </is>
       </c>
       <c r="C226" s="0">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D226" s="0">
         <v>8</v>
@@ -7738,7 +7738,7 @@
         </is>
       </c>
       <c r="H226" s="0">
-        <v>2.49</v>
+        <v>2.74</v>
       </c>
     </row>
     <row r="227" spans="1:8">
@@ -7753,7 +7753,7 @@
         </is>
       </c>
       <c r="C227" s="0">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D227" s="0">
         <v>8</v>
@@ -7772,7 +7772,7 @@
         </is>
       </c>
       <c r="H227" s="0">
-        <v>4.93</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="228" spans="1:8">
@@ -7787,10 +7787,10 @@
         </is>
       </c>
       <c r="C228" s="0">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="D228" s="0">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E228" s="0">
         <v>2024</v>
@@ -7806,7 +7806,7 @@
         </is>
       </c>
       <c r="H228" s="0">
-        <v>2.04</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="229" spans="1:8">
@@ -7821,10 +7821,10 @@
         </is>
       </c>
       <c r="C229" s="0">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="D229" s="0">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E229" s="0">
         <v>2024</v>
@@ -7840,7 +7840,7 @@
         </is>
       </c>
       <c r="H229" s="0">
-        <v>3.76</v>
+        <v>4.93</v>
       </c>
     </row>
     <row r="230" spans="1:8">
@@ -7855,7 +7855,7 @@
         </is>
       </c>
       <c r="C230" s="0">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="D230" s="0">
         <v>7</v>
@@ -7874,7 +7874,7 @@
         </is>
       </c>
       <c r="H230" s="0">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="231" spans="1:8">
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="C231" s="0">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="D231" s="0">
         <v>7</v>
@@ -7908,7 +7908,7 @@
         </is>
       </c>
       <c r="H231" s="0">
-        <v>3.16</v>
+        <v>3.76</v>
       </c>
     </row>
     <row r="232" spans="1:8">
@@ -7923,7 +7923,7 @@
         </is>
       </c>
       <c r="C232" s="0">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D232" s="0">
         <v>7</v>
@@ -7942,7 +7942,7 @@
         </is>
       </c>
       <c r="H232" s="0">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
     </row>
     <row r="233" spans="1:8">
@@ -7957,7 +7957,7 @@
         </is>
       </c>
       <c r="C233" s="0">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D233" s="0">
         <v>7</v>
@@ -7976,7 +7976,7 @@
         </is>
       </c>
       <c r="H233" s="0">
-        <v>2.85</v>
+        <v>3.16</v>
       </c>
     </row>
     <row r="234" spans="1:8">
@@ -7991,7 +7991,7 @@
         </is>
       </c>
       <c r="C234" s="0">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D234" s="0">
         <v>7</v>
@@ -8025,7 +8025,7 @@
         </is>
       </c>
       <c r="C235" s="0">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D235" s="0">
         <v>7</v>
@@ -8044,7 +8044,7 @@
         </is>
       </c>
       <c r="H235" s="0">
-        <v>2.66</v>
+        <v>2.85</v>
       </c>
     </row>
     <row r="236" spans="1:8">
@@ -8059,10 +8059,10 @@
         </is>
       </c>
       <c r="C236" s="0">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="D236" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E236" s="0">
         <v>2024</v>
@@ -8074,11 +8074,11 @@
       </c>
       <c r="G236" s="0" t="inlineStr">
         <is>
-          <t>quilograma</t>
+          <t>caixa de 22 Kg</t>
         </is>
       </c>
       <c r="H236" s="0">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="237" spans="1:8">
@@ -8093,10 +8093,10 @@
         </is>
       </c>
       <c r="C237" s="0">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="D237" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E237" s="0">
         <v>2024</v>
@@ -8108,11 +8108,11 @@
       </c>
       <c r="G237" s="0" t="inlineStr">
         <is>
-          <t>quilograma</t>
+          <t>Caixa 20 Kg</t>
         </is>
       </c>
       <c r="H237" s="0">
-        <v>2.32</v>
+        <v>2.66</v>
       </c>
     </row>
     <row r="238" spans="1:8">
@@ -8127,7 +8127,7 @@
         </is>
       </c>
       <c r="C238" s="0">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D238" s="0">
         <v>6</v>
@@ -8146,7 +8146,7 @@
         </is>
       </c>
       <c r="H238" s="0">
-        <v>1.97</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="239" spans="1:8">
@@ -8161,7 +8161,7 @@
         </is>
       </c>
       <c r="C239" s="0">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D239" s="0">
         <v>6</v>
@@ -8180,7 +8180,7 @@
         </is>
       </c>
       <c r="H239" s="0">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="240" spans="1:8">
@@ -8195,7 +8195,7 @@
         </is>
       </c>
       <c r="C240" s="0">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D240" s="0">
         <v>6</v>
@@ -8214,7 +8214,7 @@
         </is>
       </c>
       <c r="H240" s="0">
-        <v>1.65</v>
+        <v>1.97</v>
       </c>
     </row>
     <row r="241" spans="1:8">
@@ -8229,7 +8229,7 @@
         </is>
       </c>
       <c r="C241" s="0">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D241" s="0">
         <v>6</v>
@@ -8248,7 +8248,7 @@
         </is>
       </c>
       <c r="H241" s="0">
-        <v>2.49</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="242" spans="1:8">
@@ -8263,7 +8263,7 @@
         </is>
       </c>
       <c r="C242" s="0">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D242" s="0">
         <v>6</v>
@@ -8282,7 +8282,7 @@
         </is>
       </c>
       <c r="H242" s="0">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="243" spans="1:8">
@@ -8297,7 +8297,7 @@
         </is>
       </c>
       <c r="C243" s="0">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D243" s="0">
         <v>6</v>
@@ -8316,7 +8316,7 @@
         </is>
       </c>
       <c r="H243" s="0">
-        <v>2.73</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="244" spans="1:8">
@@ -8331,10 +8331,10 @@
         </is>
       </c>
       <c r="C244" s="0">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="D244" s="0">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E244" s="0">
         <v>2024</v>
@@ -8350,7 +8350,7 @@
         </is>
       </c>
       <c r="H244" s="0">
-        <v>1.17</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="245" spans="1:8">
@@ -8365,10 +8365,10 @@
         </is>
       </c>
       <c r="C245" s="0">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="D245" s="0">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E245" s="0">
         <v>2024</v>
@@ -8384,7 +8384,7 @@
         </is>
       </c>
       <c r="H245" s="0">
-        <v>3.05</v>
+        <v>2.73</v>
       </c>
     </row>
     <row r="246" spans="1:8">
@@ -8399,7 +8399,7 @@
         </is>
       </c>
       <c r="C246" s="0">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="D246" s="0">
         <v>5</v>
@@ -8418,7 +8418,7 @@
         </is>
       </c>
       <c r="H246" s="0">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="247" spans="1:8">
@@ -8433,7 +8433,7 @@
         </is>
       </c>
       <c r="C247" s="0">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="D247" s="0">
         <v>5</v>
@@ -8452,7 +8452,7 @@
         </is>
       </c>
       <c r="H247" s="0">
-        <v>2.73</v>
+        <v>3.05</v>
       </c>
     </row>
     <row r="248" spans="1:8">
@@ -8467,7 +8467,7 @@
         </is>
       </c>
       <c r="C248" s="0">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D248" s="0">
         <v>5</v>
@@ -8501,7 +8501,7 @@
         </is>
       </c>
       <c r="C249" s="0">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D249" s="0">
         <v>5</v>
@@ -8520,7 +8520,7 @@
         </is>
       </c>
       <c r="H249" s="0">
-        <v>2.85</v>
+        <v>2.73</v>
       </c>
     </row>
     <row r="250" spans="1:8">
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="C250" s="0">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D250" s="0">
         <v>5</v>
@@ -8554,7 +8554,7 @@
         </is>
       </c>
       <c r="H250" s="0">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="251" spans="1:8">
@@ -8569,7 +8569,7 @@
         </is>
       </c>
       <c r="C251" s="0">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D251" s="0">
         <v>5</v>
@@ -8588,7 +8588,7 @@
         </is>
       </c>
       <c r="H251" s="0">
-        <v>2.69</v>
+        <v>2.85</v>
       </c>
     </row>
     <row r="252" spans="1:8">
@@ -8603,7 +8603,7 @@
         </is>
       </c>
       <c r="C252" s="0">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D252" s="0">
         <v>5</v>
@@ -8622,7 +8622,7 @@
         </is>
       </c>
       <c r="H252" s="0">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="253" spans="1:8">
@@ -8637,7 +8637,7 @@
         </is>
       </c>
       <c r="C253" s="0">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D253" s="0">
         <v>5</v>
@@ -8656,7 +8656,7 @@
         </is>
       </c>
       <c r="H253" s="0">
-        <v>2.65</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="254" spans="1:8">
@@ -8671,10 +8671,10 @@
         </is>
       </c>
       <c r="C254" s="0">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="D254" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E254" s="0">
         <v>2024</v>
@@ -8690,7 +8690,7 @@
         </is>
       </c>
       <c r="H254" s="0">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
     </row>
     <row r="255" spans="1:8">
@@ -8705,10 +8705,10 @@
         </is>
       </c>
       <c r="C255" s="0">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="D255" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E255" s="0">
         <v>2024</v>
@@ -8724,7 +8724,7 @@
         </is>
       </c>
       <c r="H255" s="0">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
     </row>
     <row r="256" spans="1:8">
@@ -8739,7 +8739,7 @@
         </is>
       </c>
       <c r="C256" s="0">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="D256" s="0">
         <v>4</v>
@@ -8758,7 +8758,7 @@
         </is>
       </c>
       <c r="H256" s="0">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
     </row>
     <row r="257" spans="1:8">
@@ -8773,7 +8773,7 @@
         </is>
       </c>
       <c r="C257" s="0">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="D257" s="0">
         <v>4</v>
@@ -8792,7 +8792,7 @@
         </is>
       </c>
       <c r="H257" s="0">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="258" spans="1:8">
@@ -8807,7 +8807,7 @@
         </is>
       </c>
       <c r="C258" s="0">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D258" s="0">
         <v>4</v>
@@ -8826,7 +8826,7 @@
         </is>
       </c>
       <c r="H258" s="0">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="259" spans="1:8">
@@ -8841,7 +8841,7 @@
         </is>
       </c>
       <c r="C259" s="0">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D259" s="0">
         <v>4</v>
@@ -8860,7 +8860,7 @@
         </is>
       </c>
       <c r="H259" s="0">
-        <v>4.86</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="260" spans="1:8">
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="C260" s="0">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D260" s="0">
         <v>4</v>
@@ -8894,7 +8894,7 @@
         </is>
       </c>
       <c r="H260" s="0">
-        <v>1.54</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="261" spans="1:8">
@@ -8909,7 +8909,7 @@
         </is>
       </c>
       <c r="C261" s="0">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D261" s="0">
         <v>4</v>
@@ -8928,7 +8928,7 @@
         </is>
       </c>
       <c r="H261" s="0">
-        <v>6.23</v>
+        <v>4.86</v>
       </c>
     </row>
     <row r="262" spans="1:8">
@@ -8943,10 +8943,10 @@
         </is>
       </c>
       <c r="C262" s="0">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="D262" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E262" s="0">
         <v>2024</v>
@@ -8962,7 +8962,7 @@
         </is>
       </c>
       <c r="H262" s="0">
-        <v>2.13</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="263" spans="1:8">
@@ -8977,10 +8977,10 @@
         </is>
       </c>
       <c r="C263" s="0">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="D263" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E263" s="0">
         <v>2024</v>
@@ -8996,7 +8996,7 @@
         </is>
       </c>
       <c r="H263" s="0">
-        <v>6.4</v>
+        <v>6.23</v>
       </c>
     </row>
     <row r="264" spans="1:8">
@@ -9011,7 +9011,7 @@
         </is>
       </c>
       <c r="C264" s="0">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D264" s="0">
         <v>3</v>
@@ -9030,7 +9030,7 @@
         </is>
       </c>
       <c r="H264" s="0">
-        <v>2.49</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="265" spans="1:8">
@@ -9045,7 +9045,7 @@
         </is>
       </c>
       <c r="C265" s="0">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D265" s="0">
         <v>3</v>
@@ -9064,7 +9064,7 @@
         </is>
       </c>
       <c r="H265" s="0">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="266" spans="1:8">
@@ -9079,7 +9079,7 @@
         </is>
       </c>
       <c r="C266" s="0">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="D266" s="0">
         <v>3</v>
@@ -9098,7 +9098,7 @@
         </is>
       </c>
       <c r="H266" s="0">
-        <v>2.64</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="267" spans="1:8">
@@ -9113,7 +9113,7 @@
         </is>
       </c>
       <c r="C267" s="0">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="D267" s="0">
         <v>3</v>
@@ -9132,13 +9132,13 @@
         </is>
       </c>
       <c r="H267" s="0">
-        <v>6.46</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="268" spans="1:8">
       <c r="A268" s="0" t="inlineStr">
         <is>
-          <t>Prata anã primeira - produtor</t>
+          <t>Nanica primeira - produtor</t>
         </is>
       </c>
       <c r="B268" s="0" t="inlineStr">
@@ -9147,7 +9147,7 @@
         </is>
       </c>
       <c r="C268" s="0">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D268" s="0">
         <v>3</v>
@@ -9166,13 +9166,13 @@
         </is>
       </c>
       <c r="H268" s="0">
-        <v>6.39</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="269" spans="1:8">
       <c r="A269" s="0" t="inlineStr">
         <is>
-          <t>Nanica primeira - produtor</t>
+          <t>Prata anã primeira - produtor</t>
         </is>
       </c>
       <c r="B269" s="0" t="inlineStr">
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="C269" s="0">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="D269" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E269" s="0">
         <v>2024</v>
@@ -9200,7 +9200,7 @@
         </is>
       </c>
       <c r="H269" s="0">
-        <v>2.91</v>
+        <v>6.46</v>
       </c>
     </row>
     <row r="270" spans="1:8">
@@ -9215,10 +9215,10 @@
         </is>
       </c>
       <c r="C270" s="0">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="D270" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E270" s="0">
         <v>2024</v>
@@ -9234,7 +9234,7 @@
         </is>
       </c>
       <c r="H270" s="0">
-        <v>6.31</v>
+        <v>6.39</v>
       </c>
     </row>
     <row r="271" spans="1:8">
@@ -9249,7 +9249,7 @@
         </is>
       </c>
       <c r="C271" s="0">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D271" s="0">
         <v>2</v>
@@ -9268,7 +9268,7 @@
         </is>
       </c>
       <c r="H271" s="0">
-        <v>3.79</v>
+        <v>2.91</v>
       </c>
     </row>
     <row r="272" spans="1:8">
@@ -9283,7 +9283,7 @@
         </is>
       </c>
       <c r="C272" s="0">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D272" s="0">
         <v>2</v>
@@ -9302,7 +9302,7 @@
         </is>
       </c>
       <c r="H272" s="0">
-        <v>6.26</v>
+        <v>6.31</v>
       </c>
     </row>
     <row r="273" spans="1:8">
@@ -9317,7 +9317,7 @@
         </is>
       </c>
       <c r="C273" s="0">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="D273" s="0">
         <v>2</v>
@@ -9336,7 +9336,7 @@
         </is>
       </c>
       <c r="H273" s="0">
-        <v>4.11</v>
+        <v>3.79</v>
       </c>
     </row>
     <row r="274" spans="1:8">
@@ -9351,7 +9351,7 @@
         </is>
       </c>
       <c r="C274" s="0">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="D274" s="0">
         <v>2</v>
@@ -9370,7 +9370,7 @@
         </is>
       </c>
       <c r="H274" s="0">
-        <v>6.16</v>
+        <v>6.26</v>
       </c>
     </row>
     <row r="275" spans="1:8">
@@ -9385,7 +9385,7 @@
         </is>
       </c>
       <c r="C275" s="0">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D275" s="0">
         <v>2</v>
@@ -9404,7 +9404,7 @@
         </is>
       </c>
       <c r="H275" s="0">
-        <v>4.05</v>
+        <v>4.11</v>
       </c>
     </row>
     <row r="276" spans="1:8">
@@ -9419,7 +9419,7 @@
         </is>
       </c>
       <c r="C276" s="0">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D276" s="0">
         <v>2</v>
@@ -9438,7 +9438,7 @@
         </is>
       </c>
       <c r="H276" s="0">
-        <v>5.88</v>
+        <v>6.16</v>
       </c>
     </row>
     <row r="277" spans="1:8">
@@ -9453,7 +9453,7 @@
         </is>
       </c>
       <c r="C277" s="0">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D277" s="0">
         <v>2</v>
@@ -9472,7 +9472,7 @@
         </is>
       </c>
       <c r="H277" s="0">
-        <v>2.42</v>
+        <v>4.05</v>
       </c>
     </row>
     <row r="278" spans="1:8">
@@ -9487,7 +9487,7 @@
         </is>
       </c>
       <c r="C278" s="0">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D278" s="0">
         <v>2</v>
@@ -9506,7 +9506,7 @@
         </is>
       </c>
       <c r="H278" s="0">
-        <v>5.61</v>
+        <v>5.88</v>
       </c>
     </row>
     <row r="279" spans="1:8">
@@ -9521,10 +9521,10 @@
         </is>
       </c>
       <c r="C279" s="0">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="D279" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E279" s="0">
         <v>2024</v>
@@ -9540,7 +9540,7 @@
         </is>
       </c>
       <c r="H279" s="0">
-        <v>2.21</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="280" spans="1:8">
@@ -9555,10 +9555,10 @@
         </is>
       </c>
       <c r="C280" s="0">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="D280" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E280" s="0">
         <v>2024</v>
@@ -9574,7 +9574,7 @@
         </is>
       </c>
       <c r="H280" s="0">
-        <v>5.47</v>
+        <v>5.61</v>
       </c>
     </row>
     <row r="281" spans="1:8">
@@ -9589,7 +9589,7 @@
         </is>
       </c>
       <c r="C281" s="0">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="D281" s="0">
         <v>1</v>
@@ -9608,7 +9608,7 @@
         </is>
       </c>
       <c r="H281" s="0">
-        <v>2.12</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="282" spans="1:8">
@@ -9623,7 +9623,7 @@
         </is>
       </c>
       <c r="C282" s="0">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="D282" s="0">
         <v>1</v>
@@ -9642,7 +9642,7 @@
         </is>
       </c>
       <c r="H282" s="0">
-        <v>5.5</v>
+        <v>5.47</v>
       </c>
     </row>
     <row r="283" spans="1:8">
@@ -9657,7 +9657,7 @@
         </is>
       </c>
       <c r="C283" s="0">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D283" s="0">
         <v>1</v>
@@ -9676,7 +9676,7 @@
         </is>
       </c>
       <c r="H283" s="0">
-        <v>2.4</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="284" spans="1:8">
@@ -9691,7 +9691,7 @@
         </is>
       </c>
       <c r="C284" s="0">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D284" s="0">
         <v>1</v>
@@ -9710,7 +9710,7 @@
         </is>
       </c>
       <c r="H284" s="0">
-        <v>5.46</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="285" spans="1:8">
@@ -9725,7 +9725,7 @@
         </is>
       </c>
       <c r="C285" s="0">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D285" s="0">
         <v>1</v>
@@ -9744,13 +9744,13 @@
         </is>
       </c>
       <c r="H285" s="0">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="286" spans="1:8">
       <c r="A286" s="0" t="inlineStr">
         <is>
-          <t>Nanica primeira - produtor</t>
+          <t>Prata anã primeira - produtor</t>
         </is>
       </c>
       <c r="B286" s="0" t="inlineStr">
@@ -9759,7 +9759,7 @@
         </is>
       </c>
       <c r="C286" s="0">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D286" s="0">
         <v>1</v>
@@ -9778,13 +9778,13 @@
         </is>
       </c>
       <c r="H286" s="0">
-        <v>2.42</v>
+        <v>5.46</v>
       </c>
     </row>
     <row r="287" spans="1:8">
       <c r="A287" s="0" t="inlineStr">
         <is>
-          <t>Prata anã primeira - produtor</t>
+          <t>Nanica primeira - produtor</t>
         </is>
       </c>
       <c r="B287" s="0" t="inlineStr">
@@ -9812,13 +9812,13 @@
         </is>
       </c>
       <c r="H287" s="0">
-        <v>5.47</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="288" spans="1:8">
       <c r="A288" s="0" t="inlineStr">
         <is>
-          <t>Prata anã primeira - produtor</t>
+          <t>Nanica primeira - produtor</t>
         </is>
       </c>
       <c r="B288" s="0" t="inlineStr">
@@ -9846,13 +9846,13 @@
         </is>
       </c>
       <c r="H288" s="0">
-        <v>5.47</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="289" spans="1:8">
       <c r="A289" s="0" t="inlineStr">
         <is>
-          <t>Nanica primeira - produtor</t>
+          <t>Prata anã primeira - produtor</t>
         </is>
       </c>
       <c r="B289" s="0" t="inlineStr">
@@ -9861,13 +9861,13 @@
         </is>
       </c>
       <c r="C289" s="0">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="D289" s="0">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E289" s="0">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F289" s="0" t="inlineStr">
         <is>
@@ -9880,7 +9880,7 @@
         </is>
       </c>
       <c r="H289" s="0">
-        <v>2.43</v>
+        <v>5.47</v>
       </c>
     </row>
     <row r="290" spans="1:8">
@@ -9895,13 +9895,13 @@
         </is>
       </c>
       <c r="C290" s="0">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="D290" s="0">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E290" s="0">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F290" s="0" t="inlineStr">
         <is>
@@ -9914,7 +9914,7 @@
         </is>
       </c>
       <c r="H290" s="0">
-        <v>5.5</v>
+        <v>5.47</v>
       </c>
     </row>
     <row r="291" spans="1:8">
@@ -9929,7 +9929,7 @@
         </is>
       </c>
       <c r="C291" s="0">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D291" s="0">
         <v>12</v>
@@ -9948,7 +9948,7 @@
         </is>
       </c>
       <c r="H291" s="0">
-        <v>2.36</v>
+        <v>2.43</v>
       </c>
     </row>
     <row r="292" spans="1:8">
@@ -9963,7 +9963,7 @@
         </is>
       </c>
       <c r="C292" s="0">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D292" s="0">
         <v>12</v>
@@ -9982,7 +9982,7 @@
         </is>
       </c>
       <c r="H292" s="0">
-        <v>5.44</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="293" spans="1:8">
@@ -9997,7 +9997,7 @@
         </is>
       </c>
       <c r="C293" s="0">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="D293" s="0">
         <v>12</v>
@@ -10016,7 +10016,7 @@
         </is>
       </c>
       <c r="H293" s="0">
-        <v>2.21</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="294" spans="1:8">
@@ -10031,7 +10031,7 @@
         </is>
       </c>
       <c r="C294" s="0">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="D294" s="0">
         <v>12</v>
@@ -10050,7 +10050,7 @@
         </is>
       </c>
       <c r="H294" s="0">
-        <v>5.2</v>
+        <v>5.44</v>
       </c>
     </row>
     <row r="295" spans="1:8">
@@ -10065,7 +10065,7 @@
         </is>
       </c>
       <c r="C295" s="0">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D295" s="0">
         <v>12</v>
@@ -10084,7 +10084,7 @@
         </is>
       </c>
       <c r="H295" s="0">
-        <v>2.04</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="296" spans="1:8">
@@ -10099,7 +10099,7 @@
         </is>
       </c>
       <c r="C296" s="0">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D296" s="0">
         <v>12</v>
@@ -10118,7 +10118,7 @@
         </is>
       </c>
       <c r="H296" s="0">
-        <v>4.73</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="297" spans="1:8">
@@ -10133,10 +10133,10 @@
         </is>
       </c>
       <c r="C297" s="0">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="D297" s="0">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E297" s="0">
         <v>2023</v>
@@ -10152,7 +10152,7 @@
         </is>
       </c>
       <c r="H297" s="0">
-        <v>2.3</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="298" spans="1:8">
@@ -10167,10 +10167,10 @@
         </is>
       </c>
       <c r="C298" s="0">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="D298" s="0">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E298" s="0">
         <v>2023</v>
@@ -10186,7 +10186,7 @@
         </is>
       </c>
       <c r="H298" s="0">
-        <v>3.88</v>
+        <v>4.73</v>
       </c>
     </row>
     <row r="299" spans="1:8">
@@ -10201,7 +10201,7 @@
         </is>
       </c>
       <c r="C299" s="0">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="D299" s="0">
         <v>11</v>
@@ -10220,7 +10220,7 @@
         </is>
       </c>
       <c r="H299" s="0">
-        <v>2.58</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="300" spans="1:8">
@@ -10235,7 +10235,7 @@
         </is>
       </c>
       <c r="C300" s="0">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="D300" s="0">
         <v>11</v>
@@ -10254,7 +10254,7 @@
         </is>
       </c>
       <c r="H300" s="0">
-        <v>3.8</v>
+        <v>3.88</v>
       </c>
     </row>
     <row r="301" spans="1:8">
@@ -10269,7 +10269,7 @@
         </is>
       </c>
       <c r="C301" s="0">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D301" s="0">
         <v>11</v>
@@ -10288,7 +10288,7 @@
         </is>
       </c>
       <c r="H301" s="0">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="302" spans="1:8">
@@ -10303,7 +10303,7 @@
         </is>
       </c>
       <c r="C302" s="0">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D302" s="0">
         <v>11</v>
@@ -10322,7 +10322,7 @@
         </is>
       </c>
       <c r="H302" s="0">
-        <v>3.83</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="303" spans="1:8">
@@ -10337,7 +10337,7 @@
         </is>
       </c>
       <c r="C303" s="0">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D303" s="0">
         <v>11</v>
@@ -10356,7 +10356,7 @@
         </is>
       </c>
       <c r="H303" s="0">
-        <v>2.59</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="304" spans="1:8">
@@ -10371,7 +10371,7 @@
         </is>
       </c>
       <c r="C304" s="0">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D304" s="0">
         <v>11</v>
@@ -10390,7 +10390,7 @@
         </is>
       </c>
       <c r="H304" s="0">
-        <v>3.54</v>
+        <v>3.83</v>
       </c>
     </row>
     <row r="305" spans="1:8">
@@ -10405,7 +10405,7 @@
         </is>
       </c>
       <c r="C305" s="0">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D305" s="0">
         <v>11</v>
@@ -10424,7 +10424,7 @@
         </is>
       </c>
       <c r="H305" s="0">
-        <v>2.19</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="306" spans="1:8">
@@ -10439,7 +10439,7 @@
         </is>
       </c>
       <c r="C306" s="0">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D306" s="0">
         <v>11</v>
@@ -10458,7 +10458,7 @@
         </is>
       </c>
       <c r="H306" s="0">
-        <v>2.81</v>
+        <v>3.54</v>
       </c>
     </row>
     <row r="307" spans="1:8">
@@ -10473,10 +10473,10 @@
         </is>
       </c>
       <c r="C307" s="0">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="D307" s="0">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E307" s="0">
         <v>2023</v>
@@ -10492,7 +10492,7 @@
         </is>
       </c>
       <c r="H307" s="0">
-        <v>1.98</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="308" spans="1:8">
@@ -10507,10 +10507,10 @@
         </is>
       </c>
       <c r="C308" s="0">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="D308" s="0">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E308" s="0">
         <v>2023</v>
@@ -10526,7 +10526,7 @@
         </is>
       </c>
       <c r="H308" s="0">
-        <v>2.67</v>
+        <v>2.81</v>
       </c>
     </row>
     <row r="309" spans="1:8">
@@ -10541,7 +10541,7 @@
         </is>
       </c>
       <c r="C309" s="0">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D309" s="0">
         <v>10</v>
@@ -10560,7 +10560,7 @@
         </is>
       </c>
       <c r="H309" s="0">
-        <v>2.06</v>
+        <v>1.98</v>
       </c>
     </row>
     <row r="310" spans="1:8">
@@ -10575,7 +10575,7 @@
         </is>
       </c>
       <c r="C310" s="0">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D310" s="0">
         <v>10</v>
@@ -10594,7 +10594,7 @@
         </is>
       </c>
       <c r="H310" s="0">
-        <v>2.74</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="311" spans="1:8">
@@ -10609,7 +10609,7 @@
         </is>
       </c>
       <c r="C311" s="0">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D311" s="0">
         <v>10</v>
@@ -10628,7 +10628,7 @@
         </is>
       </c>
       <c r="H311" s="0">
-        <v>1.89</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="312" spans="1:8">
@@ -10643,7 +10643,7 @@
         </is>
       </c>
       <c r="C312" s="0">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D312" s="0">
         <v>10</v>
@@ -10662,7 +10662,7 @@
         </is>
       </c>
       <c r="H312" s="0">
-        <v>2.64</v>
+        <v>2.74</v>
       </c>
     </row>
     <row r="313" spans="1:8">
@@ -10677,7 +10677,7 @@
         </is>
       </c>
       <c r="C313" s="0">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D313" s="0">
         <v>10</v>
@@ -10696,7 +10696,7 @@
         </is>
       </c>
       <c r="H313" s="0">
-        <v>1.7</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="314" spans="1:8">
@@ -10711,7 +10711,7 @@
         </is>
       </c>
       <c r="C314" s="0">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D314" s="0">
         <v>10</v>
@@ -10730,7 +10730,7 @@
         </is>
       </c>
       <c r="H314" s="0">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="315" spans="1:8">
@@ -10745,10 +10745,10 @@
         </is>
       </c>
       <c r="C315" s="0">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="D315" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E315" s="0">
         <v>2023</v>
@@ -10764,7 +10764,7 @@
         </is>
       </c>
       <c r="H315" s="0">
-        <v>1.86</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="316" spans="1:8">
@@ -10779,10 +10779,10 @@
         </is>
       </c>
       <c r="C316" s="0">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="D316" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E316" s="0">
         <v>2023</v>
@@ -10798,7 +10798,7 @@
         </is>
       </c>
       <c r="H316" s="0">
-        <v>2.59</v>
+        <v>2.66</v>
       </c>
     </row>
     <row r="317" spans="1:8">
@@ -10813,7 +10813,7 @@
         </is>
       </c>
       <c r="C317" s="0">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D317" s="0">
         <v>9</v>
@@ -10832,7 +10832,7 @@
         </is>
       </c>
       <c r="H317" s="0">
-        <v>2.34</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="318" spans="1:8">
@@ -10847,7 +10847,7 @@
         </is>
       </c>
       <c r="C318" s="0">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D318" s="0">
         <v>9</v>
@@ -10866,7 +10866,7 @@
         </is>
       </c>
       <c r="H318" s="0">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="319" spans="1:8">
@@ -10881,7 +10881,7 @@
         </is>
       </c>
       <c r="C319" s="0">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="D319" s="0">
         <v>9</v>
@@ -10900,7 +10900,7 @@
         </is>
       </c>
       <c r="H319" s="0">
-        <v>2.45</v>
+        <v>2.34</v>
       </c>
     </row>
     <row r="320" spans="1:8">
@@ -10915,7 +10915,7 @@
         </is>
       </c>
       <c r="C320" s="0">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="D320" s="0">
         <v>9</v>
@@ -10934,7 +10934,7 @@
         </is>
       </c>
       <c r="H320" s="0">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="321" spans="1:8">
@@ -10949,7 +10949,7 @@
         </is>
       </c>
       <c r="C321" s="0">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="D321" s="0">
         <v>9</v>
@@ -10968,7 +10968,7 @@
         </is>
       </c>
       <c r="H321" s="0">
-        <v>2.86</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="322" spans="1:8">
@@ -10983,7 +10983,7 @@
         </is>
       </c>
       <c r="C322" s="0">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="D322" s="0">
         <v>9</v>
@@ -11002,7 +11002,7 @@
         </is>
       </c>
       <c r="H322" s="0">
-        <v>2.69</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="323" spans="1:8">
@@ -11017,10 +11017,10 @@
         </is>
       </c>
       <c r="C323" s="0">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="D323" s="0">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E323" s="0">
         <v>2023</v>
@@ -11036,7 +11036,7 @@
         </is>
       </c>
       <c r="H323" s="0">
-        <v>3.05</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="324" spans="1:8">
@@ -11051,10 +11051,10 @@
         </is>
       </c>
       <c r="C324" s="0">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="D324" s="0">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E324" s="0">
         <v>2023</v>
@@ -11070,7 +11070,7 @@
         </is>
       </c>
       <c r="H324" s="0">
-        <v>2.86</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="325" spans="1:8">
@@ -11085,7 +11085,7 @@
         </is>
       </c>
       <c r="C325" s="0">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D325" s="0">
         <v>8</v>
@@ -11104,7 +11104,7 @@
         </is>
       </c>
       <c r="H325" s="0">
-        <v>3.26</v>
+        <v>3.05</v>
       </c>
     </row>
     <row r="326" spans="1:8">
@@ -11119,7 +11119,7 @@
         </is>
       </c>
       <c r="C326" s="0">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D326" s="0">
         <v>8</v>
@@ -11138,7 +11138,7 @@
         </is>
       </c>
       <c r="H326" s="0">
-        <v>3.06</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="327" spans="1:8">
@@ -11153,7 +11153,7 @@
         </is>
       </c>
       <c r="C327" s="0">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D327" s="0">
         <v>8</v>
@@ -11172,7 +11172,7 @@
         </is>
       </c>
       <c r="H327" s="0">
-        <v>3.2</v>
+        <v>3.26</v>
       </c>
     </row>
     <row r="328" spans="1:8">
@@ -11187,7 +11187,7 @@
         </is>
       </c>
       <c r="C328" s="0">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D328" s="0">
         <v>8</v>
@@ -11221,7 +11221,7 @@
         </is>
       </c>
       <c r="C329" s="0">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="D329" s="0">
         <v>8</v>
@@ -11240,7 +11240,7 @@
         </is>
       </c>
       <c r="H329" s="0">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="330" spans="1:8">
@@ -11255,7 +11255,7 @@
         </is>
       </c>
       <c r="C330" s="0">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="D330" s="0">
         <v>8</v>
@@ -11274,7 +11274,7 @@
         </is>
       </c>
       <c r="H330" s="0">
-        <v>3.2</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="331" spans="1:8">
@@ -11289,7 +11289,7 @@
         </is>
       </c>
       <c r="C331" s="0">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D331" s="0">
         <v>8</v>
@@ -11308,7 +11308,7 @@
         </is>
       </c>
       <c r="H331" s="0">
-        <v>2.85</v>
+        <v>3.21</v>
       </c>
     </row>
     <row r="332" spans="1:8">
@@ -11323,7 +11323,7 @@
         </is>
       </c>
       <c r="C332" s="0">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D332" s="0">
         <v>8</v>
@@ -11342,7 +11342,7 @@
         </is>
       </c>
       <c r="H332" s="0">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="333" spans="1:8">
@@ -11357,10 +11357,10 @@
         </is>
       </c>
       <c r="C333" s="0">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="D333" s="0">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E333" s="0">
         <v>2023</v>
@@ -11376,7 +11376,7 @@
         </is>
       </c>
       <c r="H333" s="0">
-        <v>2.66</v>
+        <v>2.85</v>
       </c>
     </row>
     <row r="334" spans="1:8">
@@ -11391,10 +11391,10 @@
         </is>
       </c>
       <c r="C334" s="0">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="D334" s="0">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E334" s="0">
         <v>2023</v>
@@ -11410,7 +11410,7 @@
         </is>
       </c>
       <c r="H334" s="0">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="335" spans="1:8">
@@ -11425,7 +11425,7 @@
         </is>
       </c>
       <c r="C335" s="0">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D335" s="0">
         <v>7</v>
@@ -11444,7 +11444,7 @@
         </is>
       </c>
       <c r="H335" s="0">
-        <v>2.45</v>
+        <v>2.66</v>
       </c>
     </row>
     <row r="336" spans="1:8">
@@ -11459,7 +11459,7 @@
         </is>
       </c>
       <c r="C336" s="0">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D336" s="0">
         <v>7</v>
@@ -11478,7 +11478,7 @@
         </is>
       </c>
       <c r="H336" s="0">
-        <v>2.89</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="337" spans="1:8">
@@ -11493,7 +11493,7 @@
         </is>
       </c>
       <c r="C337" s="0">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D337" s="0">
         <v>7</v>
@@ -11512,7 +11512,7 @@
         </is>
       </c>
       <c r="H337" s="0">
-        <v>2.28</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="338" spans="1:8">
@@ -11527,7 +11527,7 @@
         </is>
       </c>
       <c r="C338" s="0">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D338" s="0">
         <v>7</v>
@@ -11546,7 +11546,7 @@
         </is>
       </c>
       <c r="H338" s="0">
-        <v>3.04</v>
+        <v>2.89</v>
       </c>
     </row>
     <row r="339" spans="1:8">
@@ -11561,7 +11561,7 @@
         </is>
       </c>
       <c r="C339" s="0">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D339" s="0">
         <v>7</v>
@@ -11580,7 +11580,7 @@
         </is>
       </c>
       <c r="H339" s="0">
-        <v>1.96</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="340" spans="1:8">
@@ -11595,7 +11595,7 @@
         </is>
       </c>
       <c r="C340" s="0">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D340" s="0">
         <v>7</v>
@@ -11614,7 +11614,7 @@
         </is>
       </c>
       <c r="H340" s="0">
-        <v>3.01</v>
+        <v>3.04</v>
       </c>
     </row>
     <row r="341" spans="1:8">
@@ -11629,10 +11629,10 @@
         </is>
       </c>
       <c r="C341" s="0">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="D341" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E341" s="0">
         <v>2023</v>
@@ -11648,7 +11648,7 @@
         </is>
       </c>
       <c r="H341" s="0">
-        <v>1.57</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="342" spans="1:8">
@@ -11663,10 +11663,10 @@
         </is>
       </c>
       <c r="C342" s="0">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="D342" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E342" s="0">
         <v>2023</v>
@@ -11682,7 +11682,7 @@
         </is>
       </c>
       <c r="H342" s="0">
-        <v>2.86</v>
+        <v>3.01</v>
       </c>
     </row>
     <row r="343" spans="1:8">
@@ -11697,7 +11697,7 @@
         </is>
       </c>
       <c r="C343" s="0">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="D343" s="0">
         <v>6</v>
@@ -11716,7 +11716,7 @@
         </is>
       </c>
       <c r="H343" s="0">
-        <v>1.42</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="344" spans="1:8">
@@ -11731,7 +11731,7 @@
         </is>
       </c>
       <c r="C344" s="0">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="D344" s="0">
         <v>6</v>
@@ -11750,7 +11750,7 @@
         </is>
       </c>
       <c r="H344" s="0">
-        <v>2.7</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="345" spans="1:8">
@@ -11765,7 +11765,7 @@
         </is>
       </c>
       <c r="C345" s="0">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="D345" s="0">
         <v>6</v>
@@ -11784,7 +11784,7 @@
         </is>
       </c>
       <c r="H345" s="0">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="346" spans="1:8">
@@ -11799,7 +11799,7 @@
         </is>
       </c>
       <c r="C346" s="0">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="D346" s="0">
         <v>6</v>
@@ -11818,7 +11818,7 @@
         </is>
       </c>
       <c r="H346" s="0">
-        <v>2.61</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="347" spans="1:8">
@@ -11833,7 +11833,7 @@
         </is>
       </c>
       <c r="C347" s="0">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="D347" s="0">
         <v>6</v>
@@ -11852,7 +11852,7 @@
         </is>
       </c>
       <c r="H347" s="0">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="348" spans="1:8">
@@ -11867,7 +11867,7 @@
         </is>
       </c>
       <c r="C348" s="0">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="D348" s="0">
         <v>6</v>
@@ -11886,7 +11886,7 @@
         </is>
       </c>
       <c r="H348" s="0">
-        <v>2.64</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="349" spans="1:8">
@@ -11901,7 +11901,7 @@
         </is>
       </c>
       <c r="C349" s="0">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D349" s="0">
         <v>6</v>
@@ -11920,7 +11920,7 @@
         </is>
       </c>
       <c r="H349" s="0">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="350" spans="1:8">
@@ -11935,7 +11935,7 @@
         </is>
       </c>
       <c r="C350" s="0">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D350" s="0">
         <v>6</v>
@@ -11954,7 +11954,7 @@
         </is>
       </c>
       <c r="H350" s="0">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="351" spans="1:8">
@@ -11969,10 +11969,10 @@
         </is>
       </c>
       <c r="C351" s="0">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="D351" s="0">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E351" s="0">
         <v>2023</v>
@@ -11988,7 +11988,7 @@
         </is>
       </c>
       <c r="H351" s="0">
-        <v>1.57</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="352" spans="1:8">
@@ -12003,10 +12003,10 @@
         </is>
       </c>
       <c r="C352" s="0">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="D352" s="0">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E352" s="0">
         <v>2023</v>
@@ -12022,7 +12022,7 @@
         </is>
       </c>
       <c r="H352" s="0">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="353" spans="1:8">
@@ -12037,7 +12037,7 @@
         </is>
       </c>
       <c r="C353" s="0">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="D353" s="0">
         <v>5</v>
@@ -12056,7 +12056,7 @@
         </is>
       </c>
       <c r="H353" s="0">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="354" spans="1:8">
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="C354" s="0">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="D354" s="0">
         <v>5</v>
@@ -12090,7 +12090,7 @@
         </is>
       </c>
       <c r="H354" s="0">
-        <v>2.47</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="355" spans="1:8">
@@ -12105,7 +12105,7 @@
         </is>
       </c>
       <c r="C355" s="0">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D355" s="0">
         <v>5</v>
@@ -12124,7 +12124,7 @@
         </is>
       </c>
       <c r="H355" s="0">
-        <v>1.35</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="356" spans="1:8">
@@ -12139,7 +12139,7 @@
         </is>
       </c>
       <c r="C356" s="0">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D356" s="0">
         <v>5</v>
@@ -12158,7 +12158,7 @@
         </is>
       </c>
       <c r="H356" s="0">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="357" spans="1:8">
@@ -12173,7 +12173,7 @@
         </is>
       </c>
       <c r="C357" s="0">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D357" s="0">
         <v>5</v>
@@ -12192,7 +12192,7 @@
         </is>
       </c>
       <c r="H357" s="0">
-        <v>1.47</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="358" spans="1:8">
@@ -12207,7 +12207,7 @@
         </is>
       </c>
       <c r="C358" s="0">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D358" s="0">
         <v>5</v>
@@ -12226,7 +12226,7 @@
         </is>
       </c>
       <c r="H358" s="0">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="359" spans="1:8">
@@ -12241,10 +12241,10 @@
         </is>
       </c>
       <c r="C359" s="0">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="D359" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E359" s="0">
         <v>2023</v>
@@ -12260,7 +12260,7 @@
         </is>
       </c>
       <c r="H359" s="0">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="360" spans="1:8">
@@ -12275,10 +12275,10 @@
         </is>
       </c>
       <c r="C360" s="0">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="D360" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E360" s="0">
         <v>2023</v>
@@ -12294,7 +12294,7 @@
         </is>
       </c>
       <c r="H360" s="0">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="361" spans="1:8">
@@ -12309,7 +12309,7 @@
         </is>
       </c>
       <c r="C361" s="0">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D361" s="0">
         <v>4</v>
@@ -12328,7 +12328,7 @@
         </is>
       </c>
       <c r="H361" s="0">
-        <v>1.58</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="362" spans="1:8">
@@ -12343,7 +12343,7 @@
         </is>
       </c>
       <c r="C362" s="0">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D362" s="0">
         <v>4</v>
@@ -12362,7 +12362,7 @@
         </is>
       </c>
       <c r="H362" s="0">
-        <v>2.76</v>
+        <v>2.51</v>
       </c>
     </row>
     <row r="363" spans="1:8">
@@ -12377,7 +12377,7 @@
         </is>
       </c>
       <c r="C363" s="0">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D363" s="0">
         <v>4</v>
@@ -12396,7 +12396,7 @@
         </is>
       </c>
       <c r="H363" s="0">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="364" spans="1:8">
@@ -12411,7 +12411,7 @@
         </is>
       </c>
       <c r="C364" s="0">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D364" s="0">
         <v>4</v>
@@ -12430,7 +12430,7 @@
         </is>
       </c>
       <c r="H364" s="0">
-        <v>2.84</v>
+        <v>2.76</v>
       </c>
     </row>
     <row r="365" spans="1:8">
@@ -12445,7 +12445,7 @@
         </is>
       </c>
       <c r="C365" s="0">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D365" s="0">
         <v>4</v>
@@ -12464,7 +12464,7 @@
         </is>
       </c>
       <c r="H365" s="0">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="366" spans="1:8">
@@ -12479,7 +12479,7 @@
         </is>
       </c>
       <c r="C366" s="0">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D366" s="0">
         <v>4</v>
@@ -12498,7 +12498,7 @@
         </is>
       </c>
       <c r="H366" s="0">
-        <v>2.65</v>
+        <v>2.84</v>
       </c>
     </row>
     <row r="367" spans="1:8">
@@ -12513,10 +12513,10 @@
         </is>
       </c>
       <c r="C367" s="0">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="D367" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E367" s="0">
         <v>2023</v>
@@ -12532,7 +12532,7 @@
         </is>
       </c>
       <c r="H367" s="0">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="368" spans="1:8">
@@ -12547,10 +12547,10 @@
         </is>
       </c>
       <c r="C368" s="0">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="D368" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E368" s="0">
         <v>2023</v>
@@ -12566,7 +12566,7 @@
         </is>
       </c>
       <c r="H368" s="0">
-        <v>2.29</v>
+        <v>2.65</v>
       </c>
     </row>
     <row r="369" spans="1:8">
@@ -12581,7 +12581,7 @@
         </is>
       </c>
       <c r="C369" s="0">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="D369" s="0">
         <v>3</v>
@@ -12600,7 +12600,7 @@
         </is>
       </c>
       <c r="H369" s="0">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="370" spans="1:8">
@@ -12615,7 +12615,7 @@
         </is>
       </c>
       <c r="C370" s="0">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="D370" s="0">
         <v>3</v>
@@ -12634,7 +12634,7 @@
         </is>
       </c>
       <c r="H370" s="0">
-        <v>2.36</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="371" spans="1:8">
@@ -12649,7 +12649,7 @@
         </is>
       </c>
       <c r="C371" s="0">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D371" s="0">
         <v>3</v>
@@ -12668,7 +12668,7 @@
         </is>
       </c>
       <c r="H371" s="0">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
     </row>
     <row r="372" spans="1:8">
@@ -12683,7 +12683,7 @@
         </is>
       </c>
       <c r="C372" s="0">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D372" s="0">
         <v>3</v>
@@ -12702,7 +12702,7 @@
         </is>
       </c>
       <c r="H372" s="0">
-        <v>2.48</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="373" spans="1:8">
@@ -12717,7 +12717,7 @@
         </is>
       </c>
       <c r="C373" s="0">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D373" s="0">
         <v>3</v>
@@ -12736,7 +12736,7 @@
         </is>
       </c>
       <c r="H373" s="0">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="374" spans="1:8">
@@ -12751,7 +12751,7 @@
         </is>
       </c>
       <c r="C374" s="0">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D374" s="0">
         <v>3</v>
@@ -12770,7 +12770,7 @@
         </is>
       </c>
       <c r="H374" s="0">
-        <v>3.61</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="375" spans="1:8">
@@ -12785,7 +12785,7 @@
         </is>
       </c>
       <c r="C375" s="0">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D375" s="0">
         <v>3</v>
@@ -12804,7 +12804,7 @@
         </is>
       </c>
       <c r="H375" s="0">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="376" spans="1:8">
@@ -12819,7 +12819,7 @@
         </is>
       </c>
       <c r="C376" s="0">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D376" s="0">
         <v>3</v>
@@ -12838,7 +12838,7 @@
         </is>
       </c>
       <c r="H376" s="0">
-        <v>3.58</v>
+        <v>3.61</v>
       </c>
     </row>
     <row r="377" spans="1:8">
@@ -12853,10 +12853,10 @@
         </is>
       </c>
       <c r="C377" s="0">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="D377" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E377" s="0">
         <v>2023</v>
@@ -12872,7 +12872,7 @@
         </is>
       </c>
       <c r="H377" s="0">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="378" spans="1:8">
@@ -12887,10 +12887,10 @@
         </is>
       </c>
       <c r="C378" s="0">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="D378" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E378" s="0">
         <v>2023</v>
@@ -12906,7 +12906,7 @@
         </is>
       </c>
       <c r="H378" s="0">
-        <v>3.97</v>
+        <v>3.58</v>
       </c>
     </row>
     <row r="379" spans="1:8">
@@ -12921,7 +12921,7 @@
         </is>
       </c>
       <c r="C379" s="0">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D379" s="0">
         <v>2</v>
@@ -12940,7 +12940,7 @@
         </is>
       </c>
       <c r="H379" s="0">
-        <v>1.63</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="380" spans="1:8">
@@ -12955,7 +12955,7 @@
         </is>
       </c>
       <c r="C380" s="0">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D380" s="0">
         <v>2</v>
@@ -12974,7 +12974,7 @@
         </is>
       </c>
       <c r="H380" s="0">
-        <v>4.41</v>
+        <v>3.97</v>
       </c>
     </row>
     <row r="381" spans="1:8">
@@ -12989,7 +12989,7 @@
         </is>
       </c>
       <c r="C381" s="0">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D381" s="0">
         <v>2</v>
@@ -13023,7 +13023,7 @@
         </is>
       </c>
       <c r="C382" s="0">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D382" s="0">
         <v>2</v>
@@ -13042,7 +13042,7 @@
         </is>
       </c>
       <c r="H382" s="0">
-        <v>4.44</v>
+        <v>4.41</v>
       </c>
     </row>
     <row r="383" spans="1:8">
@@ -13057,7 +13057,7 @@
         </is>
       </c>
       <c r="C383" s="0">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D383" s="0">
         <v>2</v>
@@ -13076,7 +13076,7 @@
         </is>
       </c>
       <c r="H383" s="0">
-        <v>1.39</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="384" spans="1:8">
@@ -13091,7 +13091,7 @@
         </is>
       </c>
       <c r="C384" s="0">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D384" s="0">
         <v>2</v>
@@ -13110,7 +13110,7 @@
         </is>
       </c>
       <c r="H384" s="0">
-        <v>4.47</v>
+        <v>4.44</v>
       </c>
     </row>
     <row r="385" spans="1:8">
@@ -13125,10 +13125,10 @@
         </is>
       </c>
       <c r="C385" s="0">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="D385" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E385" s="0">
         <v>2023</v>
@@ -13144,7 +13144,7 @@
         </is>
       </c>
       <c r="H385" s="0">
-        <v>1.18</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="386" spans="1:8">
@@ -13159,10 +13159,10 @@
         </is>
       </c>
       <c r="C386" s="0">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="D386" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E386" s="0">
         <v>2023</v>
@@ -13178,7 +13178,7 @@
         </is>
       </c>
       <c r="H386" s="0">
-        <v>4.37</v>
+        <v>4.47</v>
       </c>
     </row>
     <row r="387" spans="1:8">
@@ -13193,7 +13193,7 @@
         </is>
       </c>
       <c r="C387" s="0">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D387" s="0">
         <v>1</v>
@@ -13212,7 +13212,7 @@
         </is>
       </c>
       <c r="H387" s="0">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="388" spans="1:8">
@@ -13227,7 +13227,7 @@
         </is>
       </c>
       <c r="C388" s="0">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D388" s="0">
         <v>1</v>
@@ -13246,7 +13246,7 @@
         </is>
       </c>
       <c r="H388" s="0">
-        <v>4.51</v>
+        <v>4.37</v>
       </c>
     </row>
     <row r="389" spans="1:8">
@@ -13261,7 +13261,7 @@
         </is>
       </c>
       <c r="C389" s="0">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D389" s="0">
         <v>1</v>
@@ -13280,7 +13280,7 @@
         </is>
       </c>
       <c r="H389" s="0">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="390" spans="1:8">
@@ -13295,7 +13295,7 @@
         </is>
       </c>
       <c r="C390" s="0">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D390" s="0">
         <v>1</v>
@@ -13314,7 +13314,7 @@
         </is>
       </c>
       <c r="H390" s="0">
-        <v>4.56</v>
+        <v>4.51</v>
       </c>
     </row>
     <row r="391" spans="1:8">
@@ -13329,7 +13329,7 @@
         </is>
       </c>
       <c r="C391" s="0">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D391" s="0">
         <v>1</v>
@@ -13348,7 +13348,7 @@
         </is>
       </c>
       <c r="H391" s="0">
-        <v>1.76</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="392" spans="1:8">
@@ -13363,7 +13363,7 @@
         </is>
       </c>
       <c r="C392" s="0">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D392" s="0">
         <v>1</v>
@@ -13382,11 +13382,79 @@
         </is>
       </c>
       <c r="H392" s="0">
+        <v>4.56</v>
+      </c>
+    </row>
+    <row r="393" spans="1:8">
+      <c r="A393" s="0" t="inlineStr">
+        <is>
+          <t>Nanica primeira - produtor</t>
+        </is>
+      </c>
+      <c r="B393" s="0" t="inlineStr">
+        <is>
+          <t>Bom Jesus da Lapa</t>
+        </is>
+      </c>
+      <c r="C393" s="0">
+        <v>6</v>
+      </c>
+      <c r="D393" s="0">
+        <v>1</v>
+      </c>
+      <c r="E393" s="0">
+        <v>2023</v>
+      </c>
+      <c r="F393" s="0" t="inlineStr">
+        <is>
+          <t>R$   </t>
+        </is>
+      </c>
+      <c r="G393" s="0" t="inlineStr">
+        <is>
+          <t>quilograma</t>
+        </is>
+      </c>
+      <c r="H393" s="0">
+        <v>1.76</v>
+      </c>
+    </row>
+    <row r="394" spans="1:8">
+      <c r="A394" s="0" t="inlineStr">
+        <is>
+          <t>Prata anã primeira - produtor</t>
+        </is>
+      </c>
+      <c r="B394" s="0" t="inlineStr">
+        <is>
+          <t>Bom Jesus da Lapa</t>
+        </is>
+      </c>
+      <c r="C394" s="0">
+        <v>6</v>
+      </c>
+      <c r="D394" s="0">
+        <v>1</v>
+      </c>
+      <c r="E394" s="0">
+        <v>2023</v>
+      </c>
+      <c r="F394" s="0" t="inlineStr">
+        <is>
+          <t>R$   </t>
+        </is>
+      </c>
+      <c r="G394" s="0" t="inlineStr">
+        <is>
+          <t>quilograma</t>
+        </is>
+      </c>
+      <c r="H394" s="0">
         <v>4.59</v>
       </c>
     </row>
-    <row r="393" spans="1:1">
-      <c r="A393" s="0" t="inlineStr">
+    <row r="395" spans="1:1">
+      <c r="A395" s="0" t="inlineStr">
         <is>
           <t>Fonte: Hortifruti/Cepea</t>
         </is>

--- a/fuentes/precios_banana_BJLapa.xlsx
+++ b/fuentes/precios_banana_BJLapa.xlsx
@@ -103,7 +103,7 @@
         </is>
       </c>
       <c r="C2" s="0">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D2" s="0">
         <v>10</v>
@@ -122,7 +122,7 @@
         </is>
       </c>
       <c r="H2" s="0">
-        <v>0.99</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -137,7 +137,7 @@
         </is>
       </c>
       <c r="C3" s="0">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D3" s="0">
         <v>10</v>
@@ -156,7 +156,7 @@
         </is>
       </c>
       <c r="H3" s="0">
-        <v>1.59</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -171,10 +171,10 @@
         </is>
       </c>
       <c r="C4" s="0">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="D4" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E4" s="0">
         <v>2026</v>
@@ -190,7 +190,7 @@
         </is>
       </c>
       <c r="H4" s="0">
-        <v>1.14</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -205,10 +205,10 @@
         </is>
       </c>
       <c r="C5" s="0">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="D5" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E5" s="0">
         <v>2026</v>
@@ -224,7 +224,7 @@
         </is>
       </c>
       <c r="H5" s="0">
-        <v>1.81</v>
+        <v>1.59</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -239,7 +239,7 @@
         </is>
       </c>
       <c r="C6" s="0">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D6" s="0">
         <v>9</v>
@@ -258,7 +258,7 @@
         </is>
       </c>
       <c r="H6" s="0">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -273,7 +273,7 @@
         </is>
       </c>
       <c r="C7" s="0">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D7" s="0">
         <v>9</v>
@@ -292,7 +292,7 @@
         </is>
       </c>
       <c r="H7" s="0">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -307,7 +307,7 @@
         </is>
       </c>
       <c r="C8" s="0">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="D8" s="0">
         <v>9</v>
@@ -326,7 +326,7 @@
         </is>
       </c>
       <c r="H8" s="0">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -341,7 +341,7 @@
         </is>
       </c>
       <c r="C9" s="0">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="D9" s="0">
         <v>9</v>
@@ -360,7 +360,7 @@
         </is>
       </c>
       <c r="H9" s="0">
-        <v>1.73</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -375,7 +375,7 @@
         </is>
       </c>
       <c r="C10" s="0">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D10" s="0">
         <v>9</v>
@@ -394,7 +394,7 @@
         </is>
       </c>
       <c r="H10" s="0">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -409,7 +409,7 @@
         </is>
       </c>
       <c r="C11" s="0">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D11" s="0">
         <v>9</v>
@@ -428,7 +428,7 @@
         </is>
       </c>
       <c r="H11" s="0">
-        <v>1.98</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -443,10 +443,10 @@
         </is>
       </c>
       <c r="C12" s="0">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="D12" s="0">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E12" s="0">
         <v>2026</v>
@@ -462,7 +462,7 @@
         </is>
       </c>
       <c r="H12" s="0">
-        <v>1.36</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -477,10 +477,10 @@
         </is>
       </c>
       <c r="C13" s="0">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="D13" s="0">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E13" s="0">
         <v>2026</v>
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="H13" s="0">
-        <v>2.24</v>
+        <v>1.98</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="C14" s="0">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D14" s="0">
         <v>8</v>
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="H14" s="0">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="C15" s="0">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D15" s="0">
         <v>8</v>
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="H15" s="0">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -579,7 +579,7 @@
         </is>
       </c>
       <c r="C16" s="0">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D16" s="0">
         <v>8</v>
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="H16" s="0">
-        <v>2.14</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -613,7 +613,7 @@
         </is>
       </c>
       <c r="C17" s="0">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D17" s="0">
         <v>8</v>
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="H17" s="0">
-        <v>2.53</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -647,7 +647,7 @@
         </is>
       </c>
       <c r="C18" s="0">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D18" s="0">
         <v>8</v>
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="H18" s="0">
-        <v>2.4</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="C19" s="0">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D19" s="0">
         <v>8</v>
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="H19" s="0">
-        <v>2.66</v>
+        <v>2.53</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="C20" s="0">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="D20" s="0">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E20" s="0">
         <v>2026</v>
@@ -749,10 +749,10 @@
         </is>
       </c>
       <c r="C21" s="0">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="D21" s="0">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E21" s="0">
         <v>2026</v>
@@ -768,7 +768,7 @@
         </is>
       </c>
       <c r="H21" s="0">
-        <v>2.4</v>
+        <v>2.66</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="C22" s="0">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="D22" s="0">
         <v>7</v>
@@ -798,17 +798,17 @@
       </c>
       <c r="G22" s="0" t="inlineStr">
         <is>
-          <t>Cento</t>
+          <t>quilograma</t>
         </is>
       </c>
       <c r="H22" s="0">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="0" t="inlineStr">
         <is>
-          <t>Nanica primeira - produtor</t>
+          <t>Prata anã primeira - produtor</t>
         </is>
       </c>
       <c r="B23" s="0" t="inlineStr">
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="C23" s="0">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="D23" s="0">
         <v>7</v>
@@ -836,13 +836,13 @@
         </is>
       </c>
       <c r="H23" s="0">
-        <v>2.22</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="0" t="inlineStr">
         <is>
-          <t>Prata anã primeira - produtor</t>
+          <t>Nanica primeira - produtor</t>
         </is>
       </c>
       <c r="B24" s="0" t="inlineStr">
@@ -866,11 +866,11 @@
       </c>
       <c r="G24" s="0" t="inlineStr">
         <is>
-          <t>quilograma</t>
+          <t>Cento</t>
         </is>
       </c>
       <c r="H24" s="0">
-        <v>2.07</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -885,7 +885,7 @@
         </is>
       </c>
       <c r="C25" s="0">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D25" s="0">
         <v>7</v>
@@ -904,7 +904,7 @@
         </is>
       </c>
       <c r="H25" s="0">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -919,7 +919,7 @@
         </is>
       </c>
       <c r="C26" s="0">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D26" s="0">
         <v>7</v>
@@ -938,7 +938,7 @@
         </is>
       </c>
       <c r="H26" s="0">
-        <v>1.83</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -953,7 +953,7 @@
         </is>
       </c>
       <c r="C27" s="0">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D27" s="0">
         <v>7</v>
@@ -968,17 +968,17 @@
       </c>
       <c r="G27" s="0" t="inlineStr">
         <is>
-          <t>Cento</t>
+          <t>quilograma</t>
         </is>
       </c>
       <c r="H27" s="0">
-        <v>1.9</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="0" t="inlineStr">
         <is>
-          <t>Nanica primeira - produtor</t>
+          <t>Prata anã primeira - produtor</t>
         </is>
       </c>
       <c r="B28" s="0" t="inlineStr">
@@ -987,7 +987,7 @@
         </is>
       </c>
       <c r="C28" s="0">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D28" s="0">
         <v>7</v>
@@ -1006,13 +1006,13 @@
         </is>
       </c>
       <c r="H28" s="0">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="0" t="inlineStr">
         <is>
-          <t>Prata anã primeira - produtor</t>
+          <t>Nanica primeira - produtor</t>
         </is>
       </c>
       <c r="B29" s="0" t="inlineStr">
@@ -1036,11 +1036,11 @@
       </c>
       <c r="G29" s="0" t="inlineStr">
         <is>
-          <t>quilograma</t>
+          <t>Cento</t>
         </is>
       </c>
       <c r="H29" s="0">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -1055,7 +1055,7 @@
         </is>
       </c>
       <c r="C30" s="0">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D30" s="0">
         <v>7</v>
@@ -1074,7 +1074,7 @@
         </is>
       </c>
       <c r="H30" s="0">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -1089,7 +1089,7 @@
         </is>
       </c>
       <c r="C31" s="0">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D31" s="0">
         <v>7</v>
@@ -1108,7 +1108,7 @@
         </is>
       </c>
       <c r="H31" s="0">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="C32" s="0">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="D32" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E32" s="0">
         <v>2026</v>
@@ -1142,7 +1142,7 @@
         </is>
       </c>
       <c r="H32" s="0">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -1157,10 +1157,10 @@
         </is>
       </c>
       <c r="C33" s="0">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="D33" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E33" s="0">
         <v>2026</v>
@@ -1176,7 +1176,7 @@
         </is>
       </c>
       <c r="H33" s="0">
-        <v>2.37</v>
+        <v>1.98</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -1191,7 +1191,7 @@
         </is>
       </c>
       <c r="C34" s="0">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="D34" s="0">
         <v>6</v>
@@ -1225,7 +1225,7 @@
         </is>
       </c>
       <c r="C35" s="0">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="D35" s="0">
         <v>6</v>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="H35" s="0">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -1259,7 +1259,7 @@
         </is>
       </c>
       <c r="C36" s="0">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D36" s="0">
         <v>6</v>
@@ -1278,7 +1278,7 @@
         </is>
       </c>
       <c r="H36" s="0">
-        <v>1.56</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="C37" s="0">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D37" s="0">
         <v>6</v>
@@ -1312,7 +1312,7 @@
         </is>
       </c>
       <c r="H37" s="0">
-        <v>2.58</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -1327,7 +1327,7 @@
         </is>
       </c>
       <c r="C38" s="0">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D38" s="0">
         <v>6</v>
@@ -1346,7 +1346,7 @@
         </is>
       </c>
       <c r="H38" s="0">
-        <v>1.12</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="C39" s="0">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D39" s="0">
         <v>6</v>
@@ -1380,7 +1380,7 @@
         </is>
       </c>
       <c r="H39" s="0">
-        <v>2.63</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -1395,10 +1395,10 @@
         </is>
       </c>
       <c r="C40" s="0">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="D40" s="0">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E40" s="0">
         <v>2026</v>
@@ -1414,7 +1414,7 @@
         </is>
       </c>
       <c r="H40" s="0">
-        <v>0.86</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="C41" s="0">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="D41" s="0">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E41" s="0">
         <v>2026</v>
@@ -1448,7 +1448,7 @@
         </is>
       </c>
       <c r="H41" s="0">
-        <v>2.54</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="C42" s="0">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D42" s="0">
         <v>5</v>
@@ -1482,7 +1482,7 @@
         </is>
       </c>
       <c r="H42" s="0">
-        <v>0.61</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -1497,7 +1497,7 @@
         </is>
       </c>
       <c r="C43" s="0">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D43" s="0">
         <v>5</v>
@@ -1516,7 +1516,7 @@
         </is>
       </c>
       <c r="H43" s="0">
-        <v>2.63</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="44" spans="1:8">
@@ -1531,7 +1531,7 @@
         </is>
       </c>
       <c r="C44" s="0">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="D44" s="0">
         <v>5</v>
@@ -1550,7 +1550,7 @@
         </is>
       </c>
       <c r="H44" s="0">
-        <v>0.62</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="45" spans="1:8">
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="C45" s="0">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="D45" s="0">
         <v>5</v>
@@ -1584,7 +1584,7 @@
         </is>
       </c>
       <c r="H45" s="0">
-        <v>2.66</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="46" spans="1:8">
@@ -1599,7 +1599,7 @@
         </is>
       </c>
       <c r="C46" s="0">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D46" s="0">
         <v>5</v>
@@ -1618,13 +1618,13 @@
         </is>
       </c>
       <c r="H46" s="0">
-        <v>0.75</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="0" t="inlineStr">
         <is>
-          <t>Nanica primeira - produtor</t>
+          <t>Prata anã primeira - produtor</t>
         </is>
       </c>
       <c r="B47" s="0" t="inlineStr">
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="C47" s="0">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="D47" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E47" s="0">
         <v>2026</v>
@@ -1652,13 +1652,13 @@
         </is>
       </c>
       <c r="H47" s="0">
-        <v>0.93</v>
+        <v>2.66</v>
       </c>
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="0" t="inlineStr">
         <is>
-          <t>Prata anã primeira - produtor</t>
+          <t>Nanica primeira - produtor</t>
         </is>
       </c>
       <c r="B48" s="0" t="inlineStr">
@@ -1667,10 +1667,10 @@
         </is>
       </c>
       <c r="C48" s="0">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="D48" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E48" s="0">
         <v>2026</v>
@@ -1686,7 +1686,7 @@
         </is>
       </c>
       <c r="H48" s="0">
-        <v>3.08</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="49" spans="1:8">
@@ -1701,7 +1701,7 @@
         </is>
       </c>
       <c r="C49" s="0">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="D49" s="0">
         <v>4</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="C50" s="0">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="D50" s="0">
         <v>4</v>
@@ -1754,7 +1754,7 @@
         </is>
       </c>
       <c r="H50" s="0">
-        <v>3.04</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="51" spans="1:8">
@@ -1769,7 +1769,7 @@
         </is>
       </c>
       <c r="C51" s="0">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D51" s="0">
         <v>4</v>
@@ -1788,7 +1788,7 @@
         </is>
       </c>
       <c r="H51" s="0">
-        <v>1.02</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="52" spans="1:8">
@@ -1803,7 +1803,7 @@
         </is>
       </c>
       <c r="C52" s="0">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D52" s="0">
         <v>4</v>
@@ -1822,7 +1822,7 @@
         </is>
       </c>
       <c r="H52" s="0">
-        <v>3.09</v>
+        <v>3.04</v>
       </c>
     </row>
     <row r="53" spans="1:8">
@@ -1837,7 +1837,7 @@
         </is>
       </c>
       <c r="C53" s="0">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D53" s="0">
         <v>4</v>
@@ -1856,7 +1856,7 @@
         </is>
       </c>
       <c r="H53" s="0">
-        <v>1.27</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="54" spans="1:8">
@@ -1871,7 +1871,7 @@
         </is>
       </c>
       <c r="C54" s="0">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D54" s="0">
         <v>4</v>
@@ -1890,7 +1890,7 @@
         </is>
       </c>
       <c r="H54" s="0">
-        <v>3.12</v>
+        <v>3.09</v>
       </c>
     </row>
     <row r="55" spans="1:8">
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="C55" s="0">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D55" s="0">
         <v>4</v>
@@ -1924,7 +1924,7 @@
         </is>
       </c>
       <c r="H55" s="0">
-        <v>1.56</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="56" spans="1:8">
@@ -1939,7 +1939,7 @@
         </is>
       </c>
       <c r="C56" s="0">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D56" s="0">
         <v>4</v>
@@ -1958,7 +1958,7 @@
         </is>
       </c>
       <c r="H56" s="0">
-        <v>3.13</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="57" spans="1:8">
@@ -1973,10 +1973,10 @@
         </is>
       </c>
       <c r="C57" s="0">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="D57" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E57" s="0">
         <v>2026</v>
@@ -1992,7 +1992,7 @@
         </is>
       </c>
       <c r="H57" s="0">
-        <v>2.04</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="58" spans="1:8">
@@ -2007,10 +2007,10 @@
         </is>
       </c>
       <c r="C58" s="0">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="D58" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E58" s="0">
         <v>2026</v>
@@ -2026,7 +2026,7 @@
         </is>
       </c>
       <c r="H58" s="0">
-        <v>3.23</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="59" spans="1:8">
@@ -2041,7 +2041,7 @@
         </is>
       </c>
       <c r="C59" s="0">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D59" s="0">
         <v>3</v>
@@ -2060,7 +2060,7 @@
         </is>
       </c>
       <c r="H59" s="0">
-        <v>2.36</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="60" spans="1:8">
@@ -2075,7 +2075,7 @@
         </is>
       </c>
       <c r="C60" s="0">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D60" s="0">
         <v>3</v>
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="H60" s="0">
-        <v>3.4</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="61" spans="1:8">
@@ -2109,7 +2109,7 @@
         </is>
       </c>
       <c r="C61" s="0">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D61" s="0">
         <v>3</v>
@@ -2128,7 +2128,7 @@
         </is>
       </c>
       <c r="H61" s="0">
-        <v>2.23</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="62" spans="1:8">
@@ -2143,7 +2143,7 @@
         </is>
       </c>
       <c r="C62" s="0">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D62" s="0">
         <v>3</v>
@@ -2162,7 +2162,7 @@
         </is>
       </c>
       <c r="H62" s="0">
-        <v>3.19</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="63" spans="1:8">
@@ -2177,7 +2177,7 @@
         </is>
       </c>
       <c r="C63" s="0">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D63" s="0">
         <v>3</v>
@@ -2196,7 +2196,7 @@
         </is>
       </c>
       <c r="H63" s="0">
-        <v>1.9</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="64" spans="1:8">
@@ -2211,7 +2211,7 @@
         </is>
       </c>
       <c r="C64" s="0">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D64" s="0">
         <v>3</v>
@@ -2230,7 +2230,7 @@
         </is>
       </c>
       <c r="H64" s="0">
-        <v>3.11</v>
+        <v>3.19</v>
       </c>
     </row>
     <row r="65" spans="1:8">
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="C65" s="0">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="D65" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E65" s="0">
         <v>2026</v>
@@ -2264,7 +2264,7 @@
         </is>
       </c>
       <c r="H65" s="0">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="66" spans="1:8">
@@ -2279,10 +2279,10 @@
         </is>
       </c>
       <c r="C66" s="0">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="D66" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E66" s="0">
         <v>2026</v>
@@ -2298,7 +2298,7 @@
         </is>
       </c>
       <c r="H66" s="0">
-        <v>3</v>
+        <v>3.11</v>
       </c>
     </row>
     <row r="67" spans="1:8">
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="C67" s="0">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D67" s="0">
         <v>2</v>
@@ -2332,7 +2332,7 @@
         </is>
       </c>
       <c r="H67" s="0">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="68" spans="1:8">
@@ -2347,7 +2347,7 @@
         </is>
       </c>
       <c r="C68" s="0">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D68" s="0">
         <v>2</v>
@@ -2366,7 +2366,7 @@
         </is>
       </c>
       <c r="H68" s="0">
-        <v>3.27</v>
+        <v>3</v>
       </c>
     </row>
     <row r="69" spans="1:8">
@@ -2381,7 +2381,7 @@
         </is>
       </c>
       <c r="C69" s="0">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D69" s="0">
         <v>2</v>
@@ -2400,7 +2400,7 @@
         </is>
       </c>
       <c r="H69" s="0">
-        <v>1.24</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="70" spans="1:8">
@@ -2415,7 +2415,7 @@
         </is>
       </c>
       <c r="C70" s="0">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D70" s="0">
         <v>2</v>
@@ -2434,7 +2434,7 @@
         </is>
       </c>
       <c r="H70" s="0">
-        <v>3.06</v>
+        <v>3.27</v>
       </c>
     </row>
     <row r="71" spans="1:8">
@@ -2449,7 +2449,7 @@
         </is>
       </c>
       <c r="C71" s="0">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D71" s="0">
         <v>2</v>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="H71" s="0">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="72" spans="1:8">
@@ -2483,7 +2483,7 @@
         </is>
       </c>
       <c r="C72" s="0">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D72" s="0">
         <v>2</v>
@@ -2502,7 +2502,7 @@
         </is>
       </c>
       <c r="H72" s="0">
-        <v>3.05</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="73" spans="1:8">
@@ -2517,10 +2517,10 @@
         </is>
       </c>
       <c r="C73" s="0">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="D73" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E73" s="0">
         <v>2026</v>
@@ -2536,7 +2536,7 @@
         </is>
       </c>
       <c r="H73" s="0">
-        <v>1</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="74" spans="1:8">
@@ -2551,10 +2551,10 @@
         </is>
       </c>
       <c r="C74" s="0">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="D74" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E74" s="0">
         <v>2026</v>
@@ -2570,7 +2570,7 @@
         </is>
       </c>
       <c r="H74" s="0">
-        <v>3.01</v>
+        <v>3.05</v>
       </c>
     </row>
     <row r="75" spans="1:8">
@@ -2585,7 +2585,7 @@
         </is>
       </c>
       <c r="C75" s="0">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D75" s="0">
         <v>1</v>
@@ -2604,7 +2604,7 @@
         </is>
       </c>
       <c r="H75" s="0">
-        <v>1.06</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76" spans="1:8">
@@ -2619,7 +2619,7 @@
         </is>
       </c>
       <c r="C76" s="0">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D76" s="0">
         <v>1</v>
@@ -2638,7 +2638,7 @@
         </is>
       </c>
       <c r="H76" s="0">
-        <v>2.97</v>
+        <v>3.01</v>
       </c>
     </row>
     <row r="77" spans="1:8">
@@ -2653,7 +2653,7 @@
         </is>
       </c>
       <c r="C77" s="0">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="D77" s="0">
         <v>1</v>
@@ -2672,7 +2672,7 @@
         </is>
       </c>
       <c r="H77" s="0">
-        <v>1.64</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="78" spans="1:8">
@@ -2687,7 +2687,7 @@
         </is>
       </c>
       <c r="C78" s="0">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="D78" s="0">
         <v>1</v>
@@ -2706,7 +2706,7 @@
         </is>
       </c>
       <c r="H78" s="0">
-        <v>3.49</v>
+        <v>2.97</v>
       </c>
     </row>
     <row r="79" spans="1:8">
@@ -2721,7 +2721,7 @@
         </is>
       </c>
       <c r="C79" s="0">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D79" s="0">
         <v>1</v>
@@ -2740,7 +2740,7 @@
         </is>
       </c>
       <c r="H79" s="0">
-        <v>2.06</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="80" spans="1:8">
@@ -2755,7 +2755,7 @@
         </is>
       </c>
       <c r="C80" s="0">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D80" s="0">
         <v>1</v>
@@ -2774,7 +2774,7 @@
         </is>
       </c>
       <c r="H80" s="0">
-        <v>3.63</v>
+        <v>3.49</v>
       </c>
     </row>
     <row r="81" spans="1:8">
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="C81" s="0">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D81" s="0">
         <v>1</v>
@@ -2808,7 +2808,7 @@
         </is>
       </c>
       <c r="H81" s="0">
-        <v>2.63</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="82" spans="1:8">
@@ -2823,7 +2823,7 @@
         </is>
       </c>
       <c r="C82" s="0">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D82" s="0">
         <v>1</v>
@@ -2842,7 +2842,7 @@
         </is>
       </c>
       <c r="H82" s="0">
-        <v>3.49</v>
+        <v>3.63</v>
       </c>
     </row>
     <row r="83" spans="1:8">
@@ -2857,13 +2857,13 @@
         </is>
       </c>
       <c r="C83" s="0">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="D83" s="0">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E83" s="0">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="F83" s="0" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
         </is>
       </c>
       <c r="H83" s="0">
-        <v>2.67</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="84" spans="1:8">
@@ -2891,13 +2891,13 @@
         </is>
       </c>
       <c r="C84" s="0">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="D84" s="0">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E84" s="0">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="F84" s="0" t="inlineStr">
         <is>
@@ -2910,13 +2910,13 @@
         </is>
       </c>
       <c r="H84" s="0">
-        <v>3.4</v>
+        <v>3.49</v>
       </c>
     </row>
     <row r="85" spans="1:8">
       <c r="A85" s="0" t="inlineStr">
         <is>
-          <t>Prata litoral primeira - produtor</t>
+          <t>Nanica primeira - produtor</t>
         </is>
       </c>
       <c r="B85" s="0" t="inlineStr">
@@ -2944,13 +2944,13 @@
         </is>
       </c>
       <c r="H85" s="0">
-        <v>3</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="86" spans="1:8">
       <c r="A86" s="0" t="inlineStr">
         <is>
-          <t>Nanica primeira - produtor</t>
+          <t>Prata anã primeira - produtor</t>
         </is>
       </c>
       <c r="B86" s="0" t="inlineStr">
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="C86" s="0">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="D86" s="0">
         <v>12</v>
@@ -2978,13 +2978,13 @@
         </is>
       </c>
       <c r="H86" s="0">
-        <v>2.83</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="87" spans="1:8">
       <c r="A87" s="0" t="inlineStr">
         <is>
-          <t>Prata anã primeira - produtor</t>
+          <t>Prata litoral primeira - produtor</t>
         </is>
       </c>
       <c r="B87" s="0" t="inlineStr">
@@ -2993,7 +2993,7 @@
         </is>
       </c>
       <c r="C87" s="0">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="D87" s="0">
         <v>12</v>
@@ -3012,7 +3012,7 @@
         </is>
       </c>
       <c r="H87" s="0">
-        <v>3.59</v>
+        <v>3</v>
       </c>
     </row>
     <row r="88" spans="1:8">
@@ -3027,7 +3027,7 @@
         </is>
       </c>
       <c r="C88" s="0">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D88" s="0">
         <v>12</v>
@@ -3046,7 +3046,7 @@
         </is>
       </c>
       <c r="H88" s="0">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
     </row>
     <row r="89" spans="1:8">
@@ -3061,7 +3061,7 @@
         </is>
       </c>
       <c r="C89" s="0">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D89" s="0">
         <v>12</v>
@@ -3080,7 +3080,7 @@
         </is>
       </c>
       <c r="H89" s="0">
-        <v>3.54</v>
+        <v>3.59</v>
       </c>
     </row>
     <row r="90" spans="1:8">
@@ -3095,7 +3095,7 @@
         </is>
       </c>
       <c r="C90" s="0">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D90" s="0">
         <v>12</v>
@@ -3114,7 +3114,7 @@
         </is>
       </c>
       <c r="H90" s="0">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="91" spans="1:8">
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="C91" s="0">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D91" s="0">
         <v>12</v>
@@ -3148,7 +3148,7 @@
         </is>
       </c>
       <c r="H91" s="0">
-        <v>3.7</v>
+        <v>3.54</v>
       </c>
     </row>
     <row r="92" spans="1:8">
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="C92" s="0">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="D92" s="0">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E92" s="0">
         <v>2025</v>
@@ -3182,7 +3182,7 @@
         </is>
       </c>
       <c r="H92" s="0">
-        <v>2.82</v>
+        <v>2.89</v>
       </c>
     </row>
     <row r="93" spans="1:8">
@@ -3197,10 +3197,10 @@
         </is>
       </c>
       <c r="C93" s="0">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="D93" s="0">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E93" s="0">
         <v>2025</v>
@@ -3231,7 +3231,7 @@
         </is>
       </c>
       <c r="C94" s="0">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D94" s="0">
         <v>11</v>
@@ -3250,7 +3250,7 @@
         </is>
       </c>
       <c r="H94" s="0">
-        <v>2.79</v>
+        <v>2.82</v>
       </c>
     </row>
     <row r="95" spans="1:8">
@@ -3265,7 +3265,7 @@
         </is>
       </c>
       <c r="C95" s="0">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D95" s="0">
         <v>11</v>
@@ -3284,7 +3284,7 @@
         </is>
       </c>
       <c r="H95" s="0">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="96" spans="1:8">
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="C96" s="0">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D96" s="0">
         <v>11</v>
@@ -3318,7 +3318,7 @@
         </is>
       </c>
       <c r="H96" s="0">
-        <v>2.67</v>
+        <v>2.79</v>
       </c>
     </row>
     <row r="97" spans="1:8">
@@ -3333,7 +3333,7 @@
         </is>
       </c>
       <c r="C97" s="0">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D97" s="0">
         <v>11</v>
@@ -3352,7 +3352,7 @@
         </is>
       </c>
       <c r="H97" s="0">
-        <v>3.59</v>
+        <v>3.58</v>
       </c>
     </row>
     <row r="98" spans="1:8">
@@ -3367,7 +3367,7 @@
         </is>
       </c>
       <c r="C98" s="0">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D98" s="0">
         <v>11</v>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="H98" s="0">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="99" spans="1:8">
@@ -3401,7 +3401,7 @@
         </is>
       </c>
       <c r="C99" s="0">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D99" s="0">
         <v>11</v>
@@ -3420,7 +3420,7 @@
         </is>
       </c>
       <c r="H99" s="0">
-        <v>3.2</v>
+        <v>3.59</v>
       </c>
     </row>
     <row r="100" spans="1:8">
@@ -3435,10 +3435,10 @@
         </is>
       </c>
       <c r="C100" s="0">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="D100" s="0">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E100" s="0">
         <v>2025</v>
@@ -3454,7 +3454,7 @@
         </is>
       </c>
       <c r="H100" s="0">
-        <v>2.98</v>
+        <v>2.68</v>
       </c>
     </row>
     <row r="101" spans="1:8">
@@ -3469,10 +3469,10 @@
         </is>
       </c>
       <c r="C101" s="0">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="D101" s="0">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E101" s="0">
         <v>2025</v>
@@ -3488,7 +3488,7 @@
         </is>
       </c>
       <c r="H101" s="0">
-        <v>2.43</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="102" spans="1:8">
@@ -3503,7 +3503,7 @@
         </is>
       </c>
       <c r="C102" s="0">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="D102" s="0">
         <v>10</v>
@@ -3522,7 +3522,7 @@
         </is>
       </c>
       <c r="H102" s="0">
-        <v>2.77</v>
+        <v>2.98</v>
       </c>
     </row>
     <row r="103" spans="1:8">
@@ -3537,7 +3537,7 @@
         </is>
       </c>
       <c r="C103" s="0">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="D103" s="0">
         <v>10</v>
@@ -3556,7 +3556,7 @@
         </is>
       </c>
       <c r="H103" s="0">
-        <v>2.25</v>
+        <v>2.43</v>
       </c>
     </row>
     <row r="104" spans="1:8">
@@ -3571,7 +3571,7 @@
         </is>
       </c>
       <c r="C104" s="0">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D104" s="0">
         <v>10</v>
@@ -3590,7 +3590,7 @@
         </is>
       </c>
       <c r="H104" s="0">
-        <v>2.88</v>
+        <v>2.77</v>
       </c>
     </row>
     <row r="105" spans="1:8">
@@ -3605,7 +3605,7 @@
         </is>
       </c>
       <c r="C105" s="0">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D105" s="0">
         <v>10</v>
@@ -3624,7 +3624,7 @@
         </is>
       </c>
       <c r="H105" s="0">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="106" spans="1:8">
@@ -3639,7 +3639,7 @@
         </is>
       </c>
       <c r="C106" s="0">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D106" s="0">
         <v>10</v>
@@ -3658,7 +3658,7 @@
         </is>
       </c>
       <c r="H106" s="0">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="107" spans="1:8">
@@ -3673,7 +3673,7 @@
         </is>
       </c>
       <c r="C107" s="0">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D107" s="0">
         <v>10</v>
@@ -3692,7 +3692,7 @@
         </is>
       </c>
       <c r="H107" s="0">
-        <v>2.37</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="108" spans="1:8">
@@ -3707,7 +3707,7 @@
         </is>
       </c>
       <c r="C108" s="0">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D108" s="0">
         <v>10</v>
@@ -3726,7 +3726,7 @@
         </is>
       </c>
       <c r="H108" s="0">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
     </row>
     <row r="109" spans="1:8">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="C109" s="0">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D109" s="0">
         <v>10</v>
@@ -3760,7 +3760,7 @@
         </is>
       </c>
       <c r="H109" s="0">
-        <v>2.6</v>
+        <v>2.37</v>
       </c>
     </row>
     <row r="110" spans="1:8">
@@ -3775,10 +3775,10 @@
         </is>
       </c>
       <c r="C110" s="0">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="D110" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E110" s="0">
         <v>2025</v>
@@ -3794,7 +3794,7 @@
         </is>
       </c>
       <c r="H110" s="0">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
     </row>
     <row r="111" spans="1:8">
@@ -3809,10 +3809,10 @@
         </is>
       </c>
       <c r="C111" s="0">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="D111" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E111" s="0">
         <v>2025</v>
@@ -3828,7 +3828,7 @@
         </is>
       </c>
       <c r="H111" s="0">
-        <v>3.11</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="112" spans="1:8">
@@ -3843,7 +3843,7 @@
         </is>
       </c>
       <c r="C112" s="0">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D112" s="0">
         <v>9</v>
@@ -3862,7 +3862,7 @@
         </is>
       </c>
       <c r="H112" s="0">
-        <v>3.03</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="113" spans="1:8">
@@ -3877,7 +3877,7 @@
         </is>
       </c>
       <c r="C113" s="0">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D113" s="0">
         <v>9</v>
@@ -3896,7 +3896,7 @@
         </is>
       </c>
       <c r="H113" s="0">
-        <v>3.77</v>
+        <v>3.11</v>
       </c>
     </row>
     <row r="114" spans="1:8">
@@ -3911,7 +3911,7 @@
         </is>
       </c>
       <c r="C114" s="0">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D114" s="0">
         <v>9</v>
@@ -3930,7 +3930,7 @@
         </is>
       </c>
       <c r="H114" s="0">
-        <v>2.96</v>
+        <v>3.03</v>
       </c>
     </row>
     <row r="115" spans="1:8">
@@ -3945,7 +3945,7 @@
         </is>
       </c>
       <c r="C115" s="0">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D115" s="0">
         <v>9</v>
@@ -3964,7 +3964,7 @@
         </is>
       </c>
       <c r="H115" s="0">
-        <v>3.61</v>
+        <v>3.77</v>
       </c>
     </row>
     <row r="116" spans="1:8">
@@ -3979,7 +3979,7 @@
         </is>
       </c>
       <c r="C116" s="0">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D116" s="0">
         <v>9</v>
@@ -3998,7 +3998,7 @@
         </is>
       </c>
       <c r="H116" s="0">
-        <v>2.84</v>
+        <v>2.96</v>
       </c>
     </row>
     <row r="117" spans="1:8">
@@ -4013,7 +4013,7 @@
         </is>
       </c>
       <c r="C117" s="0">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D117" s="0">
         <v>9</v>
@@ -4032,7 +4032,7 @@
         </is>
       </c>
       <c r="H117" s="0">
-        <v>3.48</v>
+        <v>3.61</v>
       </c>
     </row>
     <row r="118" spans="1:8">
@@ -4047,10 +4047,10 @@
         </is>
       </c>
       <c r="C118" s="0">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="D118" s="0">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E118" s="0">
         <v>2025</v>
@@ -4066,7 +4066,7 @@
         </is>
       </c>
       <c r="H118" s="0">
-        <v>3.12</v>
+        <v>2.84</v>
       </c>
     </row>
     <row r="119" spans="1:8">
@@ -4081,10 +4081,10 @@
         </is>
       </c>
       <c r="C119" s="0">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="D119" s="0">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E119" s="0">
         <v>2025</v>
@@ -4100,7 +4100,7 @@
         </is>
       </c>
       <c r="H119" s="0">
-        <v>3.72</v>
+        <v>3.48</v>
       </c>
     </row>
     <row r="120" spans="1:8">
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="C120" s="0">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D120" s="0">
         <v>8</v>
@@ -4134,7 +4134,7 @@
         </is>
       </c>
       <c r="H120" s="0">
-        <v>3.06</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="121" spans="1:8">
@@ -4149,7 +4149,7 @@
         </is>
       </c>
       <c r="C121" s="0">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D121" s="0">
         <v>8</v>
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="H121" s="0">
-        <v>3.6</v>
+        <v>3.72</v>
       </c>
     </row>
     <row r="122" spans="1:8">
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="C122" s="0">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D122" s="0">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         </is>
       </c>
       <c r="C123" s="0">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D123" s="0">
         <v>8</v>
@@ -4236,7 +4236,7 @@
         </is>
       </c>
       <c r="H123" s="0">
-        <v>3.67</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="124" spans="1:8">
@@ -4251,7 +4251,7 @@
         </is>
       </c>
       <c r="C124" s="0">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D124" s="0">
         <v>8</v>
@@ -4270,7 +4270,7 @@
         </is>
       </c>
       <c r="H124" s="0">
-        <v>2.73</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="125" spans="1:8">
@@ -4285,7 +4285,7 @@
         </is>
       </c>
       <c r="C125" s="0">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D125" s="0">
         <v>8</v>
@@ -4304,7 +4304,7 @@
         </is>
       </c>
       <c r="H125" s="0">
-        <v>3.3</v>
+        <v>3.67</v>
       </c>
     </row>
     <row r="126" spans="1:8">
@@ -4319,10 +4319,10 @@
         </is>
       </c>
       <c r="C126" s="0">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="D126" s="0">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E126" s="0">
         <v>2025</v>
@@ -4338,7 +4338,7 @@
         </is>
       </c>
       <c r="H126" s="0">
-        <v>2.3</v>
+        <v>2.73</v>
       </c>
     </row>
     <row r="127" spans="1:8">
@@ -4353,10 +4353,10 @@
         </is>
       </c>
       <c r="C127" s="0">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="D127" s="0">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E127" s="0">
         <v>2025</v>
@@ -4372,7 +4372,7 @@
         </is>
       </c>
       <c r="H127" s="0">
-        <v>3.16</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="128" spans="1:8">
@@ -4387,7 +4387,7 @@
         </is>
       </c>
       <c r="C128" s="0">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D128" s="0">
         <v>7</v>
@@ -4406,7 +4406,7 @@
         </is>
       </c>
       <c r="H128" s="0">
-        <v>1.61</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="129" spans="1:8">
@@ -4421,7 +4421,7 @@
         </is>
       </c>
       <c r="C129" s="0">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D129" s="0">
         <v>7</v>
@@ -4440,7 +4440,7 @@
         </is>
       </c>
       <c r="H129" s="0">
-        <v>2.97</v>
+        <v>3.16</v>
       </c>
     </row>
     <row r="130" spans="1:8">
@@ -4455,7 +4455,7 @@
         </is>
       </c>
       <c r="C130" s="0">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D130" s="0">
         <v>7</v>
@@ -4474,7 +4474,7 @@
         </is>
       </c>
       <c r="H130" s="0">
-        <v>1.4</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="131" spans="1:8">
@@ -4489,7 +4489,7 @@
         </is>
       </c>
       <c r="C131" s="0">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D131" s="0">
         <v>7</v>
@@ -4508,7 +4508,7 @@
         </is>
       </c>
       <c r="H131" s="0">
-        <v>2.79</v>
+        <v>2.97</v>
       </c>
     </row>
     <row r="132" spans="1:8">
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="C132" s="0">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="D132" s="0">
         <v>7</v>
@@ -4542,7 +4542,7 @@
         </is>
       </c>
       <c r="H132" s="0">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="133" spans="1:8">
@@ -4557,7 +4557,7 @@
         </is>
       </c>
       <c r="C133" s="0">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="D133" s="0">
         <v>7</v>
@@ -4576,7 +4576,7 @@
         </is>
       </c>
       <c r="H133" s="0">
-        <v>2.69</v>
+        <v>2.79</v>
       </c>
     </row>
     <row r="134" spans="1:8">
@@ -4591,7 +4591,7 @@
         </is>
       </c>
       <c r="C134" s="0">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D134" s="0">
         <v>7</v>
@@ -4610,7 +4610,7 @@
         </is>
       </c>
       <c r="H134" s="0">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="135" spans="1:8">
@@ -4625,7 +4625,7 @@
         </is>
       </c>
       <c r="C135" s="0">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D135" s="0">
         <v>7</v>
@@ -4644,7 +4644,7 @@
         </is>
       </c>
       <c r="H135" s="0">
-        <v>2.82</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="136" spans="1:8">
@@ -4659,10 +4659,10 @@
         </is>
       </c>
       <c r="C136" s="0">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="D136" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E136" s="0">
         <v>2025</v>
@@ -4678,7 +4678,7 @@
         </is>
       </c>
       <c r="H136" s="0">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="137" spans="1:8">
@@ -4693,10 +4693,10 @@
         </is>
       </c>
       <c r="C137" s="0">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="D137" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E137" s="0">
         <v>2025</v>
@@ -4712,7 +4712,7 @@
         </is>
       </c>
       <c r="H137" s="0">
-        <v>2.73</v>
+        <v>2.82</v>
       </c>
     </row>
     <row r="138" spans="1:8">
@@ -4727,7 +4727,7 @@
         </is>
       </c>
       <c r="C138" s="0">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D138" s="0">
         <v>6</v>
@@ -4746,7 +4746,7 @@
         </is>
       </c>
       <c r="H138" s="0">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="139" spans="1:8">
@@ -4761,7 +4761,7 @@
         </is>
       </c>
       <c r="C139" s="0">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D139" s="0">
         <v>6</v>
@@ -4780,7 +4780,7 @@
         </is>
       </c>
       <c r="H139" s="0">
-        <v>2.57</v>
+        <v>2.73</v>
       </c>
     </row>
     <row r="140" spans="1:8">
@@ -4795,7 +4795,7 @@
         </is>
       </c>
       <c r="C140" s="0">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D140" s="0">
         <v>6</v>
@@ -4814,7 +4814,7 @@
         </is>
       </c>
       <c r="H140" s="0">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="141" spans="1:8">
@@ -4829,7 +4829,7 @@
         </is>
       </c>
       <c r="C141" s="0">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D141" s="0">
         <v>6</v>
@@ -4848,7 +4848,7 @@
         </is>
       </c>
       <c r="H141" s="0">
-        <v>2.4</v>
+        <v>2.57</v>
       </c>
     </row>
     <row r="142" spans="1:8">
@@ -4863,7 +4863,7 @@
         </is>
       </c>
       <c r="C142" s="0">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D142" s="0">
         <v>6</v>
@@ -4882,7 +4882,7 @@
         </is>
       </c>
       <c r="H142" s="0">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="143" spans="1:8">
@@ -4897,7 +4897,7 @@
         </is>
       </c>
       <c r="C143" s="0">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D143" s="0">
         <v>6</v>
@@ -4916,7 +4916,7 @@
         </is>
       </c>
       <c r="H143" s="0">
-        <v>2.23</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="144" spans="1:8">
@@ -4931,10 +4931,10 @@
         </is>
       </c>
       <c r="C144" s="0">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="D144" s="0">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E144" s="0">
         <v>2025</v>
@@ -4950,7 +4950,7 @@
         </is>
       </c>
       <c r="H144" s="0">
-        <v>0.73</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="145" spans="1:8">
@@ -4965,10 +4965,10 @@
         </is>
       </c>
       <c r="C145" s="0">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="D145" s="0">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E145" s="0">
         <v>2025</v>
@@ -4999,7 +4999,7 @@
         </is>
       </c>
       <c r="C146" s="0">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D146" s="0">
         <v>5</v>
@@ -5018,7 +5018,7 @@
         </is>
       </c>
       <c r="H146" s="0">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="147" spans="1:8">
@@ -5033,7 +5033,7 @@
         </is>
       </c>
       <c r="C147" s="0">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D147" s="0">
         <v>5</v>
@@ -5052,7 +5052,7 @@
         </is>
       </c>
       <c r="H147" s="0">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="148" spans="1:8">
@@ -5067,7 +5067,7 @@
         </is>
       </c>
       <c r="C148" s="0">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="D148" s="0">
         <v>5</v>
@@ -5086,7 +5086,7 @@
         </is>
       </c>
       <c r="H148" s="0">
-        <v>0.89</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="149" spans="1:8">
@@ -5101,7 +5101,7 @@
         </is>
       </c>
       <c r="C149" s="0">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="D149" s="0">
         <v>5</v>
@@ -5120,7 +5120,7 @@
         </is>
       </c>
       <c r="H149" s="0">
-        <v>2.53</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="150" spans="1:8">
@@ -5135,7 +5135,7 @@
         </is>
       </c>
       <c r="C150" s="0">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D150" s="0">
         <v>5</v>
@@ -5154,7 +5154,7 @@
         </is>
       </c>
       <c r="H150" s="0">
-        <v>1.01</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="151" spans="1:8">
@@ -5169,7 +5169,7 @@
         </is>
       </c>
       <c r="C151" s="0">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D151" s="0">
         <v>5</v>
@@ -5188,7 +5188,7 @@
         </is>
       </c>
       <c r="H151" s="0">
-        <v>2.66</v>
+        <v>2.53</v>
       </c>
     </row>
     <row r="152" spans="1:8">
@@ -5203,7 +5203,7 @@
         </is>
       </c>
       <c r="C152" s="0">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D152" s="0">
         <v>5</v>
@@ -5222,7 +5222,7 @@
         </is>
       </c>
       <c r="H152" s="0">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="153" spans="1:8">
@@ -5237,7 +5237,7 @@
         </is>
       </c>
       <c r="C153" s="0">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D153" s="0">
         <v>5</v>
@@ -5256,7 +5256,7 @@
         </is>
       </c>
       <c r="H153" s="0">
-        <v>3.19</v>
+        <v>2.66</v>
       </c>
     </row>
     <row r="154" spans="1:8">
@@ -5271,10 +5271,10 @@
         </is>
       </c>
       <c r="C154" s="0">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="D154" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E154" s="0">
         <v>2025</v>
@@ -5290,7 +5290,7 @@
         </is>
       </c>
       <c r="H154" s="0">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="155" spans="1:8">
@@ -5305,10 +5305,10 @@
         </is>
       </c>
       <c r="C155" s="0">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="D155" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E155" s="0">
         <v>2025</v>
@@ -5324,7 +5324,7 @@
         </is>
       </c>
       <c r="H155" s="0">
-        <v>3.26</v>
+        <v>3.19</v>
       </c>
     </row>
     <row r="156" spans="1:8">
@@ -5339,7 +5339,7 @@
         </is>
       </c>
       <c r="C156" s="0">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D156" s="0">
         <v>4</v>
@@ -5358,7 +5358,7 @@
         </is>
       </c>
       <c r="H156" s="0">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="157" spans="1:8">
@@ -5373,7 +5373,7 @@
         </is>
       </c>
       <c r="C157" s="0">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D157" s="0">
         <v>4</v>
@@ -5392,7 +5392,7 @@
         </is>
       </c>
       <c r="H157" s="0">
-        <v>3.12</v>
+        <v>3.26</v>
       </c>
     </row>
     <row r="158" spans="1:8">
@@ -5407,7 +5407,7 @@
         </is>
       </c>
       <c r="C158" s="0">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D158" s="0">
         <v>4</v>
@@ -5426,7 +5426,7 @@
         </is>
       </c>
       <c r="H158" s="0">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="159" spans="1:8">
@@ -5441,7 +5441,7 @@
         </is>
       </c>
       <c r="C159" s="0">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D159" s="0">
         <v>4</v>
@@ -5460,7 +5460,7 @@
         </is>
       </c>
       <c r="H159" s="0">
-        <v>2.94</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="160" spans="1:8">
@@ -5475,7 +5475,7 @@
         </is>
       </c>
       <c r="C160" s="0">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D160" s="0">
         <v>4</v>
@@ -5494,7 +5494,7 @@
         </is>
       </c>
       <c r="H160" s="0">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="161" spans="1:8">
@@ -5509,7 +5509,7 @@
         </is>
       </c>
       <c r="C161" s="0">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D161" s="0">
         <v>4</v>
@@ -5528,7 +5528,7 @@
         </is>
       </c>
       <c r="H161" s="0">
-        <v>2.81</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="162" spans="1:8">
@@ -5543,10 +5543,10 @@
         </is>
       </c>
       <c r="C162" s="0">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="D162" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E162" s="0">
         <v>2025</v>
@@ -5562,7 +5562,7 @@
         </is>
       </c>
       <c r="H162" s="0">
-        <v>1.51</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="163" spans="1:8">
@@ -5577,10 +5577,10 @@
         </is>
       </c>
       <c r="C163" s="0">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="D163" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E163" s="0">
         <v>2025</v>
@@ -5596,7 +5596,7 @@
         </is>
       </c>
       <c r="H163" s="0">
-        <v>3.18</v>
+        <v>2.81</v>
       </c>
     </row>
     <row r="164" spans="1:8">
@@ -5611,7 +5611,7 @@
         </is>
       </c>
       <c r="C164" s="0">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D164" s="0">
         <v>3</v>
@@ -5630,7 +5630,7 @@
         </is>
       </c>
       <c r="H164" s="0">
-        <v>1.6</v>
+        <v>1.51</v>
       </c>
     </row>
     <row r="165" spans="1:8">
@@ -5645,7 +5645,7 @@
         </is>
       </c>
       <c r="C165" s="0">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D165" s="0">
         <v>3</v>
@@ -5664,7 +5664,7 @@
         </is>
       </c>
       <c r="H165" s="0">
-        <v>3.58</v>
+        <v>3.18</v>
       </c>
     </row>
     <row r="166" spans="1:8">
@@ -5679,7 +5679,7 @@
         </is>
       </c>
       <c r="C166" s="0">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D166" s="0">
         <v>3</v>
@@ -5698,7 +5698,7 @@
         </is>
       </c>
       <c r="H166" s="0">
-        <v>1.69</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="167" spans="1:8">
@@ -5713,7 +5713,7 @@
         </is>
       </c>
       <c r="C167" s="0">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D167" s="0">
         <v>3</v>
@@ -5732,7 +5732,7 @@
         </is>
       </c>
       <c r="H167" s="0">
-        <v>3.75</v>
+        <v>3.58</v>
       </c>
     </row>
     <row r="168" spans="1:8">
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="C168" s="0">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D168" s="0">
         <v>3</v>
@@ -5766,7 +5766,7 @@
         </is>
       </c>
       <c r="H168" s="0">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="169" spans="1:8">
@@ -5781,7 +5781,7 @@
         </is>
       </c>
       <c r="C169" s="0">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D169" s="0">
         <v>3</v>
@@ -5800,7 +5800,7 @@
         </is>
       </c>
       <c r="H169" s="0">
-        <v>3.59</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="170" spans="1:8">
@@ -5815,10 +5815,10 @@
         </is>
       </c>
       <c r="C170" s="0">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="D170" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E170" s="0">
         <v>2025</v>
@@ -5834,7 +5834,7 @@
         </is>
       </c>
       <c r="H170" s="0">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="171" spans="1:8">
@@ -5849,10 +5849,10 @@
         </is>
       </c>
       <c r="C171" s="0">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="D171" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E171" s="0">
         <v>2025</v>
@@ -5868,7 +5868,7 @@
         </is>
       </c>
       <c r="H171" s="0">
-        <v>3.66</v>
+        <v>3.59</v>
       </c>
     </row>
     <row r="172" spans="1:8">
@@ -5883,7 +5883,7 @@
         </is>
       </c>
       <c r="C172" s="0">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D172" s="0">
         <v>2</v>
@@ -5902,7 +5902,7 @@
         </is>
       </c>
       <c r="H172" s="0">
-        <v>1.87</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="173" spans="1:8">
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="C173" s="0">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D173" s="0">
         <v>2</v>
@@ -5936,7 +5936,7 @@
         </is>
       </c>
       <c r="H173" s="0">
-        <v>3.71</v>
+        <v>3.66</v>
       </c>
     </row>
     <row r="174" spans="1:8">
@@ -5951,7 +5951,7 @@
         </is>
       </c>
       <c r="C174" s="0">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D174" s="0">
         <v>2</v>
@@ -5970,7 +5970,7 @@
         </is>
       </c>
       <c r="H174" s="0">
-        <v>1.69</v>
+        <v>1.87</v>
       </c>
     </row>
     <row r="175" spans="1:8">
@@ -5985,7 +5985,7 @@
         </is>
       </c>
       <c r="C175" s="0">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D175" s="0">
         <v>2</v>
@@ -6004,7 +6004,7 @@
         </is>
       </c>
       <c r="H175" s="0">
-        <v>3.79</v>
+        <v>3.71</v>
       </c>
     </row>
     <row r="176" spans="1:8">
@@ -6019,7 +6019,7 @@
         </is>
       </c>
       <c r="C176" s="0">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D176" s="0">
         <v>2</v>
@@ -6038,7 +6038,7 @@
         </is>
       </c>
       <c r="H176" s="0">
-        <v>1.53</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="177" spans="1:8">
@@ -6053,7 +6053,7 @@
         </is>
       </c>
       <c r="C177" s="0">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D177" s="0">
         <v>2</v>
@@ -6072,7 +6072,7 @@
         </is>
       </c>
       <c r="H177" s="0">
-        <v>3.42</v>
+        <v>3.79</v>
       </c>
     </row>
     <row r="178" spans="1:8">
@@ -6087,10 +6087,10 @@
         </is>
       </c>
       <c r="C178" s="0">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="D178" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E178" s="0">
         <v>2025</v>
@@ -6106,7 +6106,7 @@
         </is>
       </c>
       <c r="H178" s="0">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
     </row>
     <row r="179" spans="1:8">
@@ -6121,10 +6121,10 @@
         </is>
       </c>
       <c r="C179" s="0">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="D179" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E179" s="0">
         <v>2025</v>
@@ -6140,7 +6140,7 @@
         </is>
       </c>
       <c r="H179" s="0">
-        <v>3.37</v>
+        <v>3.42</v>
       </c>
     </row>
     <row r="180" spans="1:8">
@@ -6155,7 +6155,7 @@
         </is>
       </c>
       <c r="C180" s="0">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="D180" s="0">
         <v>1</v>
@@ -6174,7 +6174,7 @@
         </is>
       </c>
       <c r="H180" s="0">
-        <v>1.74</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="181" spans="1:8">
@@ -6189,7 +6189,7 @@
         </is>
       </c>
       <c r="C181" s="0">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="D181" s="0">
         <v>1</v>
@@ -6208,7 +6208,7 @@
         </is>
       </c>
       <c r="H181" s="0">
-        <v>3.6</v>
+        <v>3.37</v>
       </c>
     </row>
     <row r="182" spans="1:8">
@@ -6223,7 +6223,7 @@
         </is>
       </c>
       <c r="C182" s="0">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D182" s="0">
         <v>1</v>
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="H182" s="0">
-        <v>1.88</v>
+        <v>1.74</v>
       </c>
     </row>
     <row r="183" spans="1:8">
@@ -6257,7 +6257,7 @@
         </is>
       </c>
       <c r="C183" s="0">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D183" s="0">
         <v>1</v>
@@ -6276,7 +6276,7 @@
         </is>
       </c>
       <c r="H183" s="0">
-        <v>3.68</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="184" spans="1:8">
@@ -6291,7 +6291,7 @@
         </is>
       </c>
       <c r="C184" s="0">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D184" s="0">
         <v>1</v>
@@ -6310,7 +6310,7 @@
         </is>
       </c>
       <c r="H184" s="0">
-        <v>1.96</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="185" spans="1:8">
@@ -6325,7 +6325,7 @@
         </is>
       </c>
       <c r="C185" s="0">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D185" s="0">
         <v>1</v>
@@ -6344,7 +6344,7 @@
         </is>
       </c>
       <c r="H185" s="0">
-        <v>3.25</v>
+        <v>3.68</v>
       </c>
     </row>
     <row r="186" spans="1:8">
@@ -6359,7 +6359,7 @@
         </is>
       </c>
       <c r="C186" s="0">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D186" s="0">
         <v>1</v>
@@ -6378,7 +6378,7 @@
         </is>
       </c>
       <c r="H186" s="0">
-        <v>2.33</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="187" spans="1:8">
@@ -6393,7 +6393,7 @@
         </is>
       </c>
       <c r="C187" s="0">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D187" s="0">
         <v>1</v>
@@ -6412,7 +6412,7 @@
         </is>
       </c>
       <c r="H187" s="0">
-        <v>3.02</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="188" spans="1:8">
@@ -6427,13 +6427,13 @@
         </is>
       </c>
       <c r="C188" s="0">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="D188" s="0">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E188" s="0">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="F188" s="0" t="inlineStr">
         <is>
@@ -6461,13 +6461,13 @@
         </is>
       </c>
       <c r="C189" s="0">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="D189" s="0">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E189" s="0">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="F189" s="0" t="inlineStr">
         <is>
@@ -6495,7 +6495,7 @@
         </is>
       </c>
       <c r="C190" s="0">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="D190" s="0">
         <v>12</v>
@@ -6514,7 +6514,7 @@
         </is>
       </c>
       <c r="H190" s="0">
-        <v>2.49</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="191" spans="1:8">
@@ -6529,7 +6529,7 @@
         </is>
       </c>
       <c r="C191" s="0">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="D191" s="0">
         <v>12</v>
@@ -6548,7 +6548,7 @@
         </is>
       </c>
       <c r="H191" s="0">
-        <v>3</v>
+        <v>3.02</v>
       </c>
     </row>
     <row r="192" spans="1:8">
@@ -6563,7 +6563,7 @@
         </is>
       </c>
       <c r="C192" s="0">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D192" s="0">
         <v>12</v>
@@ -6582,7 +6582,7 @@
         </is>
       </c>
       <c r="H192" s="0">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="193" spans="1:8">
@@ -6597,7 +6597,7 @@
         </is>
       </c>
       <c r="C193" s="0">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D193" s="0">
         <v>12</v>
@@ -6616,7 +6616,7 @@
         </is>
       </c>
       <c r="H193" s="0">
-        <v>3.04</v>
+        <v>3</v>
       </c>
     </row>
     <row r="194" spans="1:8">
@@ -6631,7 +6631,7 @@
         </is>
       </c>
       <c r="C194" s="0">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D194" s="0">
         <v>12</v>
@@ -6650,7 +6650,7 @@
         </is>
       </c>
       <c r="H194" s="0">
-        <v>2.61</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="195" spans="1:8">
@@ -6665,7 +6665,7 @@
         </is>
       </c>
       <c r="C195" s="0">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D195" s="0">
         <v>12</v>
@@ -6684,7 +6684,7 @@
         </is>
       </c>
       <c r="H195" s="0">
-        <v>3.06</v>
+        <v>3.04</v>
       </c>
     </row>
     <row r="196" spans="1:8">
@@ -6699,10 +6699,10 @@
         </is>
       </c>
       <c r="C196" s="0">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="D196" s="0">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E196" s="0">
         <v>2024</v>
@@ -6718,7 +6718,7 @@
         </is>
       </c>
       <c r="H196" s="0">
-        <v>2.63</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="197" spans="1:8">
@@ -6733,10 +6733,10 @@
         </is>
       </c>
       <c r="C197" s="0">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="D197" s="0">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E197" s="0">
         <v>2024</v>
@@ -6752,7 +6752,7 @@
         </is>
       </c>
       <c r="H197" s="0">
-        <v>3.21</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="198" spans="1:8">
@@ -6767,7 +6767,7 @@
         </is>
       </c>
       <c r="C198" s="0">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D198" s="0">
         <v>11</v>
@@ -6786,7 +6786,7 @@
         </is>
       </c>
       <c r="H198" s="0">
-        <v>2.58</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="199" spans="1:8">
@@ -6801,7 +6801,7 @@
         </is>
       </c>
       <c r="C199" s="0">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D199" s="0">
         <v>11</v>
@@ -6820,7 +6820,7 @@
         </is>
       </c>
       <c r="H199" s="0">
-        <v>3.28</v>
+        <v>3.21</v>
       </c>
     </row>
     <row r="200" spans="1:8">
@@ -6835,7 +6835,7 @@
         </is>
       </c>
       <c r="C200" s="0">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D200" s="0">
         <v>11</v>
@@ -6854,7 +6854,7 @@
         </is>
       </c>
       <c r="H200" s="0">
-        <v>2.22</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="201" spans="1:8">
@@ -6869,7 +6869,7 @@
         </is>
       </c>
       <c r="C201" s="0">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D201" s="0">
         <v>11</v>
@@ -6888,7 +6888,7 @@
         </is>
       </c>
       <c r="H201" s="0">
-        <v>2.8</v>
+        <v>3.28</v>
       </c>
     </row>
     <row r="202" spans="1:8">
@@ -6903,7 +6903,7 @@
         </is>
       </c>
       <c r="C202" s="0">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D202" s="0">
         <v>11</v>
@@ -6937,7 +6937,7 @@
         </is>
       </c>
       <c r="C203" s="0">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D203" s="0">
         <v>11</v>
@@ -6956,7 +6956,7 @@
         </is>
       </c>
       <c r="H203" s="0">
-        <v>2.61</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="204" spans="1:8">
@@ -6971,10 +6971,10 @@
         </is>
       </c>
       <c r="C204" s="0">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="D204" s="0">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E204" s="0">
         <v>2024</v>
@@ -6990,7 +6990,7 @@
         </is>
       </c>
       <c r="H204" s="0">
-        <v>2.45</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="205" spans="1:8">
@@ -7005,10 +7005,10 @@
         </is>
       </c>
       <c r="C205" s="0">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="D205" s="0">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E205" s="0">
         <v>2024</v>
@@ -7024,7 +7024,7 @@
         </is>
       </c>
       <c r="H205" s="0">
-        <v>2.79</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="206" spans="1:8">
@@ -7039,7 +7039,7 @@
         </is>
       </c>
       <c r="C206" s="0">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D206" s="0">
         <v>10</v>
@@ -7058,7 +7058,7 @@
         </is>
       </c>
       <c r="H206" s="0">
-        <v>2.82</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="207" spans="1:8">
@@ -7073,7 +7073,7 @@
         </is>
       </c>
       <c r="C207" s="0">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D207" s="0">
         <v>10</v>
@@ -7092,7 +7092,7 @@
         </is>
       </c>
       <c r="H207" s="0">
-        <v>3</v>
+        <v>2.79</v>
       </c>
     </row>
     <row r="208" spans="1:8">
@@ -7107,7 +7107,7 @@
         </is>
       </c>
       <c r="C208" s="0">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="D208" s="0">
         <v>10</v>
@@ -7126,7 +7126,7 @@
         </is>
       </c>
       <c r="H208" s="0">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
     </row>
     <row r="209" spans="1:8">
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="C209" s="0">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="D209" s="0">
         <v>10</v>
@@ -7160,7 +7160,7 @@
         </is>
       </c>
       <c r="H209" s="0">
-        <v>3.11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="210" spans="1:8">
@@ -7175,7 +7175,7 @@
         </is>
       </c>
       <c r="C210" s="0">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D210" s="0">
         <v>10</v>
@@ -7194,7 +7194,7 @@
         </is>
       </c>
       <c r="H210" s="0">
-        <v>2.99</v>
+        <v>2.84</v>
       </c>
     </row>
     <row r="211" spans="1:8">
@@ -7209,7 +7209,7 @@
         </is>
       </c>
       <c r="C211" s="0">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D211" s="0">
         <v>10</v>
@@ -7228,7 +7228,7 @@
         </is>
       </c>
       <c r="H211" s="0">
-        <v>3.04</v>
+        <v>3.11</v>
       </c>
     </row>
     <row r="212" spans="1:8">
@@ -7243,10 +7243,10 @@
         </is>
       </c>
       <c r="C212" s="0">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="D212" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E212" s="0">
         <v>2024</v>
@@ -7262,7 +7262,7 @@
         </is>
       </c>
       <c r="H212" s="0">
-        <v>3.06</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="213" spans="1:8">
@@ -7277,10 +7277,10 @@
         </is>
       </c>
       <c r="C213" s="0">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="D213" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E213" s="0">
         <v>2024</v>
@@ -7296,7 +7296,7 @@
         </is>
       </c>
       <c r="H213" s="0">
-        <v>3.27</v>
+        <v>3.04</v>
       </c>
     </row>
     <row r="214" spans="1:8">
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="C214" s="0">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D214" s="0">
         <v>9</v>
@@ -7330,7 +7330,7 @@
         </is>
       </c>
       <c r="H214" s="0">
-        <v>3.1</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="215" spans="1:8">
@@ -7345,7 +7345,7 @@
         </is>
       </c>
       <c r="C215" s="0">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D215" s="0">
         <v>9</v>
@@ -7364,7 +7364,7 @@
         </is>
       </c>
       <c r="H215" s="0">
-        <v>3.45</v>
+        <v>3.27</v>
       </c>
     </row>
     <row r="216" spans="1:8">
@@ -7379,7 +7379,7 @@
         </is>
       </c>
       <c r="C216" s="0">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D216" s="0">
         <v>9</v>
@@ -7398,7 +7398,7 @@
         </is>
       </c>
       <c r="H216" s="0">
-        <v>2.67</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="217" spans="1:8">
@@ -7413,7 +7413,7 @@
         </is>
       </c>
       <c r="C217" s="0">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D217" s="0">
         <v>9</v>
@@ -7432,7 +7432,7 @@
         </is>
       </c>
       <c r="H217" s="0">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="218" spans="1:8">
@@ -7447,7 +7447,7 @@
         </is>
       </c>
       <c r="C218" s="0">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D218" s="0">
         <v>9</v>
@@ -7466,7 +7466,7 @@
         </is>
       </c>
       <c r="H218" s="0">
-        <v>2.42</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="219" spans="1:8">
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="C219" s="0">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D219" s="0">
         <v>9</v>
@@ -7500,7 +7500,7 @@
         </is>
       </c>
       <c r="H219" s="0">
-        <v>3.94</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="220" spans="1:8">
@@ -7515,10 +7515,10 @@
         </is>
       </c>
       <c r="C220" s="0">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="D220" s="0">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E220" s="0">
         <v>2024</v>
@@ -7534,7 +7534,7 @@
         </is>
       </c>
       <c r="H220" s="0">
-        <v>2.6</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="221" spans="1:8">
@@ -7549,10 +7549,10 @@
         </is>
       </c>
       <c r="C221" s="0">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="D221" s="0">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E221" s="0">
         <v>2024</v>
@@ -7568,7 +7568,7 @@
         </is>
       </c>
       <c r="H221" s="0">
-        <v>4.29</v>
+        <v>3.94</v>
       </c>
     </row>
     <row r="222" spans="1:8">
@@ -7583,7 +7583,7 @@
         </is>
       </c>
       <c r="C222" s="0">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D222" s="0">
         <v>8</v>
@@ -7602,7 +7602,7 @@
         </is>
       </c>
       <c r="H222" s="0">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="223" spans="1:8">
@@ -7617,7 +7617,7 @@
         </is>
       </c>
       <c r="C223" s="0">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D223" s="0">
         <v>8</v>
@@ -7636,7 +7636,7 @@
         </is>
       </c>
       <c r="H223" s="0">
-        <v>4.44</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="224" spans="1:8">
@@ -7651,7 +7651,7 @@
         </is>
       </c>
       <c r="C224" s="0">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="D224" s="0">
         <v>8</v>
@@ -7666,11 +7666,11 @@
       </c>
       <c r="G224" s="0" t="inlineStr">
         <is>
-          <t>caixa de 22 Kg</t>
+          <t>quilograma</t>
         </is>
       </c>
       <c r="H224" s="0">
-        <v>2.82</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="225" spans="1:8">
@@ -7685,7 +7685,7 @@
         </is>
       </c>
       <c r="C225" s="0">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="D225" s="0">
         <v>8</v>
@@ -7700,11 +7700,11 @@
       </c>
       <c r="G225" s="0" t="inlineStr">
         <is>
-          <t>Caixa 20 Kg</t>
+          <t>quilograma</t>
         </is>
       </c>
       <c r="H225" s="0">
-        <v>4.99</v>
+        <v>4.44</v>
       </c>
     </row>
     <row r="226" spans="1:8">
@@ -7719,7 +7719,7 @@
         </is>
       </c>
       <c r="C226" s="0">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D226" s="0">
         <v>8</v>
@@ -7738,7 +7738,7 @@
         </is>
       </c>
       <c r="H226" s="0">
-        <v>2.74</v>
+        <v>2.82</v>
       </c>
     </row>
     <row r="227" spans="1:8">
@@ -7753,7 +7753,7 @@
         </is>
       </c>
       <c r="C227" s="0">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D227" s="0">
         <v>8</v>
@@ -7772,7 +7772,7 @@
         </is>
       </c>
       <c r="H227" s="0">
-        <v>5.2</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="228" spans="1:8">
@@ -7787,7 +7787,7 @@
         </is>
       </c>
       <c r="C228" s="0">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D228" s="0">
         <v>8</v>
@@ -7806,7 +7806,7 @@
         </is>
       </c>
       <c r="H228" s="0">
-        <v>2.49</v>
+        <v>2.74</v>
       </c>
     </row>
     <row r="229" spans="1:8">
@@ -7821,7 +7821,7 @@
         </is>
       </c>
       <c r="C229" s="0">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D229" s="0">
         <v>8</v>
@@ -7840,7 +7840,7 @@
         </is>
       </c>
       <c r="H229" s="0">
-        <v>4.93</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="230" spans="1:8">
@@ -7855,10 +7855,10 @@
         </is>
       </c>
       <c r="C230" s="0">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="D230" s="0">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E230" s="0">
         <v>2024</v>
@@ -7874,7 +7874,7 @@
         </is>
       </c>
       <c r="H230" s="0">
-        <v>2.04</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="231" spans="1:8">
@@ -7889,10 +7889,10 @@
         </is>
       </c>
       <c r="C231" s="0">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="D231" s="0">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E231" s="0">
         <v>2024</v>
@@ -7908,7 +7908,7 @@
         </is>
       </c>
       <c r="H231" s="0">
-        <v>3.76</v>
+        <v>4.93</v>
       </c>
     </row>
     <row r="232" spans="1:8">
@@ -7923,7 +7923,7 @@
         </is>
       </c>
       <c r="C232" s="0">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="D232" s="0">
         <v>7</v>
@@ -7942,7 +7942,7 @@
         </is>
       </c>
       <c r="H232" s="0">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="233" spans="1:8">
@@ -7957,7 +7957,7 @@
         </is>
       </c>
       <c r="C233" s="0">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="D233" s="0">
         <v>7</v>
@@ -7976,7 +7976,7 @@
         </is>
       </c>
       <c r="H233" s="0">
-        <v>3.16</v>
+        <v>3.76</v>
       </c>
     </row>
     <row r="234" spans="1:8">
@@ -7991,7 +7991,7 @@
         </is>
       </c>
       <c r="C234" s="0">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D234" s="0">
         <v>7</v>
@@ -8010,7 +8010,7 @@
         </is>
       </c>
       <c r="H234" s="0">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
     </row>
     <row r="235" spans="1:8">
@@ -8025,7 +8025,7 @@
         </is>
       </c>
       <c r="C235" s="0">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D235" s="0">
         <v>7</v>
@@ -8044,7 +8044,7 @@
         </is>
       </c>
       <c r="H235" s="0">
-        <v>2.85</v>
+        <v>3.16</v>
       </c>
     </row>
     <row r="236" spans="1:8">
@@ -8059,7 +8059,7 @@
         </is>
       </c>
       <c r="C236" s="0">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D236" s="0">
         <v>7</v>
@@ -8093,7 +8093,7 @@
         </is>
       </c>
       <c r="C237" s="0">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D237" s="0">
         <v>7</v>
@@ -8112,7 +8112,7 @@
         </is>
       </c>
       <c r="H237" s="0">
-        <v>2.66</v>
+        <v>2.85</v>
       </c>
     </row>
     <row r="238" spans="1:8">
@@ -8127,10 +8127,10 @@
         </is>
       </c>
       <c r="C238" s="0">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="D238" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E238" s="0">
         <v>2024</v>
@@ -8142,11 +8142,11 @@
       </c>
       <c r="G238" s="0" t="inlineStr">
         <is>
-          <t>quilograma</t>
+          <t>caixa de 22 Kg</t>
         </is>
       </c>
       <c r="H238" s="0">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="239" spans="1:8">
@@ -8161,10 +8161,10 @@
         </is>
       </c>
       <c r="C239" s="0">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="D239" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E239" s="0">
         <v>2024</v>
@@ -8176,11 +8176,11 @@
       </c>
       <c r="G239" s="0" t="inlineStr">
         <is>
-          <t>quilograma</t>
+          <t>Caixa 20 Kg</t>
         </is>
       </c>
       <c r="H239" s="0">
-        <v>2.32</v>
+        <v>2.66</v>
       </c>
     </row>
     <row r="240" spans="1:8">
@@ -8195,7 +8195,7 @@
         </is>
       </c>
       <c r="C240" s="0">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D240" s="0">
         <v>6</v>
@@ -8214,7 +8214,7 @@
         </is>
       </c>
       <c r="H240" s="0">
-        <v>1.97</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="241" spans="1:8">
@@ -8229,7 +8229,7 @@
         </is>
       </c>
       <c r="C241" s="0">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D241" s="0">
         <v>6</v>
@@ -8248,7 +8248,7 @@
         </is>
       </c>
       <c r="H241" s="0">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="242" spans="1:8">
@@ -8263,7 +8263,7 @@
         </is>
       </c>
       <c r="C242" s="0">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D242" s="0">
         <v>6</v>
@@ -8282,7 +8282,7 @@
         </is>
       </c>
       <c r="H242" s="0">
-        <v>1.65</v>
+        <v>1.97</v>
       </c>
     </row>
     <row r="243" spans="1:8">
@@ -8297,7 +8297,7 @@
         </is>
       </c>
       <c r="C243" s="0">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D243" s="0">
         <v>6</v>
@@ -8316,7 +8316,7 @@
         </is>
       </c>
       <c r="H243" s="0">
-        <v>2.49</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="244" spans="1:8">
@@ -8331,7 +8331,7 @@
         </is>
       </c>
       <c r="C244" s="0">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D244" s="0">
         <v>6</v>
@@ -8350,7 +8350,7 @@
         </is>
       </c>
       <c r="H244" s="0">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="245" spans="1:8">
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="C245" s="0">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D245" s="0">
         <v>6</v>
@@ -8384,7 +8384,7 @@
         </is>
       </c>
       <c r="H245" s="0">
-        <v>2.73</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="246" spans="1:8">
@@ -8399,10 +8399,10 @@
         </is>
       </c>
       <c r="C246" s="0">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="D246" s="0">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E246" s="0">
         <v>2024</v>
@@ -8418,7 +8418,7 @@
         </is>
       </c>
       <c r="H246" s="0">
-        <v>1.17</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="247" spans="1:8">
@@ -8433,10 +8433,10 @@
         </is>
       </c>
       <c r="C247" s="0">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="D247" s="0">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E247" s="0">
         <v>2024</v>
@@ -8452,7 +8452,7 @@
         </is>
       </c>
       <c r="H247" s="0">
-        <v>3.05</v>
+        <v>2.73</v>
       </c>
     </row>
     <row r="248" spans="1:8">
@@ -8467,7 +8467,7 @@
         </is>
       </c>
       <c r="C248" s="0">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="D248" s="0">
         <v>5</v>
@@ -8486,7 +8486,7 @@
         </is>
       </c>
       <c r="H248" s="0">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="249" spans="1:8">
@@ -8501,7 +8501,7 @@
         </is>
       </c>
       <c r="C249" s="0">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="D249" s="0">
         <v>5</v>
@@ -8520,7 +8520,7 @@
         </is>
       </c>
       <c r="H249" s="0">
-        <v>2.73</v>
+        <v>3.05</v>
       </c>
     </row>
     <row r="250" spans="1:8">
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="C250" s="0">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D250" s="0">
         <v>5</v>
@@ -8569,7 +8569,7 @@
         </is>
       </c>
       <c r="C251" s="0">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D251" s="0">
         <v>5</v>
@@ -8588,7 +8588,7 @@
         </is>
       </c>
       <c r="H251" s="0">
-        <v>2.85</v>
+        <v>2.73</v>
       </c>
     </row>
     <row r="252" spans="1:8">
@@ -8603,7 +8603,7 @@
         </is>
       </c>
       <c r="C252" s="0">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D252" s="0">
         <v>5</v>
@@ -8622,7 +8622,7 @@
         </is>
       </c>
       <c r="H252" s="0">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="253" spans="1:8">
@@ -8637,7 +8637,7 @@
         </is>
       </c>
       <c r="C253" s="0">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D253" s="0">
         <v>5</v>
@@ -8656,7 +8656,7 @@
         </is>
       </c>
       <c r="H253" s="0">
-        <v>2.69</v>
+        <v>2.85</v>
       </c>
     </row>
     <row r="254" spans="1:8">
@@ -8671,7 +8671,7 @@
         </is>
       </c>
       <c r="C254" s="0">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D254" s="0">
         <v>5</v>
@@ -8690,7 +8690,7 @@
         </is>
       </c>
       <c r="H254" s="0">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="255" spans="1:8">
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="C255" s="0">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D255" s="0">
         <v>5</v>
@@ -8724,7 +8724,7 @@
         </is>
       </c>
       <c r="H255" s="0">
-        <v>2.65</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="256" spans="1:8">
@@ -8739,10 +8739,10 @@
         </is>
       </c>
       <c r="C256" s="0">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="D256" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E256" s="0">
         <v>2024</v>
@@ -8758,7 +8758,7 @@
         </is>
       </c>
       <c r="H256" s="0">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
     </row>
     <row r="257" spans="1:8">
@@ -8773,10 +8773,10 @@
         </is>
       </c>
       <c r="C257" s="0">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="D257" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E257" s="0">
         <v>2024</v>
@@ -8792,7 +8792,7 @@
         </is>
       </c>
       <c r="H257" s="0">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
     </row>
     <row r="258" spans="1:8">
@@ -8807,7 +8807,7 @@
         </is>
       </c>
       <c r="C258" s="0">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="D258" s="0">
         <v>4</v>
@@ -8826,7 +8826,7 @@
         </is>
       </c>
       <c r="H258" s="0">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
     </row>
     <row r="259" spans="1:8">
@@ -8841,7 +8841,7 @@
         </is>
       </c>
       <c r="C259" s="0">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="D259" s="0">
         <v>4</v>
@@ -8860,7 +8860,7 @@
         </is>
       </c>
       <c r="H259" s="0">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="260" spans="1:8">
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="C260" s="0">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D260" s="0">
         <v>4</v>
@@ -8894,7 +8894,7 @@
         </is>
       </c>
       <c r="H260" s="0">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="261" spans="1:8">
@@ -8909,7 +8909,7 @@
         </is>
       </c>
       <c r="C261" s="0">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D261" s="0">
         <v>4</v>
@@ -8928,7 +8928,7 @@
         </is>
       </c>
       <c r="H261" s="0">
-        <v>4.86</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="262" spans="1:8">
@@ -8943,7 +8943,7 @@
         </is>
       </c>
       <c r="C262" s="0">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D262" s="0">
         <v>4</v>
@@ -8962,7 +8962,7 @@
         </is>
       </c>
       <c r="H262" s="0">
-        <v>1.54</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="263" spans="1:8">
@@ -8977,7 +8977,7 @@
         </is>
       </c>
       <c r="C263" s="0">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D263" s="0">
         <v>4</v>
@@ -8996,7 +8996,7 @@
         </is>
       </c>
       <c r="H263" s="0">
-        <v>6.23</v>
+        <v>4.86</v>
       </c>
     </row>
     <row r="264" spans="1:8">
@@ -9011,10 +9011,10 @@
         </is>
       </c>
       <c r="C264" s="0">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="D264" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E264" s="0">
         <v>2024</v>
@@ -9030,7 +9030,7 @@
         </is>
       </c>
       <c r="H264" s="0">
-        <v>2.13</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="265" spans="1:8">
@@ -9045,10 +9045,10 @@
         </is>
       </c>
       <c r="C265" s="0">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="D265" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E265" s="0">
         <v>2024</v>
@@ -9064,7 +9064,7 @@
         </is>
       </c>
       <c r="H265" s="0">
-        <v>6.4</v>
+        <v>6.23</v>
       </c>
     </row>
     <row r="266" spans="1:8">
@@ -9079,7 +9079,7 @@
         </is>
       </c>
       <c r="C266" s="0">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D266" s="0">
         <v>3</v>
@@ -9098,7 +9098,7 @@
         </is>
       </c>
       <c r="H266" s="0">
-        <v>2.49</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="267" spans="1:8">
@@ -9113,7 +9113,7 @@
         </is>
       </c>
       <c r="C267" s="0">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D267" s="0">
         <v>3</v>
@@ -9132,7 +9132,7 @@
         </is>
       </c>
       <c r="H267" s="0">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="268" spans="1:8">
@@ -9147,7 +9147,7 @@
         </is>
       </c>
       <c r="C268" s="0">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="D268" s="0">
         <v>3</v>
@@ -9166,7 +9166,7 @@
         </is>
       </c>
       <c r="H268" s="0">
-        <v>2.64</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="269" spans="1:8">
@@ -9181,7 +9181,7 @@
         </is>
       </c>
       <c r="C269" s="0">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="D269" s="0">
         <v>3</v>
@@ -9200,13 +9200,13 @@
         </is>
       </c>
       <c r="H269" s="0">
-        <v>6.46</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="270" spans="1:8">
       <c r="A270" s="0" t="inlineStr">
         <is>
-          <t>Prata anã primeira - produtor</t>
+          <t>Nanica primeira - produtor</t>
         </is>
       </c>
       <c r="B270" s="0" t="inlineStr">
@@ -9215,7 +9215,7 @@
         </is>
       </c>
       <c r="C270" s="0">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D270" s="0">
         <v>3</v>
@@ -9234,13 +9234,13 @@
         </is>
       </c>
       <c r="H270" s="0">
-        <v>6.39</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="271" spans="1:8">
       <c r="A271" s="0" t="inlineStr">
         <is>
-          <t>Nanica primeira - produtor</t>
+          <t>Prata anã primeira - produtor</t>
         </is>
       </c>
       <c r="B271" s="0" t="inlineStr">
@@ -9249,10 +9249,10 @@
         </is>
       </c>
       <c r="C271" s="0">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="D271" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E271" s="0">
         <v>2024</v>
@@ -9268,7 +9268,7 @@
         </is>
       </c>
       <c r="H271" s="0">
-        <v>2.91</v>
+        <v>6.46</v>
       </c>
     </row>
     <row r="272" spans="1:8">
@@ -9283,10 +9283,10 @@
         </is>
       </c>
       <c r="C272" s="0">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="D272" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E272" s="0">
         <v>2024</v>
@@ -9302,7 +9302,7 @@
         </is>
       </c>
       <c r="H272" s="0">
-        <v>6.31</v>
+        <v>6.39</v>
       </c>
     </row>
     <row r="273" spans="1:8">
@@ -9317,7 +9317,7 @@
         </is>
       </c>
       <c r="C273" s="0">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D273" s="0">
         <v>2</v>
@@ -9336,7 +9336,7 @@
         </is>
       </c>
       <c r="H273" s="0">
-        <v>3.79</v>
+        <v>2.91</v>
       </c>
     </row>
     <row r="274" spans="1:8">
@@ -9351,7 +9351,7 @@
         </is>
       </c>
       <c r="C274" s="0">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D274" s="0">
         <v>2</v>
@@ -9370,7 +9370,7 @@
         </is>
       </c>
       <c r="H274" s="0">
-        <v>6.26</v>
+        <v>6.31</v>
       </c>
     </row>
     <row r="275" spans="1:8">
@@ -9385,7 +9385,7 @@
         </is>
       </c>
       <c r="C275" s="0">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="D275" s="0">
         <v>2</v>
@@ -9404,7 +9404,7 @@
         </is>
       </c>
       <c r="H275" s="0">
-        <v>4.11</v>
+        <v>3.79</v>
       </c>
     </row>
     <row r="276" spans="1:8">
@@ -9419,7 +9419,7 @@
         </is>
       </c>
       <c r="C276" s="0">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="D276" s="0">
         <v>2</v>
@@ -9438,7 +9438,7 @@
         </is>
       </c>
       <c r="H276" s="0">
-        <v>6.16</v>
+        <v>6.26</v>
       </c>
     </row>
     <row r="277" spans="1:8">
@@ -9453,7 +9453,7 @@
         </is>
       </c>
       <c r="C277" s="0">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D277" s="0">
         <v>2</v>
@@ -9472,7 +9472,7 @@
         </is>
       </c>
       <c r="H277" s="0">
-        <v>4.05</v>
+        <v>4.11</v>
       </c>
     </row>
     <row r="278" spans="1:8">
@@ -9487,7 +9487,7 @@
         </is>
       </c>
       <c r="C278" s="0">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D278" s="0">
         <v>2</v>
@@ -9506,7 +9506,7 @@
         </is>
       </c>
       <c r="H278" s="0">
-        <v>5.88</v>
+        <v>6.16</v>
       </c>
     </row>
     <row r="279" spans="1:8">
@@ -9521,7 +9521,7 @@
         </is>
       </c>
       <c r="C279" s="0">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D279" s="0">
         <v>2</v>
@@ -9540,7 +9540,7 @@
         </is>
       </c>
       <c r="H279" s="0">
-        <v>2.42</v>
+        <v>4.05</v>
       </c>
     </row>
     <row r="280" spans="1:8">
@@ -9555,7 +9555,7 @@
         </is>
       </c>
       <c r="C280" s="0">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D280" s="0">
         <v>2</v>
@@ -9574,7 +9574,7 @@
         </is>
       </c>
       <c r="H280" s="0">
-        <v>5.61</v>
+        <v>5.88</v>
       </c>
     </row>
     <row r="281" spans="1:8">
@@ -9589,10 +9589,10 @@
         </is>
       </c>
       <c r="C281" s="0">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="D281" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E281" s="0">
         <v>2024</v>
@@ -9608,7 +9608,7 @@
         </is>
       </c>
       <c r="H281" s="0">
-        <v>2.21</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="282" spans="1:8">
@@ -9623,10 +9623,10 @@
         </is>
       </c>
       <c r="C282" s="0">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="D282" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E282" s="0">
         <v>2024</v>
@@ -9642,7 +9642,7 @@
         </is>
       </c>
       <c r="H282" s="0">
-        <v>5.47</v>
+        <v>5.61</v>
       </c>
     </row>
     <row r="283" spans="1:8">
@@ -9657,7 +9657,7 @@
         </is>
       </c>
       <c r="C283" s="0">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="D283" s="0">
         <v>1</v>
@@ -9676,7 +9676,7 @@
         </is>
       </c>
       <c r="H283" s="0">
-        <v>2.12</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="284" spans="1:8">
@@ -9691,7 +9691,7 @@
         </is>
       </c>
       <c r="C284" s="0">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="D284" s="0">
         <v>1</v>
@@ -9710,7 +9710,7 @@
         </is>
       </c>
       <c r="H284" s="0">
-        <v>5.5</v>
+        <v>5.47</v>
       </c>
     </row>
     <row r="285" spans="1:8">
@@ -9725,7 +9725,7 @@
         </is>
       </c>
       <c r="C285" s="0">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D285" s="0">
         <v>1</v>
@@ -9744,7 +9744,7 @@
         </is>
       </c>
       <c r="H285" s="0">
-        <v>2.4</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="286" spans="1:8">
@@ -9759,7 +9759,7 @@
         </is>
       </c>
       <c r="C286" s="0">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D286" s="0">
         <v>1</v>
@@ -9778,7 +9778,7 @@
         </is>
       </c>
       <c r="H286" s="0">
-        <v>5.46</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="287" spans="1:8">
@@ -9793,7 +9793,7 @@
         </is>
       </c>
       <c r="C287" s="0">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D287" s="0">
         <v>1</v>
@@ -9812,13 +9812,13 @@
         </is>
       </c>
       <c r="H287" s="0">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="288" spans="1:8">
       <c r="A288" s="0" t="inlineStr">
         <is>
-          <t>Nanica primeira - produtor</t>
+          <t>Prata anã primeira - produtor</t>
         </is>
       </c>
       <c r="B288" s="0" t="inlineStr">
@@ -9827,7 +9827,7 @@
         </is>
       </c>
       <c r="C288" s="0">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D288" s="0">
         <v>1</v>
@@ -9846,13 +9846,13 @@
         </is>
       </c>
       <c r="H288" s="0">
-        <v>2.42</v>
+        <v>5.46</v>
       </c>
     </row>
     <row r="289" spans="1:8">
       <c r="A289" s="0" t="inlineStr">
         <is>
-          <t>Prata anã primeira - produtor</t>
+          <t>Nanica primeira - produtor</t>
         </is>
       </c>
       <c r="B289" s="0" t="inlineStr">
@@ -9880,13 +9880,13 @@
         </is>
       </c>
       <c r="H289" s="0">
-        <v>5.47</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="290" spans="1:8">
       <c r="A290" s="0" t="inlineStr">
         <is>
-          <t>Prata anã primeira - produtor</t>
+          <t>Nanica primeira - produtor</t>
         </is>
       </c>
       <c r="B290" s="0" t="inlineStr">
@@ -9914,13 +9914,13 @@
         </is>
       </c>
       <c r="H290" s="0">
-        <v>5.47</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="291" spans="1:8">
       <c r="A291" s="0" t="inlineStr">
         <is>
-          <t>Nanica primeira - produtor</t>
+          <t>Prata anã primeira - produtor</t>
         </is>
       </c>
       <c r="B291" s="0" t="inlineStr">
@@ -9929,13 +9929,13 @@
         </is>
       </c>
       <c r="C291" s="0">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="D291" s="0">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E291" s="0">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F291" s="0" t="inlineStr">
         <is>
@@ -9948,7 +9948,7 @@
         </is>
       </c>
       <c r="H291" s="0">
-        <v>2.43</v>
+        <v>5.47</v>
       </c>
     </row>
     <row r="292" spans="1:8">
@@ -9963,13 +9963,13 @@
         </is>
       </c>
       <c r="C292" s="0">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="D292" s="0">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E292" s="0">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F292" s="0" t="inlineStr">
         <is>
@@ -9982,7 +9982,7 @@
         </is>
       </c>
       <c r="H292" s="0">
-        <v>5.5</v>
+        <v>5.47</v>
       </c>
     </row>
     <row r="293" spans="1:8">
@@ -9997,7 +9997,7 @@
         </is>
       </c>
       <c r="C293" s="0">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D293" s="0">
         <v>12</v>
@@ -10016,7 +10016,7 @@
         </is>
       </c>
       <c r="H293" s="0">
-        <v>2.36</v>
+        <v>2.43</v>
       </c>
     </row>
     <row r="294" spans="1:8">
@@ -10031,7 +10031,7 @@
         </is>
       </c>
       <c r="C294" s="0">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D294" s="0">
         <v>12</v>
@@ -10050,7 +10050,7 @@
         </is>
       </c>
       <c r="H294" s="0">
-        <v>5.44</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="295" spans="1:8">
@@ -10065,7 +10065,7 @@
         </is>
       </c>
       <c r="C295" s="0">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="D295" s="0">
         <v>12</v>
@@ -10084,7 +10084,7 @@
         </is>
       </c>
       <c r="H295" s="0">
-        <v>2.21</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="296" spans="1:8">
@@ -10099,7 +10099,7 @@
         </is>
       </c>
       <c r="C296" s="0">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="D296" s="0">
         <v>12</v>
@@ -10118,7 +10118,7 @@
         </is>
       </c>
       <c r="H296" s="0">
-        <v>5.2</v>
+        <v>5.44</v>
       </c>
     </row>
     <row r="297" spans="1:8">
@@ -10133,7 +10133,7 @@
         </is>
       </c>
       <c r="C297" s="0">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D297" s="0">
         <v>12</v>
@@ -10152,7 +10152,7 @@
         </is>
       </c>
       <c r="H297" s="0">
-        <v>2.04</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="298" spans="1:8">
@@ -10167,7 +10167,7 @@
         </is>
       </c>
       <c r="C298" s="0">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D298" s="0">
         <v>12</v>
@@ -10186,7 +10186,7 @@
         </is>
       </c>
       <c r="H298" s="0">
-        <v>4.73</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="299" spans="1:8">
@@ -10201,10 +10201,10 @@
         </is>
       </c>
       <c r="C299" s="0">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="D299" s="0">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E299" s="0">
         <v>2023</v>
@@ -10220,7 +10220,7 @@
         </is>
       </c>
       <c r="H299" s="0">
-        <v>2.3</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="300" spans="1:8">
@@ -10235,10 +10235,10 @@
         </is>
       </c>
       <c r="C300" s="0">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="D300" s="0">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E300" s="0">
         <v>2023</v>
@@ -10254,7 +10254,7 @@
         </is>
       </c>
       <c r="H300" s="0">
-        <v>3.88</v>
+        <v>4.73</v>
       </c>
     </row>
     <row r="301" spans="1:8">
@@ -10269,7 +10269,7 @@
         </is>
       </c>
       <c r="C301" s="0">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="D301" s="0">
         <v>11</v>
@@ -10288,7 +10288,7 @@
         </is>
       </c>
       <c r="H301" s="0">
-        <v>2.58</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="302" spans="1:8">
@@ -10303,7 +10303,7 @@
         </is>
       </c>
       <c r="C302" s="0">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="D302" s="0">
         <v>11</v>
@@ -10322,7 +10322,7 @@
         </is>
       </c>
       <c r="H302" s="0">
-        <v>3.8</v>
+        <v>3.88</v>
       </c>
     </row>
     <row r="303" spans="1:8">
@@ -10337,7 +10337,7 @@
         </is>
       </c>
       <c r="C303" s="0">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D303" s="0">
         <v>11</v>
@@ -10356,7 +10356,7 @@
         </is>
       </c>
       <c r="H303" s="0">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="304" spans="1:8">
@@ -10371,7 +10371,7 @@
         </is>
       </c>
       <c r="C304" s="0">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D304" s="0">
         <v>11</v>
@@ -10390,7 +10390,7 @@
         </is>
       </c>
       <c r="H304" s="0">
-        <v>3.83</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="305" spans="1:8">
@@ -10405,7 +10405,7 @@
         </is>
       </c>
       <c r="C305" s="0">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D305" s="0">
         <v>11</v>
@@ -10424,7 +10424,7 @@
         </is>
       </c>
       <c r="H305" s="0">
-        <v>2.59</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="306" spans="1:8">
@@ -10439,7 +10439,7 @@
         </is>
       </c>
       <c r="C306" s="0">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D306" s="0">
         <v>11</v>
@@ -10458,7 +10458,7 @@
         </is>
       </c>
       <c r="H306" s="0">
-        <v>3.54</v>
+        <v>3.83</v>
       </c>
     </row>
     <row r="307" spans="1:8">
@@ -10473,7 +10473,7 @@
         </is>
       </c>
       <c r="C307" s="0">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D307" s="0">
         <v>11</v>
@@ -10492,7 +10492,7 @@
         </is>
       </c>
       <c r="H307" s="0">
-        <v>2.19</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="308" spans="1:8">
@@ -10507,7 +10507,7 @@
         </is>
       </c>
       <c r="C308" s="0">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D308" s="0">
         <v>11</v>
@@ -10526,7 +10526,7 @@
         </is>
       </c>
       <c r="H308" s="0">
-        <v>2.81</v>
+        <v>3.54</v>
       </c>
     </row>
     <row r="309" spans="1:8">
@@ -10541,10 +10541,10 @@
         </is>
       </c>
       <c r="C309" s="0">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="D309" s="0">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E309" s="0">
         <v>2023</v>
@@ -10560,7 +10560,7 @@
         </is>
       </c>
       <c r="H309" s="0">
-        <v>1.98</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="310" spans="1:8">
@@ -10575,10 +10575,10 @@
         </is>
       </c>
       <c r="C310" s="0">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="D310" s="0">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E310" s="0">
         <v>2023</v>
@@ -10594,7 +10594,7 @@
         </is>
       </c>
       <c r="H310" s="0">
-        <v>2.67</v>
+        <v>2.81</v>
       </c>
     </row>
     <row r="311" spans="1:8">
@@ -10609,7 +10609,7 @@
         </is>
       </c>
       <c r="C311" s="0">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D311" s="0">
         <v>10</v>
@@ -10628,7 +10628,7 @@
         </is>
       </c>
       <c r="H311" s="0">
-        <v>2.06</v>
+        <v>1.98</v>
       </c>
     </row>
     <row r="312" spans="1:8">
@@ -10643,7 +10643,7 @@
         </is>
       </c>
       <c r="C312" s="0">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D312" s="0">
         <v>10</v>
@@ -10662,7 +10662,7 @@
         </is>
       </c>
       <c r="H312" s="0">
-        <v>2.74</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="313" spans="1:8">
@@ -10677,7 +10677,7 @@
         </is>
       </c>
       <c r="C313" s="0">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D313" s="0">
         <v>10</v>
@@ -10696,7 +10696,7 @@
         </is>
       </c>
       <c r="H313" s="0">
-        <v>1.89</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="314" spans="1:8">
@@ -10711,7 +10711,7 @@
         </is>
       </c>
       <c r="C314" s="0">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D314" s="0">
         <v>10</v>
@@ -10730,7 +10730,7 @@
         </is>
       </c>
       <c r="H314" s="0">
-        <v>2.64</v>
+        <v>2.74</v>
       </c>
     </row>
     <row r="315" spans="1:8">
@@ -10745,7 +10745,7 @@
         </is>
       </c>
       <c r="C315" s="0">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D315" s="0">
         <v>10</v>
@@ -10764,7 +10764,7 @@
         </is>
       </c>
       <c r="H315" s="0">
-        <v>1.7</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="316" spans="1:8">
@@ -10779,7 +10779,7 @@
         </is>
       </c>
       <c r="C316" s="0">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D316" s="0">
         <v>10</v>
@@ -10798,7 +10798,7 @@
         </is>
       </c>
       <c r="H316" s="0">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="317" spans="1:8">
@@ -10813,10 +10813,10 @@
         </is>
       </c>
       <c r="C317" s="0">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="D317" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E317" s="0">
         <v>2023</v>
@@ -10832,7 +10832,7 @@
         </is>
       </c>
       <c r="H317" s="0">
-        <v>1.86</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="318" spans="1:8">
@@ -10847,10 +10847,10 @@
         </is>
       </c>
       <c r="C318" s="0">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="D318" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E318" s="0">
         <v>2023</v>
@@ -10866,7 +10866,7 @@
         </is>
       </c>
       <c r="H318" s="0">
-        <v>2.59</v>
+        <v>2.66</v>
       </c>
     </row>
     <row r="319" spans="1:8">
@@ -10881,7 +10881,7 @@
         </is>
       </c>
       <c r="C319" s="0">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D319" s="0">
         <v>9</v>
@@ -10900,7 +10900,7 @@
         </is>
       </c>
       <c r="H319" s="0">
-        <v>2.34</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="320" spans="1:8">
@@ -10915,7 +10915,7 @@
         </is>
       </c>
       <c r="C320" s="0">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D320" s="0">
         <v>9</v>
@@ -10934,7 +10934,7 @@
         </is>
       </c>
       <c r="H320" s="0">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="321" spans="1:8">
@@ -10949,7 +10949,7 @@
         </is>
       </c>
       <c r="C321" s="0">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="D321" s="0">
         <v>9</v>
@@ -10968,7 +10968,7 @@
         </is>
       </c>
       <c r="H321" s="0">
-        <v>2.45</v>
+        <v>2.34</v>
       </c>
     </row>
     <row r="322" spans="1:8">
@@ -10983,7 +10983,7 @@
         </is>
       </c>
       <c r="C322" s="0">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="D322" s="0">
         <v>9</v>
@@ -11002,7 +11002,7 @@
         </is>
       </c>
       <c r="H322" s="0">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="323" spans="1:8">
@@ -11017,7 +11017,7 @@
         </is>
       </c>
       <c r="C323" s="0">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="D323" s="0">
         <v>9</v>
@@ -11036,7 +11036,7 @@
         </is>
       </c>
       <c r="H323" s="0">
-        <v>2.86</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="324" spans="1:8">
@@ -11051,7 +11051,7 @@
         </is>
       </c>
       <c r="C324" s="0">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="D324" s="0">
         <v>9</v>
@@ -11070,7 +11070,7 @@
         </is>
       </c>
       <c r="H324" s="0">
-        <v>2.69</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="325" spans="1:8">
@@ -11085,10 +11085,10 @@
         </is>
       </c>
       <c r="C325" s="0">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="D325" s="0">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E325" s="0">
         <v>2023</v>
@@ -11104,7 +11104,7 @@
         </is>
       </c>
       <c r="H325" s="0">
-        <v>3.05</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="326" spans="1:8">
@@ -11119,10 +11119,10 @@
         </is>
       </c>
       <c r="C326" s="0">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="D326" s="0">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E326" s="0">
         <v>2023</v>
@@ -11138,7 +11138,7 @@
         </is>
       </c>
       <c r="H326" s="0">
-        <v>2.86</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="327" spans="1:8">
@@ -11153,7 +11153,7 @@
         </is>
       </c>
       <c r="C327" s="0">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D327" s="0">
         <v>8</v>
@@ -11172,7 +11172,7 @@
         </is>
       </c>
       <c r="H327" s="0">
-        <v>3.26</v>
+        <v>3.05</v>
       </c>
     </row>
     <row r="328" spans="1:8">
@@ -11187,7 +11187,7 @@
         </is>
       </c>
       <c r="C328" s="0">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D328" s="0">
         <v>8</v>
@@ -11206,7 +11206,7 @@
         </is>
       </c>
       <c r="H328" s="0">
-        <v>3.06</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="329" spans="1:8">
@@ -11221,7 +11221,7 @@
         </is>
       </c>
       <c r="C329" s="0">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D329" s="0">
         <v>8</v>
@@ -11240,7 +11240,7 @@
         </is>
       </c>
       <c r="H329" s="0">
-        <v>3.2</v>
+        <v>3.26</v>
       </c>
     </row>
     <row r="330" spans="1:8">
@@ -11255,7 +11255,7 @@
         </is>
       </c>
       <c r="C330" s="0">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D330" s="0">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         </is>
       </c>
       <c r="C331" s="0">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="D331" s="0">
         <v>8</v>
@@ -11308,7 +11308,7 @@
         </is>
       </c>
       <c r="H331" s="0">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="332" spans="1:8">
@@ -11323,7 +11323,7 @@
         </is>
       </c>
       <c r="C332" s="0">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="D332" s="0">
         <v>8</v>
@@ -11342,7 +11342,7 @@
         </is>
       </c>
       <c r="H332" s="0">
-        <v>3.2</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="333" spans="1:8">
@@ -11357,7 +11357,7 @@
         </is>
       </c>
       <c r="C333" s="0">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D333" s="0">
         <v>8</v>
@@ -11376,7 +11376,7 @@
         </is>
       </c>
       <c r="H333" s="0">
-        <v>2.85</v>
+        <v>3.21</v>
       </c>
     </row>
     <row r="334" spans="1:8">
@@ -11391,7 +11391,7 @@
         </is>
       </c>
       <c r="C334" s="0">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D334" s="0">
         <v>8</v>
@@ -11410,7 +11410,7 @@
         </is>
       </c>
       <c r="H334" s="0">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="335" spans="1:8">
@@ -11425,10 +11425,10 @@
         </is>
       </c>
       <c r="C335" s="0">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="D335" s="0">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E335" s="0">
         <v>2023</v>
@@ -11444,7 +11444,7 @@
         </is>
       </c>
       <c r="H335" s="0">
-        <v>2.66</v>
+        <v>2.85</v>
       </c>
     </row>
     <row r="336" spans="1:8">
@@ -11459,10 +11459,10 @@
         </is>
       </c>
       <c r="C336" s="0">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="D336" s="0">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E336" s="0">
         <v>2023</v>
@@ -11478,7 +11478,7 @@
         </is>
       </c>
       <c r="H336" s="0">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="337" spans="1:8">
@@ -11493,7 +11493,7 @@
         </is>
       </c>
       <c r="C337" s="0">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D337" s="0">
         <v>7</v>
@@ -11512,7 +11512,7 @@
         </is>
       </c>
       <c r="H337" s="0">
-        <v>2.45</v>
+        <v>2.66</v>
       </c>
     </row>
     <row r="338" spans="1:8">
@@ -11527,7 +11527,7 @@
         </is>
       </c>
       <c r="C338" s="0">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D338" s="0">
         <v>7</v>
@@ -11546,7 +11546,7 @@
         </is>
       </c>
       <c r="H338" s="0">
-        <v>2.89</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="339" spans="1:8">
@@ -11561,7 +11561,7 @@
         </is>
       </c>
       <c r="C339" s="0">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D339" s="0">
         <v>7</v>
@@ -11580,7 +11580,7 @@
         </is>
       </c>
       <c r="H339" s="0">
-        <v>2.28</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="340" spans="1:8">
@@ -11595,7 +11595,7 @@
         </is>
       </c>
       <c r="C340" s="0">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D340" s="0">
         <v>7</v>
@@ -11614,7 +11614,7 @@
         </is>
       </c>
       <c r="H340" s="0">
-        <v>3.04</v>
+        <v>2.89</v>
       </c>
     </row>
     <row r="341" spans="1:8">
@@ -11629,7 +11629,7 @@
         </is>
       </c>
       <c r="C341" s="0">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D341" s="0">
         <v>7</v>
@@ -11648,7 +11648,7 @@
         </is>
       </c>
       <c r="H341" s="0">
-        <v>1.96</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="342" spans="1:8">
@@ -11663,7 +11663,7 @@
         </is>
       </c>
       <c r="C342" s="0">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D342" s="0">
         <v>7</v>
@@ -11682,7 +11682,7 @@
         </is>
       </c>
       <c r="H342" s="0">
-        <v>3.01</v>
+        <v>3.04</v>
       </c>
     </row>
     <row r="343" spans="1:8">
@@ -11697,10 +11697,10 @@
         </is>
       </c>
       <c r="C343" s="0">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="D343" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E343" s="0">
         <v>2023</v>
@@ -11716,7 +11716,7 @@
         </is>
       </c>
       <c r="H343" s="0">
-        <v>1.57</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="344" spans="1:8">
@@ -11731,10 +11731,10 @@
         </is>
       </c>
       <c r="C344" s="0">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="D344" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E344" s="0">
         <v>2023</v>
@@ -11750,7 +11750,7 @@
         </is>
       </c>
       <c r="H344" s="0">
-        <v>2.86</v>
+        <v>3.01</v>
       </c>
     </row>
     <row r="345" spans="1:8">
@@ -11765,7 +11765,7 @@
         </is>
       </c>
       <c r="C345" s="0">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="D345" s="0">
         <v>6</v>
@@ -11784,7 +11784,7 @@
         </is>
       </c>
       <c r="H345" s="0">
-        <v>1.42</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="346" spans="1:8">
@@ -11799,7 +11799,7 @@
         </is>
       </c>
       <c r="C346" s="0">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="D346" s="0">
         <v>6</v>
@@ -11818,7 +11818,7 @@
         </is>
       </c>
       <c r="H346" s="0">
-        <v>2.7</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="347" spans="1:8">
@@ -11833,7 +11833,7 @@
         </is>
       </c>
       <c r="C347" s="0">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="D347" s="0">
         <v>6</v>
@@ -11852,7 +11852,7 @@
         </is>
       </c>
       <c r="H347" s="0">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="348" spans="1:8">
@@ -11867,7 +11867,7 @@
         </is>
       </c>
       <c r="C348" s="0">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="D348" s="0">
         <v>6</v>
@@ -11886,7 +11886,7 @@
         </is>
       </c>
       <c r="H348" s="0">
-        <v>2.61</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="349" spans="1:8">
@@ -11901,7 +11901,7 @@
         </is>
       </c>
       <c r="C349" s="0">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="D349" s="0">
         <v>6</v>
@@ -11920,7 +11920,7 @@
         </is>
       </c>
       <c r="H349" s="0">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="350" spans="1:8">
@@ -11935,7 +11935,7 @@
         </is>
       </c>
       <c r="C350" s="0">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="D350" s="0">
         <v>6</v>
@@ -11954,7 +11954,7 @@
         </is>
       </c>
       <c r="H350" s="0">
-        <v>2.64</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="351" spans="1:8">
@@ -11969,7 +11969,7 @@
         </is>
       </c>
       <c r="C351" s="0">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D351" s="0">
         <v>6</v>
@@ -11988,7 +11988,7 @@
         </is>
       </c>
       <c r="H351" s="0">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="352" spans="1:8">
@@ -12003,7 +12003,7 @@
         </is>
       </c>
       <c r="C352" s="0">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D352" s="0">
         <v>6</v>
@@ -12022,7 +12022,7 @@
         </is>
       </c>
       <c r="H352" s="0">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="353" spans="1:8">
@@ -12037,10 +12037,10 @@
         </is>
       </c>
       <c r="C353" s="0">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="D353" s="0">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E353" s="0">
         <v>2023</v>
@@ -12056,7 +12056,7 @@
         </is>
       </c>
       <c r="H353" s="0">
-        <v>1.57</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="354" spans="1:8">
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="C354" s="0">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="D354" s="0">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E354" s="0">
         <v>2023</v>
@@ -12090,7 +12090,7 @@
         </is>
       </c>
       <c r="H354" s="0">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="355" spans="1:8">
@@ -12105,7 +12105,7 @@
         </is>
       </c>
       <c r="C355" s="0">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="D355" s="0">
         <v>5</v>
@@ -12124,7 +12124,7 @@
         </is>
       </c>
       <c r="H355" s="0">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="356" spans="1:8">
@@ -12139,7 +12139,7 @@
         </is>
       </c>
       <c r="C356" s="0">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="D356" s="0">
         <v>5</v>
@@ -12158,7 +12158,7 @@
         </is>
       </c>
       <c r="H356" s="0">
-        <v>2.47</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="357" spans="1:8">
@@ -12173,7 +12173,7 @@
         </is>
       </c>
       <c r="C357" s="0">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D357" s="0">
         <v>5</v>
@@ -12192,7 +12192,7 @@
         </is>
       </c>
       <c r="H357" s="0">
-        <v>1.35</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="358" spans="1:8">
@@ -12207,7 +12207,7 @@
         </is>
       </c>
       <c r="C358" s="0">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D358" s="0">
         <v>5</v>
@@ -12226,7 +12226,7 @@
         </is>
       </c>
       <c r="H358" s="0">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="359" spans="1:8">
@@ -12241,7 +12241,7 @@
         </is>
       </c>
       <c r="C359" s="0">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D359" s="0">
         <v>5</v>
@@ -12260,7 +12260,7 @@
         </is>
       </c>
       <c r="H359" s="0">
-        <v>1.47</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="360" spans="1:8">
@@ -12275,7 +12275,7 @@
         </is>
       </c>
       <c r="C360" s="0">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D360" s="0">
         <v>5</v>
@@ -12294,7 +12294,7 @@
         </is>
       </c>
       <c r="H360" s="0">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="361" spans="1:8">
@@ -12309,10 +12309,10 @@
         </is>
       </c>
       <c r="C361" s="0">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="D361" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E361" s="0">
         <v>2023</v>
@@ -12328,7 +12328,7 @@
         </is>
       </c>
       <c r="H361" s="0">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="362" spans="1:8">
@@ -12343,10 +12343,10 @@
         </is>
       </c>
       <c r="C362" s="0">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="D362" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E362" s="0">
         <v>2023</v>
@@ -12362,7 +12362,7 @@
         </is>
       </c>
       <c r="H362" s="0">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="363" spans="1:8">
@@ -12377,7 +12377,7 @@
         </is>
       </c>
       <c r="C363" s="0">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D363" s="0">
         <v>4</v>
@@ -12396,7 +12396,7 @@
         </is>
       </c>
       <c r="H363" s="0">
-        <v>1.58</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="364" spans="1:8">
@@ -12411,7 +12411,7 @@
         </is>
       </c>
       <c r="C364" s="0">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D364" s="0">
         <v>4</v>
@@ -12430,7 +12430,7 @@
         </is>
       </c>
       <c r="H364" s="0">
-        <v>2.76</v>
+        <v>2.51</v>
       </c>
     </row>
     <row r="365" spans="1:8">
@@ -12445,7 +12445,7 @@
         </is>
       </c>
       <c r="C365" s="0">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D365" s="0">
         <v>4</v>
@@ -12464,7 +12464,7 @@
         </is>
       </c>
       <c r="H365" s="0">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="366" spans="1:8">
@@ -12479,7 +12479,7 @@
         </is>
       </c>
       <c r="C366" s="0">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D366" s="0">
         <v>4</v>
@@ -12498,7 +12498,7 @@
         </is>
       </c>
       <c r="H366" s="0">
-        <v>2.84</v>
+        <v>2.76</v>
       </c>
     </row>
     <row r="367" spans="1:8">
@@ -12513,7 +12513,7 @@
         </is>
       </c>
       <c r="C367" s="0">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D367" s="0">
         <v>4</v>
@@ -12532,7 +12532,7 @@
         </is>
       </c>
       <c r="H367" s="0">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="368" spans="1:8">
@@ -12547,7 +12547,7 @@
         </is>
       </c>
       <c r="C368" s="0">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D368" s="0">
         <v>4</v>
@@ -12566,7 +12566,7 @@
         </is>
       </c>
       <c r="H368" s="0">
-        <v>2.65</v>
+        <v>2.84</v>
       </c>
     </row>
     <row r="369" spans="1:8">
@@ -12581,10 +12581,10 @@
         </is>
       </c>
       <c r="C369" s="0">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="D369" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E369" s="0">
         <v>2023</v>
@@ -12600,7 +12600,7 @@
         </is>
       </c>
       <c r="H369" s="0">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="370" spans="1:8">
@@ -12615,10 +12615,10 @@
         </is>
       </c>
       <c r="C370" s="0">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="D370" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E370" s="0">
         <v>2023</v>
@@ -12634,7 +12634,7 @@
         </is>
       </c>
       <c r="H370" s="0">
-        <v>2.29</v>
+        <v>2.65</v>
       </c>
     </row>
     <row r="371" spans="1:8">
@@ -12649,7 +12649,7 @@
         </is>
       </c>
       <c r="C371" s="0">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="D371" s="0">
         <v>3</v>
@@ -12668,7 +12668,7 @@
         </is>
       </c>
       <c r="H371" s="0">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="372" spans="1:8">
@@ -12683,7 +12683,7 @@
         </is>
       </c>
       <c r="C372" s="0">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="D372" s="0">
         <v>3</v>
@@ -12702,7 +12702,7 @@
         </is>
       </c>
       <c r="H372" s="0">
-        <v>2.36</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="373" spans="1:8">
@@ -12717,7 +12717,7 @@
         </is>
       </c>
       <c r="C373" s="0">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D373" s="0">
         <v>3</v>
@@ -12736,7 +12736,7 @@
         </is>
       </c>
       <c r="H373" s="0">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
     </row>
     <row r="374" spans="1:8">
@@ -12751,7 +12751,7 @@
         </is>
       </c>
       <c r="C374" s="0">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D374" s="0">
         <v>3</v>
@@ -12770,7 +12770,7 @@
         </is>
       </c>
       <c r="H374" s="0">
-        <v>2.48</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="375" spans="1:8">
@@ -12785,7 +12785,7 @@
         </is>
       </c>
       <c r="C375" s="0">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D375" s="0">
         <v>3</v>
@@ -12804,7 +12804,7 @@
         </is>
       </c>
       <c r="H375" s="0">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="376" spans="1:8">
@@ -12819,7 +12819,7 @@
         </is>
       </c>
       <c r="C376" s="0">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D376" s="0">
         <v>3</v>
@@ -12838,7 +12838,7 @@
         </is>
       </c>
       <c r="H376" s="0">
-        <v>3.61</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="377" spans="1:8">
@@ -12853,7 +12853,7 @@
         </is>
       </c>
       <c r="C377" s="0">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D377" s="0">
         <v>3</v>
@@ -12872,7 +12872,7 @@
         </is>
       </c>
       <c r="H377" s="0">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="378" spans="1:8">
@@ -12887,7 +12887,7 @@
         </is>
       </c>
       <c r="C378" s="0">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D378" s="0">
         <v>3</v>
@@ -12906,7 +12906,7 @@
         </is>
       </c>
       <c r="H378" s="0">
-        <v>3.58</v>
+        <v>3.61</v>
       </c>
     </row>
     <row r="379" spans="1:8">
@@ -12921,10 +12921,10 @@
         </is>
       </c>
       <c r="C379" s="0">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="D379" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E379" s="0">
         <v>2023</v>
@@ -12940,7 +12940,7 @@
         </is>
       </c>
       <c r="H379" s="0">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="380" spans="1:8">
@@ -12955,10 +12955,10 @@
         </is>
       </c>
       <c r="C380" s="0">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="D380" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E380" s="0">
         <v>2023</v>
@@ -12974,7 +12974,7 @@
         </is>
       </c>
       <c r="H380" s="0">
-        <v>3.97</v>
+        <v>3.58</v>
       </c>
     </row>
     <row r="381" spans="1:8">
@@ -12989,7 +12989,7 @@
         </is>
       </c>
       <c r="C381" s="0">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D381" s="0">
         <v>2</v>
@@ -13008,7 +13008,7 @@
         </is>
       </c>
       <c r="H381" s="0">
-        <v>1.63</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="382" spans="1:8">
@@ -13023,7 +13023,7 @@
         </is>
       </c>
       <c r="C382" s="0">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D382" s="0">
         <v>2</v>
@@ -13042,7 +13042,7 @@
         </is>
       </c>
       <c r="H382" s="0">
-        <v>4.41</v>
+        <v>3.97</v>
       </c>
     </row>
     <row r="383" spans="1:8">
@@ -13057,7 +13057,7 @@
         </is>
       </c>
       <c r="C383" s="0">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D383" s="0">
         <v>2</v>
@@ -13091,7 +13091,7 @@
         </is>
       </c>
       <c r="C384" s="0">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D384" s="0">
         <v>2</v>
@@ -13110,7 +13110,7 @@
         </is>
       </c>
       <c r="H384" s="0">
-        <v>4.44</v>
+        <v>4.41</v>
       </c>
     </row>
     <row r="385" spans="1:8">
@@ -13125,7 +13125,7 @@
         </is>
       </c>
       <c r="C385" s="0">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D385" s="0">
         <v>2</v>
@@ -13144,7 +13144,7 @@
         </is>
       </c>
       <c r="H385" s="0">
-        <v>1.39</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="386" spans="1:8">
@@ -13159,7 +13159,7 @@
         </is>
       </c>
       <c r="C386" s="0">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D386" s="0">
         <v>2</v>
@@ -13178,7 +13178,7 @@
         </is>
       </c>
       <c r="H386" s="0">
-        <v>4.47</v>
+        <v>4.44</v>
       </c>
     </row>
     <row r="387" spans="1:8">
@@ -13193,10 +13193,10 @@
         </is>
       </c>
       <c r="C387" s="0">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="D387" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E387" s="0">
         <v>2023</v>
@@ -13212,7 +13212,7 @@
         </is>
       </c>
       <c r="H387" s="0">
-        <v>1.18</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="388" spans="1:8">
@@ -13227,10 +13227,10 @@
         </is>
       </c>
       <c r="C388" s="0">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="D388" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E388" s="0">
         <v>2023</v>
@@ -13246,7 +13246,7 @@
         </is>
       </c>
       <c r="H388" s="0">
-        <v>4.37</v>
+        <v>4.47</v>
       </c>
     </row>
     <row r="389" spans="1:8">
@@ -13261,7 +13261,7 @@
         </is>
       </c>
       <c r="C389" s="0">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D389" s="0">
         <v>1</v>
@@ -13280,7 +13280,7 @@
         </is>
       </c>
       <c r="H389" s="0">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="390" spans="1:8">
@@ -13295,7 +13295,7 @@
         </is>
       </c>
       <c r="C390" s="0">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D390" s="0">
         <v>1</v>
@@ -13314,7 +13314,7 @@
         </is>
       </c>
       <c r="H390" s="0">
-        <v>4.51</v>
+        <v>4.37</v>
       </c>
     </row>
     <row r="391" spans="1:8">
@@ -13329,7 +13329,7 @@
         </is>
       </c>
       <c r="C391" s="0">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D391" s="0">
         <v>1</v>
@@ -13348,7 +13348,7 @@
         </is>
       </c>
       <c r="H391" s="0">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="392" spans="1:8">
@@ -13363,7 +13363,7 @@
         </is>
       </c>
       <c r="C392" s="0">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D392" s="0">
         <v>1</v>
@@ -13382,7 +13382,7 @@
         </is>
       </c>
       <c r="H392" s="0">
-        <v>4.56</v>
+        <v>4.51</v>
       </c>
     </row>
     <row r="393" spans="1:8">
@@ -13397,7 +13397,7 @@
         </is>
       </c>
       <c r="C393" s="0">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D393" s="0">
         <v>1</v>
@@ -13416,7 +13416,7 @@
         </is>
       </c>
       <c r="H393" s="0">
-        <v>1.76</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="394" spans="1:8">
@@ -13431,7 +13431,7 @@
         </is>
       </c>
       <c r="C394" s="0">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D394" s="0">
         <v>1</v>
@@ -13450,11 +13450,79 @@
         </is>
       </c>
       <c r="H394" s="0">
+        <v>4.56</v>
+      </c>
+    </row>
+    <row r="395" spans="1:8">
+      <c r="A395" s="0" t="inlineStr">
+        <is>
+          <t>Nanica primeira - produtor</t>
+        </is>
+      </c>
+      <c r="B395" s="0" t="inlineStr">
+        <is>
+          <t>Bom Jesus da Lapa</t>
+        </is>
+      </c>
+      <c r="C395" s="0">
+        <v>6</v>
+      </c>
+      <c r="D395" s="0">
+        <v>1</v>
+      </c>
+      <c r="E395" s="0">
+        <v>2023</v>
+      </c>
+      <c r="F395" s="0" t="inlineStr">
+        <is>
+          <t>R$   </t>
+        </is>
+      </c>
+      <c r="G395" s="0" t="inlineStr">
+        <is>
+          <t>quilograma</t>
+        </is>
+      </c>
+      <c r="H395" s="0">
+        <v>1.76</v>
+      </c>
+    </row>
+    <row r="396" spans="1:8">
+      <c r="A396" s="0" t="inlineStr">
+        <is>
+          <t>Prata anã primeira - produtor</t>
+        </is>
+      </c>
+      <c r="B396" s="0" t="inlineStr">
+        <is>
+          <t>Bom Jesus da Lapa</t>
+        </is>
+      </c>
+      <c r="C396" s="0">
+        <v>6</v>
+      </c>
+      <c r="D396" s="0">
+        <v>1</v>
+      </c>
+      <c r="E396" s="0">
+        <v>2023</v>
+      </c>
+      <c r="F396" s="0" t="inlineStr">
+        <is>
+          <t>R$   </t>
+        </is>
+      </c>
+      <c r="G396" s="0" t="inlineStr">
+        <is>
+          <t>quilograma</t>
+        </is>
+      </c>
+      <c r="H396" s="0">
         <v>4.59</v>
       </c>
     </row>
-    <row r="395" spans="1:1">
-      <c r="A395" s="0" t="inlineStr">
+    <row r="397" spans="1:1">
+      <c r="A397" s="0" t="inlineStr">
         <is>
           <t>Fonte: Hortifruti/Cepea</t>
         </is>
